--- a/awim/cal template.xlsx
+++ b/awim/cal template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/640dce341da437cb/02 Time v3 physical Clock/Time v3 Clock camera and image processing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:40009_{B2970093-D86E-46D6-A84B-1B4BF93138CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EA60816-A7F0-4789-BF63-90BECE7F0732}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:40009_{B2970093-D86E-46D6-A84B-1B4BF93138CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5DD7ABE-2E57-4D41-A0A0-19FD6686EC2E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="cal new slayer mobile 16 to 9" sheetId="1" r:id="rId1"/>
+    <sheet name="calibration" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -21,18 +21,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="46">
-  <si>
-    <t>az_sect</t>
-  </si>
-  <si>
-    <t>alt_sect</t>
-  </si>
-  <si>
-    <t>az_rel</t>
-  </si>
-  <si>
-    <t>alt_rel</t>
-  </si>
   <si>
     <t>rec_x</t>
   </si>
@@ -52,22 +40,10 @@
     <t>out2</t>
   </si>
   <si>
-    <t>az_total</t>
-  </si>
-  <si>
-    <t>alt_total</t>
-  </si>
-  <si>
     <t>px_x</t>
   </si>
   <si>
     <t>px_y</t>
-  </si>
-  <si>
-    <t>az</t>
-  </si>
-  <si>
-    <t>alt</t>
   </si>
   <si>
     <t>camera_name</t>
@@ -130,9 +106,6 @@
     <t>target_right</t>
   </si>
   <si>
-    <t>target_pos_azalt_relaim</t>
-  </si>
-  <si>
     <t>target_center_calculated_from_edges</t>
   </si>
   <si>
@@ -158,6 +131,33 @@
   </si>
   <si>
     <t>rotation_error_h_and_px_delta</t>
+  </si>
+  <si>
+    <t>xsph_sect</t>
+  </si>
+  <si>
+    <t>ysph_sect</t>
+  </si>
+  <si>
+    <t>xsph_rel</t>
+  </si>
+  <si>
+    <t>target_pos_xysph_relaim</t>
+  </si>
+  <si>
+    <t>ysph_rel</t>
+  </si>
+  <si>
+    <t>xsph_total</t>
+  </si>
+  <si>
+    <t>ysph_total</t>
+  </si>
+  <si>
+    <t>xsph</t>
+  </si>
+  <si>
+    <t>ysph</t>
   </si>
 </sst>
 </file>
@@ -1033,10 +1033,8 @@
   <dimension ref="A1:P592"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.77734375" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32.6640625" bestFit="1" customWidth="1"/>
@@ -1044,58 +1042,57 @@
     <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="O1" s="3" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -1106,7 +1103,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="1"/>
@@ -1126,7 +1123,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="1"/>
@@ -1146,7 +1143,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="1"/>
@@ -1166,7 +1163,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
@@ -1186,7 +1183,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="1"/>
@@ -1206,7 +1203,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="1"/>
@@ -1226,7 +1223,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
@@ -1246,7 +1243,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
@@ -1266,7 +1263,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="1"/>
@@ -1286,7 +1283,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
@@ -1318,10 +1315,10 @@
         <v>-1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1348,10 +1345,10 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1378,10 +1375,10 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1408,10 +1405,10 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1438,10 +1435,10 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1468,10 +1465,10 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1498,10 +1495,10 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1528,10 +1525,10 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1558,10 +1555,10 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1588,10 +1585,10 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1618,10 +1615,10 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1648,10 +1645,10 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1678,10 +1675,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1708,10 +1705,10 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1738,10 +1735,10 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -1768,10 +1765,10 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1798,10 +1795,10 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -1828,10 +1825,10 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1858,10 +1855,10 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -1888,7 +1885,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1916,7 +1913,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1944,7 +1941,7 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1972,7 +1969,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2000,7 +1997,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2028,7 +2025,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2056,7 +2053,7 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2084,7 +2081,7 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -2112,7 +2109,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -2140,7 +2137,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2168,7 +2165,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -2196,10 +2193,10 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -2226,10 +2223,10 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -2256,10 +2253,10 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -2286,10 +2283,10 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -2316,10 +2313,10 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -2346,10 +2343,10 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -2376,10 +2373,10 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -2406,10 +2403,10 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -2436,10 +2433,10 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -2466,10 +2463,10 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -2496,10 +2493,10 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -2526,10 +2523,10 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -2556,10 +2553,10 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -2586,10 +2583,10 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -2616,10 +2613,10 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -2646,10 +2643,10 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -2676,10 +2673,10 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -2706,10 +2703,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -2736,7 +2733,7 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -2764,7 +2761,7 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -2792,7 +2789,7 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -2820,7 +2817,7 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -2848,7 +2845,7 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -2876,7 +2873,7 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -2904,7 +2901,7 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -2932,7 +2929,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -2960,7 +2957,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -2988,7 +2985,7 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -3016,7 +3013,7 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -3044,10 +3041,10 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -3074,10 +3071,10 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -3104,10 +3101,10 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -3134,10 +3131,10 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -3164,10 +3161,10 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -3194,10 +3191,10 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -3224,10 +3221,10 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -3254,10 +3251,10 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -3284,10 +3281,10 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -3314,10 +3311,10 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -3344,10 +3341,10 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -3374,10 +3371,10 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -3404,10 +3401,10 @@
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -3434,10 +3431,10 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -3464,10 +3461,10 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -3494,10 +3491,10 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -3524,10 +3521,10 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -3554,10 +3551,10 @@
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -3584,7 +3581,7 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -3612,7 +3609,7 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -3640,7 +3637,7 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -3668,7 +3665,7 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -3696,7 +3693,7 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -3724,7 +3721,7 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -3752,7 +3749,7 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -3780,7 +3777,7 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
@@ -3808,7 +3805,7 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
@@ -3836,7 +3833,7 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -3864,7 +3861,7 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
@@ -3892,10 +3889,10 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -3922,10 +3919,10 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -3952,10 +3949,10 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -3982,10 +3979,10 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -4012,10 +4009,10 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -4042,10 +4039,10 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -4072,10 +4069,10 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -4102,10 +4099,10 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H107" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -4132,10 +4129,10 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -4162,10 +4159,10 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H109" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -4192,10 +4189,10 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -4222,10 +4219,10 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -4252,10 +4249,10 @@
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -4282,10 +4279,10 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -4312,10 +4309,10 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -4342,10 +4339,10 @@
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -4372,10 +4369,10 @@
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -4402,10 +4399,10 @@
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -4432,7 +4429,7 @@
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -4460,7 +4457,7 @@
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -4488,7 +4485,7 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
@@ -4516,7 +4513,7 @@
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
@@ -4544,7 +4541,7 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
@@ -4572,7 +4569,7 @@
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
@@ -4600,7 +4597,7 @@
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
@@ -4628,7 +4625,7 @@
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
@@ -4656,7 +4653,7 @@
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
@@ -4684,7 +4681,7 @@
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -4712,7 +4709,7 @@
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
@@ -4740,10 +4737,10 @@
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
@@ -4770,10 +4767,10 @@
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
@@ -4800,10 +4797,10 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -4830,10 +4827,10 @@
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -4860,10 +4857,10 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -4890,10 +4887,10 @@
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
@@ -4920,10 +4917,10 @@
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -4950,10 +4947,10 @@
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H136" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
@@ -4980,10 +4977,10 @@
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -5010,10 +5007,10 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H138" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H138" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -5040,10 +5037,10 @@
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -5070,10 +5067,10 @@
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -5100,10 +5097,10 @@
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
@@ -5130,10 +5127,10 @@
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -5160,10 +5157,10 @@
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
@@ -5190,10 +5187,10 @@
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
@@ -5220,10 +5217,10 @@
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
@@ -5250,10 +5247,10 @@
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -5280,7 +5277,7 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
@@ -5308,7 +5305,7 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
@@ -5336,7 +5333,7 @@
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
@@ -5364,7 +5361,7 @@
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
@@ -5392,7 +5389,7 @@
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
@@ -5420,7 +5417,7 @@
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
@@ -5448,7 +5445,7 @@
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
@@ -5476,7 +5473,7 @@
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
@@ -5504,7 +5501,7 @@
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
@@ -5532,7 +5529,7 @@
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
@@ -5560,7 +5557,7 @@
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
@@ -5588,10 +5585,10 @@
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
@@ -5618,10 +5615,10 @@
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
@@ -5648,10 +5645,10 @@
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
@@ -5678,10 +5675,10 @@
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
@@ -5708,10 +5705,10 @@
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
@@ -5738,10 +5735,10 @@
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
@@ -5768,10 +5765,10 @@
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -5798,10 +5795,10 @@
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H165" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
@@ -5828,10 +5825,10 @@
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
@@ -5858,10 +5855,10 @@
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H167" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H167" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
@@ -5888,10 +5885,10 @@
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
@@ -5918,10 +5915,10 @@
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
@@ -5948,10 +5945,10 @@
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
@@ -5978,10 +5975,10 @@
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
@@ -6008,10 +6005,10 @@
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
@@ -6038,10 +6035,10 @@
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
@@ -6068,10 +6065,10 @@
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
@@ -6098,10 +6095,10 @@
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
       <c r="G175" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
@@ -6128,7 +6125,7 @@
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
@@ -6156,7 +6153,7 @@
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
@@ -6184,7 +6181,7 @@
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
@@ -6212,7 +6209,7 @@
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
@@ -6240,7 +6237,7 @@
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
@@ -6268,7 +6265,7 @@
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
@@ -6296,7 +6293,7 @@
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
@@ -6324,7 +6321,7 @@
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
@@ -6352,7 +6349,7 @@
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
@@ -6380,7 +6377,7 @@
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
@@ -6408,7 +6405,7 @@
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
@@ -6436,10 +6433,10 @@
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I187" s="1"/>
       <c r="J187" s="1"/>
@@ -6466,10 +6463,10 @@
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
@@ -6496,10 +6493,10 @@
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
@@ -6526,10 +6523,10 @@
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
@@ -6556,10 +6553,10 @@
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I191" s="1"/>
       <c r="J191" s="1"/>
@@ -6586,10 +6583,10 @@
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I192" s="1"/>
       <c r="J192" s="1"/>
@@ -6616,10 +6613,10 @@
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I193" s="1"/>
       <c r="J193" s="1"/>
@@ -6646,10 +6643,10 @@
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H194" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H194" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I194" s="1"/>
       <c r="J194" s="1"/>
@@ -6676,10 +6673,10 @@
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I195" s="1"/>
       <c r="J195" s="1"/>
@@ -6706,10 +6703,10 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H196" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H196" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I196" s="1"/>
       <c r="J196" s="1"/>
@@ -6736,10 +6733,10 @@
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I197" s="1"/>
       <c r="J197" s="1"/>
@@ -6766,10 +6763,10 @@
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I198" s="1"/>
       <c r="J198" s="1"/>
@@ -6796,10 +6793,10 @@
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I199" s="1"/>
       <c r="J199" s="1"/>
@@ -6826,10 +6823,10 @@
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I200" s="1"/>
       <c r="J200" s="1"/>
@@ -6856,10 +6853,10 @@
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I201" s="1"/>
       <c r="J201" s="1"/>
@@ -6886,10 +6883,10 @@
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I202" s="1"/>
       <c r="J202" s="1"/>
@@ -6916,10 +6913,10 @@
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I203" s="1"/>
       <c r="J203" s="1"/>
@@ -6946,10 +6943,10 @@
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I204" s="1"/>
       <c r="J204" s="1"/>
@@ -6976,7 +6973,7 @@
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
       <c r="G205" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H205" s="1"/>
       <c r="I205" s="1"/>
@@ -7004,7 +7001,7 @@
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
       <c r="G206" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
@@ -7032,7 +7029,7 @@
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
       <c r="G207" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H207" s="1"/>
       <c r="I207" s="1"/>
@@ -7060,7 +7057,7 @@
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
       <c r="G208" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H208" s="1"/>
       <c r="I208" s="1"/>
@@ -7088,7 +7085,7 @@
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
       <c r="G209" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H209" s="1"/>
       <c r="I209" s="1"/>
@@ -7116,7 +7113,7 @@
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
       <c r="G210" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H210" s="1"/>
       <c r="I210" s="1"/>
@@ -7144,7 +7141,7 @@
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
       <c r="G211" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H211" s="1"/>
       <c r="I211" s="1"/>
@@ -7172,7 +7169,7 @@
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
       <c r="G212" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
@@ -7200,7 +7197,7 @@
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
       <c r="G213" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H213" s="1"/>
       <c r="I213" s="1"/>
@@ -7228,7 +7225,7 @@
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
       <c r="G214" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H214" s="1"/>
       <c r="I214" s="1"/>
@@ -7256,7 +7253,7 @@
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
       <c r="G215" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H215" s="1"/>
       <c r="I215" s="1"/>
@@ -7284,10 +7281,10 @@
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I216" s="1"/>
       <c r="J216" s="1"/>
@@ -7314,10 +7311,10 @@
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
       <c r="G217" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I217" s="1"/>
       <c r="J217" s="1"/>
@@ -7344,10 +7341,10 @@
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
       <c r="G218" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I218" s="1"/>
       <c r="J218" s="1"/>
@@ -7374,10 +7371,10 @@
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
       <c r="G219" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I219" s="1"/>
       <c r="J219" s="1"/>
@@ -7404,10 +7401,10 @@
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
       <c r="G220" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I220" s="1"/>
       <c r="J220" s="1"/>
@@ -7434,10 +7431,10 @@
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
       <c r="G221" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I221" s="1"/>
       <c r="J221" s="1"/>
@@ -7464,10 +7461,10 @@
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I222" s="1"/>
       <c r="J222" s="1"/>
@@ -7494,10 +7491,10 @@
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H223" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H223" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I223" s="1"/>
       <c r="J223" s="1"/>
@@ -7524,10 +7521,10 @@
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I224" s="1"/>
       <c r="J224" s="1"/>
@@ -7554,10 +7551,10 @@
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H225" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H225" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I225" s="1"/>
       <c r="J225" s="1"/>
@@ -7584,10 +7581,10 @@
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
       <c r="G226" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I226" s="1"/>
       <c r="J226" s="1"/>
@@ -7614,10 +7611,10 @@
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I227" s="1"/>
       <c r="J227" s="1"/>
@@ -7644,10 +7641,10 @@
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I228" s="1"/>
       <c r="J228" s="1"/>
@@ -7674,10 +7671,10 @@
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I229" s="1"/>
       <c r="J229" s="1"/>
@@ -7704,10 +7701,10 @@
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I230" s="1"/>
       <c r="J230" s="1"/>
@@ -7734,10 +7731,10 @@
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
       <c r="G231" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I231" s="1"/>
       <c r="J231" s="1"/>
@@ -7764,10 +7761,10 @@
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I232" s="1"/>
       <c r="J232" s="1"/>
@@ -7794,10 +7791,10 @@
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I233" s="1"/>
       <c r="J233" s="1"/>
@@ -7824,7 +7821,7 @@
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
       <c r="G234" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
@@ -7852,7 +7849,7 @@
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
@@ -7880,7 +7877,7 @@
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
@@ -7908,7 +7905,7 @@
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
       <c r="G237" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
@@ -7936,7 +7933,7 @@
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
       <c r="G238" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H238" s="1"/>
       <c r="I238" s="1"/>
@@ -7964,7 +7961,7 @@
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
@@ -7992,7 +7989,7 @@
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
@@ -8020,7 +8017,7 @@
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
       <c r="G241" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
@@ -8048,7 +8045,7 @@
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
@@ -8076,7 +8073,7 @@
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
@@ -8104,7 +8101,7 @@
       <c r="E244" s="2"/>
       <c r="F244" s="2"/>
       <c r="G244" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
@@ -8132,10 +8129,10 @@
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I245" s="1"/>
       <c r="J245" s="1"/>
@@ -8162,10 +8159,10 @@
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I246" s="1"/>
       <c r="J246" s="1"/>
@@ -8192,10 +8189,10 @@
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I247" s="1"/>
       <c r="J247" s="1"/>
@@ -8222,10 +8219,10 @@
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I248" s="1"/>
       <c r="J248" s="1"/>
@@ -8252,10 +8249,10 @@
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
       <c r="G249" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I249" s="1"/>
       <c r="J249" s="1"/>
@@ -8282,10 +8279,10 @@
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
       <c r="G250" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
@@ -8312,10 +8309,10 @@
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I251" s="1"/>
       <c r="J251" s="1"/>
@@ -8342,10 +8339,10 @@
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H252" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H252" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I252" s="1"/>
       <c r="J252" s="1"/>
@@ -8372,10 +8369,10 @@
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
       <c r="G253" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I253" s="1"/>
       <c r="J253" s="1"/>
@@ -8402,10 +8399,10 @@
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
       <c r="G254" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H254" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H254" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
@@ -8432,10 +8429,10 @@
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
       <c r="G255" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I255" s="1"/>
       <c r="J255" s="1"/>
@@ -8462,10 +8459,10 @@
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I256" s="1"/>
       <c r="J256" s="1"/>
@@ -8492,10 +8489,10 @@
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I257" s="1"/>
       <c r="J257" s="1"/>
@@ -8522,10 +8519,10 @@
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
       <c r="G258" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
@@ -8552,10 +8549,10 @@
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
       <c r="G259" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I259" s="1"/>
       <c r="J259" s="1"/>
@@ -8582,10 +8579,10 @@
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
       <c r="G260" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
@@ -8612,10 +8609,10 @@
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
@@ -8642,10 +8639,10 @@
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
@@ -8672,7 +8669,7 @@
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
       <c r="G263" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
@@ -8700,7 +8697,7 @@
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
       <c r="G264" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
@@ -8728,7 +8725,7 @@
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
@@ -8756,7 +8753,7 @@
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
       <c r="G266" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
@@ -8784,7 +8781,7 @@
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
       <c r="G267" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H267" s="1"/>
       <c r="I267" s="1"/>
@@ -8812,7 +8809,7 @@
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
       <c r="G268" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H268" s="1"/>
       <c r="I268" s="1"/>
@@ -8840,7 +8837,7 @@
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
       <c r="G269" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H269" s="1"/>
       <c r="I269" s="1"/>
@@ -8868,7 +8865,7 @@
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
       <c r="G270" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H270" s="1"/>
       <c r="I270" s="1"/>
@@ -8896,7 +8893,7 @@
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
       <c r="G271" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H271" s="1"/>
       <c r="I271" s="1"/>
@@ -8924,7 +8921,7 @@
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
       <c r="G272" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
@@ -8952,7 +8949,7 @@
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
       <c r="G273" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H273" s="1"/>
       <c r="I273" s="1"/>
@@ -8980,10 +8977,10 @@
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I274" s="1"/>
       <c r="J274" s="1"/>
@@ -9010,10 +9007,10 @@
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
       <c r="G275" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I275" s="1"/>
       <c r="J275" s="1"/>
@@ -9040,10 +9037,10 @@
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
       <c r="G276" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I276" s="1"/>
       <c r="J276" s="1"/>
@@ -9070,10 +9067,10 @@
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
       <c r="G277" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I277" s="1"/>
       <c r="J277" s="1"/>
@@ -9100,10 +9097,10 @@
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
       <c r="G278" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I278" s="1"/>
       <c r="J278" s="1"/>
@@ -9130,10 +9127,10 @@
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
       <c r="G279" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I279" s="1"/>
       <c r="J279" s="1"/>
@@ -9160,10 +9157,10 @@
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I280" s="1"/>
       <c r="J280" s="1"/>
@@ -9190,10 +9187,10 @@
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H281" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H281" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I281" s="1"/>
       <c r="J281" s="1"/>
@@ -9220,10 +9217,10 @@
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
       <c r="G282" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I282" s="1"/>
       <c r="J282" s="1"/>
@@ -9250,10 +9247,10 @@
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
       <c r="G283" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H283" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H283" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I283" s="1"/>
       <c r="J283" s="1"/>
@@ -9280,10 +9277,10 @@
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
       <c r="G284" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I284" s="1"/>
       <c r="J284" s="1"/>
@@ -9310,10 +9307,10 @@
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I285" s="1"/>
       <c r="J285" s="1"/>
@@ -9340,10 +9337,10 @@
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
@@ -9370,10 +9367,10 @@
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
       <c r="G287" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
@@ -9400,10 +9397,10 @@
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
       <c r="G288" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I288" s="1"/>
       <c r="J288" s="1"/>
@@ -9430,10 +9427,10 @@
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
       <c r="G289" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I289" s="1"/>
       <c r="J289" s="1"/>
@@ -9460,10 +9457,10 @@
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I290" s="1"/>
       <c r="J290" s="1"/>
@@ -9490,10 +9487,10 @@
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I291" s="1"/>
       <c r="J291" s="1"/>
@@ -9520,7 +9517,7 @@
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
       <c r="G292" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H292" s="1"/>
       <c r="I292" s="1"/>
@@ -9548,7 +9545,7 @@
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
       <c r="G293" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H293" s="1"/>
       <c r="I293" s="1"/>
@@ -9576,7 +9573,7 @@
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
       <c r="G294" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H294" s="1"/>
       <c r="I294" s="1"/>
@@ -9604,7 +9601,7 @@
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
       <c r="G295" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H295" s="1"/>
       <c r="I295" s="1"/>
@@ -9632,7 +9629,7 @@
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
       <c r="G296" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H296" s="1"/>
       <c r="I296" s="1"/>
@@ -9660,7 +9657,7 @@
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
       <c r="G297" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H297" s="1"/>
       <c r="I297" s="1"/>
@@ -9688,7 +9685,7 @@
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
       <c r="G298" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H298" s="1"/>
       <c r="I298" s="1"/>
@@ -9716,7 +9713,7 @@
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
       <c r="G299" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H299" s="1"/>
       <c r="I299" s="1"/>
@@ -9744,7 +9741,7 @@
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
       <c r="G300" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
@@ -9772,7 +9769,7 @@
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
       <c r="G301" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H301" s="1"/>
       <c r="I301" s="1"/>
@@ -9800,7 +9797,7 @@
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
       <c r="G302" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H302" s="1"/>
       <c r="I302" s="1"/>
@@ -9828,10 +9825,10 @@
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H303" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I303" s="1"/>
       <c r="J303" s="1"/>
@@ -9858,10 +9855,10 @@
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
       <c r="G304" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I304" s="1"/>
       <c r="J304" s="1"/>
@@ -9888,10 +9885,10 @@
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
       <c r="G305" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I305" s="1"/>
       <c r="J305" s="1"/>
@@ -9918,10 +9915,10 @@
       <c r="E306" s="2"/>
       <c r="F306" s="2"/>
       <c r="G306" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
@@ -9948,10 +9945,10 @@
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
       <c r="G307" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I307" s="1"/>
       <c r="J307" s="1"/>
@@ -9978,10 +9975,10 @@
       <c r="E308" s="2"/>
       <c r="F308" s="2"/>
       <c r="G308" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
@@ -10008,10 +10005,10 @@
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I309" s="1"/>
       <c r="J309" s="1"/>
@@ -10038,10 +10035,10 @@
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H310" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H310" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I310" s="1"/>
       <c r="J310" s="1"/>
@@ -10068,10 +10065,10 @@
       <c r="E311" s="2"/>
       <c r="F311" s="2"/>
       <c r="G311" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I311" s="1"/>
       <c r="J311" s="1"/>
@@ -10098,10 +10095,10 @@
       <c r="E312" s="2"/>
       <c r="F312" s="2"/>
       <c r="G312" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H312" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H312" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I312" s="1"/>
       <c r="J312" s="1"/>
@@ -10128,10 +10125,10 @@
       <c r="E313" s="2"/>
       <c r="F313" s="2"/>
       <c r="G313" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
@@ -10158,10 +10155,10 @@
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I314" s="1"/>
       <c r="J314" s="1"/>
@@ -10188,10 +10185,10 @@
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I315" s="1"/>
       <c r="J315" s="1"/>
@@ -10218,10 +10215,10 @@
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
       <c r="G316" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I316" s="1"/>
       <c r="J316" s="1"/>
@@ -10248,10 +10245,10 @@
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
       <c r="G317" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I317" s="1"/>
       <c r="J317" s="1"/>
@@ -10278,10 +10275,10 @@
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
       <c r="G318" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I318" s="1"/>
       <c r="J318" s="1"/>
@@ -10308,10 +10305,10 @@
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I319" s="1"/>
       <c r="J319" s="1"/>
@@ -10338,10 +10335,10 @@
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
       <c r="G320" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I320" s="1"/>
       <c r="J320" s="1"/>
@@ -10368,7 +10365,7 @@
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
       <c r="G321" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H321" s="1"/>
       <c r="I321" s="1"/>
@@ -10396,7 +10393,7 @@
       <c r="E322" s="2"/>
       <c r="F322" s="2"/>
       <c r="G322" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H322" s="1"/>
       <c r="I322" s="1"/>
@@ -10424,7 +10421,7 @@
       <c r="E323" s="2"/>
       <c r="F323" s="2"/>
       <c r="G323" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H323" s="1"/>
       <c r="I323" s="1"/>
@@ -10452,7 +10449,7 @@
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
       <c r="G324" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H324" s="1"/>
       <c r="I324" s="1"/>
@@ -10480,7 +10477,7 @@
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
       <c r="G325" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H325" s="1"/>
       <c r="I325" s="1"/>
@@ -10508,7 +10505,7 @@
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
       <c r="G326" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H326" s="1"/>
       <c r="I326" s="1"/>
@@ -10536,7 +10533,7 @@
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
       <c r="G327" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H327" s="1"/>
       <c r="I327" s="1"/>
@@ -10564,7 +10561,7 @@
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
       <c r="G328" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H328" s="1"/>
       <c r="I328" s="1"/>
@@ -10592,7 +10589,7 @@
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
       <c r="G329" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H329" s="1"/>
       <c r="I329" s="1"/>
@@ -10620,7 +10617,7 @@
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
       <c r="G330" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H330" s="1"/>
       <c r="I330" s="1"/>
@@ -10648,7 +10645,7 @@
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
       <c r="G331" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H331" s="1"/>
       <c r="I331" s="1"/>
@@ -10676,10 +10673,10 @@
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H332" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I332" s="1"/>
       <c r="J332" s="1"/>
@@ -10706,10 +10703,10 @@
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
       <c r="G333" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I333" s="1"/>
       <c r="J333" s="1"/>
@@ -10736,10 +10733,10 @@
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
       <c r="G334" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I334" s="1"/>
       <c r="J334" s="1"/>
@@ -10766,10 +10763,10 @@
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
       <c r="G335" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I335" s="1"/>
       <c r="J335" s="1"/>
@@ -10796,10 +10793,10 @@
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
       <c r="G336" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I336" s="1"/>
       <c r="J336" s="1"/>
@@ -10826,10 +10823,10 @@
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
       <c r="G337" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
@@ -10856,10 +10853,10 @@
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I338" s="1"/>
       <c r="J338" s="1"/>
@@ -10886,10 +10883,10 @@
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H339" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H339" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I339" s="1"/>
       <c r="J339" s="1"/>
@@ -10916,10 +10913,10 @@
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
       <c r="G340" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I340" s="1"/>
       <c r="J340" s="1"/>
@@ -10946,10 +10943,10 @@
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
       <c r="G341" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H341" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H341" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
@@ -10976,10 +10973,10 @@
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
       <c r="G342" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I342" s="1"/>
       <c r="J342" s="1"/>
@@ -11006,10 +11003,10 @@
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I343" s="1"/>
       <c r="J343" s="1"/>
@@ -11036,10 +11033,10 @@
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I344" s="1"/>
       <c r="J344" s="1"/>
@@ -11066,10 +11063,10 @@
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
       <c r="G345" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I345" s="1"/>
       <c r="J345" s="1"/>
@@ -11096,10 +11093,10 @@
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
       <c r="G346" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I346" s="1"/>
       <c r="J346" s="1"/>
@@ -11126,10 +11123,10 @@
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
       <c r="G347" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I347" s="1"/>
       <c r="J347" s="1"/>
@@ -11156,10 +11153,10 @@
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
@@ -11186,10 +11183,10 @@
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
       <c r="G349" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I349" s="1"/>
       <c r="J349" s="1"/>
@@ -11216,7 +11213,7 @@
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
       <c r="G350" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H350" s="1"/>
       <c r="I350" s="1"/>
@@ -11244,7 +11241,7 @@
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
       <c r="G351" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H351" s="1"/>
       <c r="I351" s="1"/>
@@ -11272,7 +11269,7 @@
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
       <c r="G352" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H352" s="1"/>
       <c r="I352" s="1"/>
@@ -11300,7 +11297,7 @@
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
       <c r="G353" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H353" s="1"/>
       <c r="I353" s="1"/>
@@ -11328,7 +11325,7 @@
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
       <c r="G354" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
@@ -11356,7 +11353,7 @@
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
       <c r="G355" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
@@ -11384,7 +11381,7 @@
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
       <c r="G356" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H356" s="1"/>
       <c r="I356" s="1"/>
@@ -11412,7 +11409,7 @@
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
       <c r="G357" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H357" s="1"/>
       <c r="I357" s="1"/>
@@ -11440,7 +11437,7 @@
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
       <c r="G358" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H358" s="1"/>
       <c r="I358" s="1"/>
@@ -11468,7 +11465,7 @@
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
       <c r="G359" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H359" s="1"/>
       <c r="I359" s="1"/>
@@ -11496,7 +11493,7 @@
       <c r="E360" s="2"/>
       <c r="F360" s="2"/>
       <c r="G360" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H360" s="1"/>
       <c r="I360" s="1"/>
@@ -11524,10 +11521,10 @@
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H361" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I361" s="1"/>
       <c r="J361" s="1"/>
@@ -11554,10 +11551,10 @@
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
       <c r="G362" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
@@ -11584,10 +11581,10 @@
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
       <c r="G363" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I363" s="1"/>
       <c r="J363" s="1"/>
@@ -11614,10 +11611,10 @@
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
       <c r="G364" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H364" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I364" s="1"/>
       <c r="J364" s="1"/>
@@ -11644,10 +11641,10 @@
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
       <c r="G365" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H365" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I365" s="1"/>
       <c r="J365" s="1"/>
@@ -11674,10 +11671,10 @@
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
       <c r="G366" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H366" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
@@ -11704,10 +11701,10 @@
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
       <c r="G367" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H367" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I367" s="1"/>
       <c r="J367" s="1"/>
@@ -11734,10 +11731,10 @@
       <c r="E368" s="1"/>
       <c r="F368" s="1"/>
       <c r="G368" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H368" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H368" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
@@ -11764,10 +11761,10 @@
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
       <c r="G369" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H369" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I369" s="1"/>
       <c r="J369" s="1"/>
@@ -11794,10 +11791,10 @@
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
       <c r="G370" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H370" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H370" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
@@ -11824,10 +11821,10 @@
       <c r="E371" s="2"/>
       <c r="F371" s="2"/>
       <c r="G371" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H371" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
@@ -11854,10 +11851,10 @@
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
       <c r="G372" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H372" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
@@ -11884,10 +11881,10 @@
       <c r="E373" s="1"/>
       <c r="F373" s="1"/>
       <c r="G373" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
@@ -11914,10 +11911,10 @@
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
       <c r="G374" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I374" s="1"/>
       <c r="J374" s="1"/>
@@ -11944,10 +11941,10 @@
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
       <c r="G375" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I375" s="1"/>
       <c r="J375" s="1"/>
@@ -11974,10 +11971,10 @@
       <c r="E376" s="2"/>
       <c r="F376" s="2"/>
       <c r="G376" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H376" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
@@ -12004,10 +12001,10 @@
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
       <c r="G377" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H377" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I377" s="1"/>
       <c r="J377" s="1"/>
@@ -12034,10 +12031,10 @@
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
       <c r="G378" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H378" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I378" s="1"/>
       <c r="J378" s="1"/>
@@ -12064,7 +12061,7 @@
       <c r="E379" s="2"/>
       <c r="F379" s="2"/>
       <c r="G379" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H379" s="1"/>
       <c r="I379" s="1"/>
@@ -12092,7 +12089,7 @@
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
       <c r="G380" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H380" s="1"/>
       <c r="I380" s="1"/>
@@ -12120,7 +12117,7 @@
       <c r="E381" s="2"/>
       <c r="F381" s="2"/>
       <c r="G381" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H381" s="1"/>
       <c r="I381" s="1"/>
@@ -12148,7 +12145,7 @@
       <c r="E382" s="2"/>
       <c r="F382" s="2"/>
       <c r="G382" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H382" s="1"/>
       <c r="I382" s="1"/>
@@ -12176,7 +12173,7 @@
       <c r="E383" s="2"/>
       <c r="F383" s="2"/>
       <c r="G383" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H383" s="1"/>
       <c r="I383" s="1"/>
@@ -12204,7 +12201,7 @@
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
       <c r="G384" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H384" s="1"/>
       <c r="I384" s="1"/>
@@ -12232,7 +12229,7 @@
       <c r="E385" s="2"/>
       <c r="F385" s="2"/>
       <c r="G385" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H385" s="1"/>
       <c r="I385" s="1"/>
@@ -12260,7 +12257,7 @@
       <c r="E386" s="2"/>
       <c r="F386" s="2"/>
       <c r="G386" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H386" s="1"/>
       <c r="I386" s="1"/>
@@ -12288,7 +12285,7 @@
       <c r="E387" s="2"/>
       <c r="F387" s="2"/>
       <c r="G387" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H387" s="1"/>
       <c r="I387" s="1"/>
@@ -12316,7 +12313,7 @@
       <c r="E388" s="2"/>
       <c r="F388" s="2"/>
       <c r="G388" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H388" s="1"/>
       <c r="I388" s="1"/>
@@ -12344,7 +12341,7 @@
       <c r="E389" s="2"/>
       <c r="F389" s="2"/>
       <c r="G389" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H389" s="1"/>
       <c r="I389" s="1"/>
@@ -12372,10 +12369,10 @@
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H390" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I390" s="1"/>
       <c r="J390" s="1"/>
@@ -12402,10 +12399,10 @@
       <c r="E391" s="2"/>
       <c r="F391" s="2"/>
       <c r="G391" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I391" s="1"/>
       <c r="J391" s="1"/>
@@ -12432,10 +12429,10 @@
       <c r="E392" s="2"/>
       <c r="F392" s="2"/>
       <c r="G392" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H392" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I392" s="1"/>
       <c r="J392" s="1"/>
@@ -12462,10 +12459,10 @@
       <c r="E393" s="2"/>
       <c r="F393" s="2"/>
       <c r="G393" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I393" s="1"/>
       <c r="J393" s="1"/>
@@ -12492,10 +12489,10 @@
       <c r="E394" s="2"/>
       <c r="F394" s="2"/>
       <c r="G394" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H394" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I394" s="1"/>
       <c r="J394" s="1"/>
@@ -12522,10 +12519,10 @@
       <c r="E395" s="2"/>
       <c r="F395" s="2"/>
       <c r="G395" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H395" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I395" s="1"/>
       <c r="J395" s="1"/>
@@ -12552,10 +12549,10 @@
       <c r="E396" s="1"/>
       <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H396" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I396" s="1"/>
       <c r="J396" s="1"/>
@@ -12582,10 +12579,10 @@
       <c r="E397" s="1"/>
       <c r="F397" s="1"/>
       <c r="G397" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H397" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H397" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I397" s="1"/>
       <c r="J397" s="1"/>
@@ -12612,10 +12609,10 @@
       <c r="E398" s="2"/>
       <c r="F398" s="2"/>
       <c r="G398" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H398" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I398" s="1"/>
       <c r="J398" s="1"/>
@@ -12642,10 +12639,10 @@
       <c r="E399" s="2"/>
       <c r="F399" s="2"/>
       <c r="G399" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H399" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H399" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I399" s="1"/>
       <c r="J399" s="1"/>
@@ -12672,10 +12669,10 @@
       <c r="E400" s="2"/>
       <c r="F400" s="2"/>
       <c r="G400" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H400" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I400" s="1"/>
       <c r="J400" s="1"/>
@@ -12702,10 +12699,10 @@
       <c r="E401" s="1"/>
       <c r="F401" s="1"/>
       <c r="G401" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H401" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I401" s="1"/>
       <c r="J401" s="1"/>
@@ -12732,10 +12729,10 @@
       <c r="E402" s="1"/>
       <c r="F402" s="1"/>
       <c r="G402" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H402" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I402" s="1"/>
       <c r="J402" s="1"/>
@@ -12762,10 +12759,10 @@
       <c r="E403" s="2"/>
       <c r="F403" s="2"/>
       <c r="G403" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H403" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I403" s="1"/>
       <c r="J403" s="1"/>
@@ -12792,10 +12789,10 @@
       <c r="E404" s="2"/>
       <c r="F404" s="2"/>
       <c r="G404" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H404" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I404" s="1"/>
       <c r="J404" s="1"/>
@@ -12822,10 +12819,10 @@
       <c r="E405" s="2"/>
       <c r="F405" s="2"/>
       <c r="G405" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H405" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I405" s="1"/>
       <c r="J405" s="1"/>
@@ -12852,10 +12849,10 @@
       <c r="E406" s="1"/>
       <c r="F406" s="1"/>
       <c r="G406" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H406" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I406" s="1"/>
       <c r="J406" s="1"/>
@@ -12882,10 +12879,10 @@
       <c r="E407" s="1"/>
       <c r="F407" s="1"/>
       <c r="G407" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H407" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I407" s="1"/>
       <c r="J407" s="1"/>
@@ -12912,7 +12909,7 @@
       <c r="E408" s="2"/>
       <c r="F408" s="2"/>
       <c r="G408" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H408" s="1"/>
       <c r="I408" s="1"/>
@@ -12940,7 +12937,7 @@
       <c r="E409" s="2"/>
       <c r="F409" s="2"/>
       <c r="G409" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H409" s="1"/>
       <c r="I409" s="1"/>
@@ -12968,7 +12965,7 @@
       <c r="E410" s="2"/>
       <c r="F410" s="2"/>
       <c r="G410" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H410" s="1"/>
       <c r="I410" s="1"/>
@@ -12996,7 +12993,7 @@
       <c r="E411" s="2"/>
       <c r="F411" s="2"/>
       <c r="G411" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H411" s="1"/>
       <c r="I411" s="1"/>
@@ -13024,7 +13021,7 @@
       <c r="E412" s="2"/>
       <c r="F412" s="2"/>
       <c r="G412" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H412" s="1"/>
       <c r="I412" s="1"/>
@@ -13052,7 +13049,7 @@
       <c r="E413" s="2"/>
       <c r="F413" s="2"/>
       <c r="G413" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H413" s="1"/>
       <c r="I413" s="1"/>
@@ -13080,7 +13077,7 @@
       <c r="E414" s="2"/>
       <c r="F414" s="2"/>
       <c r="G414" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H414" s="1"/>
       <c r="I414" s="1"/>
@@ -13108,7 +13105,7 @@
       <c r="E415" s="2"/>
       <c r="F415" s="2"/>
       <c r="G415" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H415" s="1"/>
       <c r="I415" s="1"/>
@@ -13136,7 +13133,7 @@
       <c r="E416" s="2"/>
       <c r="F416" s="2"/>
       <c r="G416" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H416" s="1"/>
       <c r="I416" s="1"/>
@@ -13164,7 +13161,7 @@
       <c r="E417" s="2"/>
       <c r="F417" s="2"/>
       <c r="G417" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H417" s="1"/>
       <c r="I417" s="1"/>
@@ -13192,7 +13189,7 @@
       <c r="E418" s="2"/>
       <c r="F418" s="2"/>
       <c r="G418" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H418" s="1"/>
       <c r="I418" s="1"/>
@@ -13220,10 +13217,10 @@
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
       <c r="G419" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H419" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I419" s="1"/>
       <c r="J419" s="1"/>
@@ -13250,10 +13247,10 @@
       <c r="E420" s="2"/>
       <c r="F420" s="2"/>
       <c r="G420" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H420" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I420" s="1"/>
       <c r="J420" s="1"/>
@@ -13280,10 +13277,10 @@
       <c r="E421" s="2"/>
       <c r="F421" s="2"/>
       <c r="G421" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H421" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I421" s="1"/>
       <c r="J421" s="1"/>
@@ -13310,10 +13307,10 @@
       <c r="E422" s="2"/>
       <c r="F422" s="2"/>
       <c r="G422" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H422" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I422" s="1"/>
       <c r="J422" s="1"/>
@@ -13340,10 +13337,10 @@
       <c r="E423" s="2"/>
       <c r="F423" s="2"/>
       <c r="G423" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I423" s="1"/>
       <c r="J423" s="1"/>
@@ -13370,10 +13367,10 @@
       <c r="E424" s="2"/>
       <c r="F424" s="2"/>
       <c r="G424" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I424" s="1"/>
       <c r="J424" s="1"/>
@@ -13400,10 +13397,10 @@
       <c r="E425" s="1"/>
       <c r="F425" s="1"/>
       <c r="G425" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H425" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I425" s="1"/>
       <c r="J425" s="1"/>
@@ -13430,10 +13427,10 @@
       <c r="E426" s="1"/>
       <c r="F426" s="1"/>
       <c r="G426" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H426" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H426" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I426" s="1"/>
       <c r="J426" s="1"/>
@@ -13460,10 +13457,10 @@
       <c r="E427" s="2"/>
       <c r="F427" s="2"/>
       <c r="G427" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I427" s="1"/>
       <c r="J427" s="1"/>
@@ -13490,10 +13487,10 @@
       <c r="E428" s="2"/>
       <c r="F428" s="2"/>
       <c r="G428" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H428" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H428" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I428" s="1"/>
       <c r="J428" s="1"/>
@@ -13520,10 +13517,10 @@
       <c r="E429" s="2"/>
       <c r="F429" s="2"/>
       <c r="G429" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I429" s="1"/>
       <c r="J429" s="1"/>
@@ -13550,10 +13547,10 @@
       <c r="E430" s="1"/>
       <c r="F430" s="1"/>
       <c r="G430" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I430" s="1"/>
       <c r="J430" s="1"/>
@@ -13580,10 +13577,10 @@
       <c r="E431" s="1"/>
       <c r="F431" s="1"/>
       <c r="G431" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I431" s="1"/>
       <c r="J431" s="1"/>
@@ -13610,10 +13607,10 @@
       <c r="E432" s="2"/>
       <c r="F432" s="2"/>
       <c r="G432" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I432" s="1"/>
       <c r="J432" s="1"/>
@@ -13640,10 +13637,10 @@
       <c r="E433" s="2"/>
       <c r="F433" s="2"/>
       <c r="G433" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I433" s="1"/>
       <c r="J433" s="1"/>
@@ -13670,10 +13667,10 @@
       <c r="E434" s="2"/>
       <c r="F434" s="2"/>
       <c r="G434" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I434" s="1"/>
       <c r="J434" s="1"/>
@@ -13700,10 +13697,10 @@
       <c r="E435" s="1"/>
       <c r="F435" s="1"/>
       <c r="G435" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H435" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I435" s="1"/>
       <c r="J435" s="1"/>
@@ -13730,10 +13727,10 @@
       <c r="E436" s="1"/>
       <c r="F436" s="1"/>
       <c r="G436" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H436" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I436" s="1"/>
       <c r="J436" s="1"/>
@@ -13760,7 +13757,7 @@
       <c r="E437" s="2"/>
       <c r="F437" s="2"/>
       <c r="G437" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H437" s="1"/>
       <c r="I437" s="1"/>
@@ -13788,7 +13785,7 @@
       <c r="E438" s="2"/>
       <c r="F438" s="2"/>
       <c r="G438" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H438" s="1"/>
       <c r="I438" s="1"/>
@@ -13816,7 +13813,7 @@
       <c r="E439" s="2"/>
       <c r="F439" s="2"/>
       <c r="G439" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H439" s="1"/>
       <c r="I439" s="1"/>
@@ -13844,7 +13841,7 @@
       <c r="E440" s="2"/>
       <c r="F440" s="2"/>
       <c r="G440" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H440" s="1"/>
       <c r="I440" s="1"/>
@@ -13872,7 +13869,7 @@
       <c r="E441" s="2"/>
       <c r="F441" s="2"/>
       <c r="G441" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H441" s="1"/>
       <c r="I441" s="1"/>
@@ -13900,7 +13897,7 @@
       <c r="E442" s="2"/>
       <c r="F442" s="2"/>
       <c r="G442" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H442" s="1"/>
       <c r="I442" s="1"/>
@@ -13928,7 +13925,7 @@
       <c r="E443" s="2"/>
       <c r="F443" s="2"/>
       <c r="G443" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H443" s="1"/>
       <c r="I443" s="1"/>
@@ -13956,7 +13953,7 @@
       <c r="E444" s="2"/>
       <c r="F444" s="2"/>
       <c r="G444" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H444" s="1"/>
       <c r="I444" s="1"/>
@@ -13984,7 +13981,7 @@
       <c r="E445" s="2"/>
       <c r="F445" s="2"/>
       <c r="G445" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H445" s="1"/>
       <c r="I445" s="1"/>
@@ -14012,7 +14009,7 @@
       <c r="E446" s="2"/>
       <c r="F446" s="2"/>
       <c r="G446" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H446" s="1"/>
       <c r="I446" s="1"/>
@@ -14040,7 +14037,7 @@
       <c r="E447" s="2"/>
       <c r="F447" s="2"/>
       <c r="G447" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H447" s="1"/>
       <c r="I447" s="1"/>
@@ -14068,10 +14065,10 @@
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H448" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I448" s="1"/>
       <c r="J448" s="1"/>
@@ -14098,10 +14095,10 @@
       <c r="E449" s="2"/>
       <c r="F449" s="2"/>
       <c r="G449" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I449" s="1"/>
       <c r="J449" s="1"/>
@@ -14128,10 +14125,10 @@
       <c r="E450" s="2"/>
       <c r="F450" s="2"/>
       <c r="G450" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I450" s="1"/>
       <c r="J450" s="1"/>
@@ -14158,10 +14155,10 @@
       <c r="E451" s="2"/>
       <c r="F451" s="2"/>
       <c r="G451" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I451" s="1"/>
       <c r="J451" s="1"/>
@@ -14188,10 +14185,10 @@
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H452" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I452" s="1"/>
       <c r="J452" s="1"/>
@@ -14218,10 +14215,10 @@
       <c r="E453" s="2"/>
       <c r="F453" s="2"/>
       <c r="G453" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H453" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I453" s="1"/>
       <c r="J453" s="1"/>
@@ -14248,10 +14245,10 @@
       <c r="E454" s="1"/>
       <c r="F454" s="1"/>
       <c r="G454" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I454" s="1"/>
       <c r="J454" s="1"/>
@@ -14278,10 +14275,10 @@
       <c r="E455" s="1"/>
       <c r="F455" s="1"/>
       <c r="G455" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H455" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H455" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I455" s="1"/>
       <c r="J455" s="1"/>
@@ -14308,10 +14305,10 @@
       <c r="E456" s="2"/>
       <c r="F456" s="2"/>
       <c r="G456" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H456" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I456" s="1"/>
       <c r="J456" s="1"/>
@@ -14338,10 +14335,10 @@
       <c r="E457" s="2"/>
       <c r="F457" s="2"/>
       <c r="G457" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H457" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H457" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I457" s="1"/>
       <c r="J457" s="1"/>
@@ -14368,10 +14365,10 @@
       <c r="E458" s="2"/>
       <c r="F458" s="2"/>
       <c r="G458" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I458" s="1"/>
       <c r="J458" s="1"/>
@@ -14398,10 +14395,10 @@
       <c r="E459" s="1"/>
       <c r="F459" s="1"/>
       <c r="G459" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I459" s="1"/>
       <c r="J459" s="1"/>
@@ -14428,10 +14425,10 @@
       <c r="E460" s="1"/>
       <c r="F460" s="1"/>
       <c r="G460" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H460" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I460" s="1"/>
       <c r="J460" s="1"/>
@@ -14458,10 +14455,10 @@
       <c r="E461" s="2"/>
       <c r="F461" s="2"/>
       <c r="G461" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I461" s="1"/>
       <c r="J461" s="1"/>
@@ -14488,10 +14485,10 @@
       <c r="E462" s="2"/>
       <c r="F462" s="2"/>
       <c r="G462" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H462" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I462" s="1"/>
       <c r="J462" s="1"/>
@@ -14518,10 +14515,10 @@
       <c r="E463" s="2"/>
       <c r="F463" s="2"/>
       <c r="G463" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H463" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I463" s="1"/>
       <c r="J463" s="1"/>
@@ -14548,10 +14545,10 @@
       <c r="E464" s="1"/>
       <c r="F464" s="1"/>
       <c r="G464" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H464" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I464" s="1"/>
       <c r="J464" s="1"/>
@@ -14578,10 +14575,10 @@
       <c r="E465" s="1"/>
       <c r="F465" s="1"/>
       <c r="G465" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H465" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I465" s="1"/>
       <c r="J465" s="1"/>
@@ -14608,7 +14605,7 @@
       <c r="E466" s="2"/>
       <c r="F466" s="2"/>
       <c r="G466" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H466" s="1"/>
       <c r="I466" s="1"/>
@@ -14636,7 +14633,7 @@
       <c r="E467" s="2"/>
       <c r="F467" s="2"/>
       <c r="G467" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H467" s="1"/>
       <c r="I467" s="1"/>
@@ -14664,7 +14661,7 @@
       <c r="E468" s="2"/>
       <c r="F468" s="2"/>
       <c r="G468" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H468" s="1"/>
       <c r="I468" s="1"/>
@@ -14692,7 +14689,7 @@
       <c r="E469" s="2"/>
       <c r="F469" s="2"/>
       <c r="G469" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H469" s="1"/>
       <c r="I469" s="1"/>
@@ -14720,7 +14717,7 @@
       <c r="E470" s="2"/>
       <c r="F470" s="2"/>
       <c r="G470" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H470" s="1"/>
       <c r="I470" s="1"/>
@@ -14748,7 +14745,7 @@
       <c r="E471" s="2"/>
       <c r="F471" s="2"/>
       <c r="G471" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H471" s="1"/>
       <c r="I471" s="1"/>
@@ -14776,7 +14773,7 @@
       <c r="E472" s="2"/>
       <c r="F472" s="2"/>
       <c r="G472" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H472" s="1"/>
       <c r="I472" s="1"/>
@@ -14804,7 +14801,7 @@
       <c r="E473" s="2"/>
       <c r="F473" s="2"/>
       <c r="G473" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H473" s="1"/>
       <c r="I473" s="1"/>
@@ -14832,7 +14829,7 @@
       <c r="E474" s="2"/>
       <c r="F474" s="2"/>
       <c r="G474" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H474" s="1"/>
       <c r="I474" s="1"/>
@@ -14860,7 +14857,7 @@
       <c r="E475" s="2"/>
       <c r="F475" s="2"/>
       <c r="G475" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H475" s="1"/>
       <c r="I475" s="1"/>
@@ -14888,7 +14885,7 @@
       <c r="E476" s="2"/>
       <c r="F476" s="2"/>
       <c r="G476" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H476" s="1"/>
       <c r="I476" s="1"/>
@@ -14916,10 +14913,10 @@
       <c r="E477" s="3"/>
       <c r="F477" s="3"/>
       <c r="G477" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H477" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I477" s="1"/>
       <c r="J477" s="1"/>
@@ -14946,10 +14943,10 @@
       <c r="E478" s="2"/>
       <c r="F478" s="2"/>
       <c r="G478" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H478" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I478" s="1"/>
       <c r="J478" s="1"/>
@@ -14976,10 +14973,10 @@
       <c r="E479" s="2"/>
       <c r="F479" s="2"/>
       <c r="G479" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H479" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I479" s="1"/>
       <c r="J479" s="1"/>
@@ -15006,10 +15003,10 @@
       <c r="E480" s="2"/>
       <c r="F480" s="2"/>
       <c r="G480" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H480" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I480" s="1"/>
       <c r="J480" s="1"/>
@@ -15036,10 +15033,10 @@
       <c r="E481" s="2"/>
       <c r="F481" s="2"/>
       <c r="G481" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H481" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I481" s="1"/>
       <c r="J481" s="1"/>
@@ -15066,10 +15063,10 @@
       <c r="E482" s="2"/>
       <c r="F482" s="2"/>
       <c r="G482" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H482" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I482" s="1"/>
       <c r="J482" s="1"/>
@@ -15096,10 +15093,10 @@
       <c r="E483" s="1"/>
       <c r="F483" s="1"/>
       <c r="G483" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H483" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I483" s="1"/>
       <c r="J483" s="1"/>
@@ -15126,10 +15123,10 @@
       <c r="E484" s="1"/>
       <c r="F484" s="1"/>
       <c r="G484" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H484" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H484" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I484" s="1"/>
       <c r="J484" s="1"/>
@@ -15156,10 +15153,10 @@
       <c r="E485" s="2"/>
       <c r="F485" s="2"/>
       <c r="G485" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H485" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I485" s="1"/>
       <c r="J485" s="1"/>
@@ -15186,10 +15183,10 @@
       <c r="E486" s="2"/>
       <c r="F486" s="2"/>
       <c r="G486" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H486" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H486" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I486" s="1"/>
       <c r="J486" s="1"/>
@@ -15216,10 +15213,10 @@
       <c r="E487" s="2"/>
       <c r="F487" s="2"/>
       <c r="G487" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H487" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I487" s="1"/>
       <c r="J487" s="1"/>
@@ -15246,10 +15243,10 @@
       <c r="E488" s="1"/>
       <c r="F488" s="1"/>
       <c r="G488" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H488" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I488" s="1"/>
       <c r="J488" s="1"/>
@@ -15276,10 +15273,10 @@
       <c r="E489" s="1"/>
       <c r="F489" s="1"/>
       <c r="G489" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H489" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I489" s="1"/>
       <c r="J489" s="1"/>
@@ -15306,10 +15303,10 @@
       <c r="E490" s="2"/>
       <c r="F490" s="2"/>
       <c r="G490" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H490" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I490" s="1"/>
       <c r="J490" s="1"/>
@@ -15336,10 +15333,10 @@
       <c r="E491" s="2"/>
       <c r="F491" s="2"/>
       <c r="G491" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I491" s="1"/>
       <c r="J491" s="1"/>
@@ -15366,10 +15363,10 @@
       <c r="E492" s="2"/>
       <c r="F492" s="2"/>
       <c r="G492" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I492" s="1"/>
       <c r="J492" s="1"/>
@@ -15396,10 +15393,10 @@
       <c r="E493" s="1"/>
       <c r="F493" s="1"/>
       <c r="G493" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I493" s="1"/>
       <c r="J493" s="1"/>
@@ -15426,10 +15423,10 @@
       <c r="E494" s="1"/>
       <c r="F494" s="1"/>
       <c r="G494" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H494" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I494" s="1"/>
       <c r="J494" s="1"/>
@@ -15456,7 +15453,7 @@
       <c r="E495" s="2"/>
       <c r="F495" s="2"/>
       <c r="G495" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H495" s="1"/>
       <c r="I495" s="1"/>
@@ -15484,7 +15481,7 @@
       <c r="E496" s="2"/>
       <c r="F496" s="2"/>
       <c r="G496" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H496" s="1"/>
       <c r="I496" s="1"/>
@@ -15512,7 +15509,7 @@
       <c r="E497" s="2"/>
       <c r="F497" s="2"/>
       <c r="G497" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H497" s="1"/>
       <c r="I497" s="1"/>
@@ -15540,7 +15537,7 @@
       <c r="E498" s="2"/>
       <c r="F498" s="2"/>
       <c r="G498" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H498" s="1"/>
       <c r="I498" s="1"/>
@@ -15568,7 +15565,7 @@
       <c r="E499" s="2"/>
       <c r="F499" s="2"/>
       <c r="G499" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H499" s="1"/>
       <c r="I499" s="1"/>
@@ -15596,7 +15593,7 @@
       <c r="E500" s="2"/>
       <c r="F500" s="2"/>
       <c r="G500" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H500" s="1"/>
       <c r="I500" s="1"/>
@@ -15624,7 +15621,7 @@
       <c r="E501" s="2"/>
       <c r="F501" s="2"/>
       <c r="G501" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H501" s="1"/>
       <c r="I501" s="1"/>
@@ -15652,7 +15649,7 @@
       <c r="E502" s="2"/>
       <c r="F502" s="2"/>
       <c r="G502" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H502" s="1"/>
       <c r="I502" s="1"/>
@@ -15680,7 +15677,7 @@
       <c r="E503" s="2"/>
       <c r="F503" s="2"/>
       <c r="G503" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H503" s="1"/>
       <c r="I503" s="1"/>
@@ -15708,7 +15705,7 @@
       <c r="E504" s="2"/>
       <c r="F504" s="2"/>
       <c r="G504" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H504" s="1"/>
       <c r="I504" s="1"/>
@@ -15736,7 +15733,7 @@
       <c r="E505" s="2"/>
       <c r="F505" s="2"/>
       <c r="G505" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H505" s="1"/>
       <c r="I505" s="1"/>
@@ -15764,10 +15761,10 @@
       <c r="E506" s="3"/>
       <c r="F506" s="3"/>
       <c r="G506" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H506" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I506" s="1"/>
       <c r="J506" s="1"/>
@@ -15794,10 +15791,10 @@
       <c r="E507" s="2"/>
       <c r="F507" s="2"/>
       <c r="G507" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H507" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I507" s="1"/>
       <c r="J507" s="1"/>
@@ -15824,10 +15821,10 @@
       <c r="E508" s="2"/>
       <c r="F508" s="2"/>
       <c r="G508" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I508" s="1"/>
       <c r="J508" s="1"/>
@@ -15854,10 +15851,10 @@
       <c r="E509" s="2"/>
       <c r="F509" s="2"/>
       <c r="G509" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I509" s="1"/>
       <c r="J509" s="1"/>
@@ -15884,10 +15881,10 @@
       <c r="E510" s="2"/>
       <c r="F510" s="2"/>
       <c r="G510" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H510" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I510" s="1"/>
       <c r="J510" s="1"/>
@@ -15914,10 +15911,10 @@
       <c r="E511" s="2"/>
       <c r="F511" s="2"/>
       <c r="G511" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H511" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I511" s="1"/>
       <c r="J511" s="1"/>
@@ -15944,10 +15941,10 @@
       <c r="E512" s="1"/>
       <c r="F512" s="1"/>
       <c r="G512" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I512" s="1"/>
       <c r="J512" s="1"/>
@@ -15974,10 +15971,10 @@
       <c r="E513" s="1"/>
       <c r="F513" s="1"/>
       <c r="G513" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H513" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H513" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I513" s="1"/>
       <c r="J513" s="1"/>
@@ -16004,10 +16001,10 @@
       <c r="E514" s="2"/>
       <c r="F514" s="2"/>
       <c r="G514" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I514" s="1"/>
       <c r="J514" s="1"/>
@@ -16034,10 +16031,10 @@
       <c r="E515" s="2"/>
       <c r="F515" s="2"/>
       <c r="G515" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H515" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H515" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I515" s="1"/>
       <c r="J515" s="1"/>
@@ -16064,10 +16061,10 @@
       <c r="E516" s="2"/>
       <c r="F516" s="2"/>
       <c r="G516" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I516" s="1"/>
       <c r="J516" s="1"/>
@@ -16094,10 +16091,10 @@
       <c r="E517" s="1"/>
       <c r="F517" s="1"/>
       <c r="G517" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I517" s="1"/>
       <c r="J517" s="1"/>
@@ -16124,10 +16121,10 @@
       <c r="E518" s="1"/>
       <c r="F518" s="1"/>
       <c r="G518" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H518" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I518" s="1"/>
       <c r="J518" s="1"/>
@@ -16154,10 +16151,10 @@
       <c r="E519" s="2"/>
       <c r="F519" s="2"/>
       <c r="G519" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H519" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I519" s="1"/>
       <c r="J519" s="1"/>
@@ -16184,10 +16181,10 @@
       <c r="E520" s="2"/>
       <c r="F520" s="2"/>
       <c r="G520" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I520" s="1"/>
       <c r="J520" s="1"/>
@@ -16214,10 +16211,10 @@
       <c r="E521" s="2"/>
       <c r="F521" s="2"/>
       <c r="G521" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I521" s="1"/>
       <c r="J521" s="1"/>
@@ -16244,10 +16241,10 @@
       <c r="E522" s="1"/>
       <c r="F522" s="1"/>
       <c r="G522" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H522" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I522" s="1"/>
       <c r="J522" s="1"/>
@@ -16274,10 +16271,10 @@
       <c r="E523" s="1"/>
       <c r="F523" s="1"/>
       <c r="G523" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H523" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I523" s="1"/>
       <c r="J523" s="1"/>
@@ -16304,7 +16301,7 @@
       <c r="E524" s="2"/>
       <c r="F524" s="2"/>
       <c r="G524" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H524" s="1"/>
       <c r="I524" s="1"/>
@@ -16332,7 +16329,7 @@
       <c r="E525" s="2"/>
       <c r="F525" s="2"/>
       <c r="G525" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H525" s="1"/>
       <c r="I525" s="1"/>
@@ -16360,7 +16357,7 @@
       <c r="E526" s="2"/>
       <c r="F526" s="2"/>
       <c r="G526" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H526" s="1"/>
       <c r="I526" s="1"/>
@@ -16388,7 +16385,7 @@
       <c r="E527" s="2"/>
       <c r="F527" s="2"/>
       <c r="G527" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H527" s="1"/>
       <c r="I527" s="1"/>
@@ -16416,7 +16413,7 @@
       <c r="E528" s="2"/>
       <c r="F528" s="2"/>
       <c r="G528" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H528" s="1"/>
       <c r="I528" s="1"/>
@@ -16444,7 +16441,7 @@
       <c r="E529" s="2"/>
       <c r="F529" s="2"/>
       <c r="G529" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H529" s="1"/>
       <c r="I529" s="1"/>
@@ -16472,7 +16469,7 @@
       <c r="E530" s="2"/>
       <c r="F530" s="2"/>
       <c r="G530" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H530" s="1"/>
       <c r="I530" s="1"/>
@@ -16500,7 +16497,7 @@
       <c r="E531" s="2"/>
       <c r="F531" s="2"/>
       <c r="G531" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H531" s="1"/>
       <c r="I531" s="1"/>
@@ -16528,7 +16525,7 @@
       <c r="E532" s="2"/>
       <c r="F532" s="2"/>
       <c r="G532" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H532" s="1"/>
       <c r="I532" s="1"/>
@@ -16556,7 +16553,7 @@
       <c r="E533" s="2"/>
       <c r="F533" s="2"/>
       <c r="G533" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H533" s="1"/>
       <c r="I533" s="1"/>
@@ -16584,7 +16581,7 @@
       <c r="E534" s="2"/>
       <c r="F534" s="2"/>
       <c r="G534" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H534" s="1"/>
       <c r="I534" s="1"/>
@@ -16612,10 +16609,10 @@
       <c r="E535" s="3"/>
       <c r="F535" s="3"/>
       <c r="G535" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H535" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I535" s="1"/>
       <c r="J535" s="1"/>
@@ -16642,10 +16639,10 @@
       <c r="E536" s="2"/>
       <c r="F536" s="2"/>
       <c r="G536" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H536" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I536" s="1"/>
       <c r="J536" s="1"/>
@@ -16672,10 +16669,10 @@
       <c r="E537" s="2"/>
       <c r="F537" s="2"/>
       <c r="G537" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H537" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I537" s="1"/>
       <c r="J537" s="1"/>
@@ -16702,10 +16699,10 @@
       <c r="E538" s="2"/>
       <c r="F538" s="2"/>
       <c r="G538" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H538" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I538" s="1"/>
       <c r="J538" s="1"/>
@@ -16732,10 +16729,10 @@
       <c r="E539" s="2"/>
       <c r="F539" s="2"/>
       <c r="G539" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H539" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I539" s="1"/>
       <c r="J539" s="1"/>
@@ -16762,10 +16759,10 @@
       <c r="E540" s="2"/>
       <c r="F540" s="2"/>
       <c r="G540" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H540" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I540" s="1"/>
       <c r="J540" s="1"/>
@@ -16792,10 +16789,10 @@
       <c r="E541" s="1"/>
       <c r="F541" s="1"/>
       <c r="G541" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H541" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I541" s="1"/>
       <c r="J541" s="1"/>
@@ -16822,10 +16819,10 @@
       <c r="E542" s="1"/>
       <c r="F542" s="1"/>
       <c r="G542" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H542" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H542" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I542" s="1"/>
       <c r="J542" s="1"/>
@@ -16852,10 +16849,10 @@
       <c r="E543" s="2"/>
       <c r="F543" s="2"/>
       <c r="G543" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H543" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I543" s="1"/>
       <c r="J543" s="1"/>
@@ -16882,10 +16879,10 @@
       <c r="E544" s="2"/>
       <c r="F544" s="2"/>
       <c r="G544" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H544" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H544" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I544" s="1"/>
       <c r="J544" s="1"/>
@@ -16912,10 +16909,10 @@
       <c r="E545" s="2"/>
       <c r="F545" s="2"/>
       <c r="G545" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H545" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I545" s="1"/>
       <c r="J545" s="1"/>
@@ -16942,10 +16939,10 @@
       <c r="E546" s="1"/>
       <c r="F546" s="1"/>
       <c r="G546" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H546" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I546" s="1"/>
       <c r="J546" s="1"/>
@@ -16972,10 +16969,10 @@
       <c r="E547" s="1"/>
       <c r="F547" s="1"/>
       <c r="G547" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H547" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I547" s="1"/>
       <c r="J547" s="1"/>
@@ -17002,10 +16999,10 @@
       <c r="E548" s="2"/>
       <c r="F548" s="2"/>
       <c r="G548" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H548" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I548" s="1"/>
       <c r="J548" s="1"/>
@@ -17032,10 +17029,10 @@
       <c r="E549" s="2"/>
       <c r="F549" s="2"/>
       <c r="G549" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H549" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I549" s="1"/>
       <c r="J549" s="1"/>
@@ -17062,10 +17059,10 @@
       <c r="E550" s="2"/>
       <c r="F550" s="2"/>
       <c r="G550" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H550" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I550" s="1"/>
       <c r="J550" s="1"/>
@@ -17092,10 +17089,10 @@
       <c r="E551" s="1"/>
       <c r="F551" s="1"/>
       <c r="G551" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H551" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I551" s="1"/>
       <c r="J551" s="1"/>
@@ -17122,10 +17119,10 @@
       <c r="E552" s="1"/>
       <c r="F552" s="1"/>
       <c r="G552" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H552" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I552" s="1"/>
       <c r="J552" s="1"/>
@@ -17152,7 +17149,7 @@
       <c r="E553" s="2"/>
       <c r="F553" s="2"/>
       <c r="G553" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H553" s="1"/>
       <c r="I553" s="1"/>
@@ -17180,7 +17177,7 @@
       <c r="E554" s="2"/>
       <c r="F554" s="2"/>
       <c r="G554" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H554" s="1"/>
       <c r="I554" s="1"/>
@@ -17208,7 +17205,7 @@
       <c r="E555" s="2"/>
       <c r="F555" s="2"/>
       <c r="G555" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H555" s="1"/>
       <c r="I555" s="1"/>
@@ -17236,7 +17233,7 @@
       <c r="E556" s="2"/>
       <c r="F556" s="2"/>
       <c r="G556" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H556" s="1"/>
       <c r="I556" s="1"/>
@@ -17264,7 +17261,7 @@
       <c r="E557" s="2"/>
       <c r="F557" s="2"/>
       <c r="G557" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H557" s="1"/>
       <c r="I557" s="1"/>
@@ -17292,7 +17289,7 @@
       <c r="E558" s="2"/>
       <c r="F558" s="2"/>
       <c r="G558" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H558" s="1"/>
       <c r="I558" s="1"/>
@@ -17320,7 +17317,7 @@
       <c r="E559" s="2"/>
       <c r="F559" s="2"/>
       <c r="G559" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H559" s="1"/>
       <c r="I559" s="1"/>
@@ -17348,7 +17345,7 @@
       <c r="E560" s="2"/>
       <c r="F560" s="2"/>
       <c r="G560" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H560" s="1"/>
       <c r="I560" s="1"/>
@@ -17376,7 +17373,7 @@
       <c r="E561" s="2"/>
       <c r="F561" s="2"/>
       <c r="G561" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H561" s="1"/>
       <c r="I561" s="1"/>
@@ -17404,7 +17401,7 @@
       <c r="E562" s="2"/>
       <c r="F562" s="2"/>
       <c r="G562" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H562" s="1"/>
       <c r="I562" s="1"/>
@@ -17432,7 +17429,7 @@
       <c r="E563" s="2"/>
       <c r="F563" s="2"/>
       <c r="G563" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H563" s="1"/>
       <c r="I563" s="1"/>
@@ -17460,10 +17457,10 @@
       <c r="E564" s="3"/>
       <c r="F564" s="3"/>
       <c r="G564" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H564" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I564" s="1"/>
       <c r="J564" s="1"/>
@@ -17490,10 +17487,10 @@
       <c r="E565" s="2"/>
       <c r="F565" s="2"/>
       <c r="G565" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H565" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I565" s="1"/>
       <c r="J565" s="1"/>
@@ -17520,10 +17517,10 @@
       <c r="E566" s="2"/>
       <c r="F566" s="2"/>
       <c r="G566" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H566" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I566" s="1"/>
       <c r="J566" s="1"/>
@@ -17550,10 +17547,10 @@
       <c r="E567" s="2"/>
       <c r="F567" s="2"/>
       <c r="G567" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H567" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I567" s="1"/>
       <c r="J567" s="1"/>
@@ -17580,10 +17577,10 @@
       <c r="E568" s="2"/>
       <c r="F568" s="2"/>
       <c r="G568" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H568" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I568" s="1"/>
       <c r="J568" s="1"/>
@@ -17610,10 +17607,10 @@
       <c r="E569" s="2"/>
       <c r="F569" s="2"/>
       <c r="G569" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H569" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I569" s="1"/>
       <c r="J569" s="1"/>
@@ -17640,10 +17637,10 @@
       <c r="E570" s="1"/>
       <c r="F570" s="1"/>
       <c r="G570" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H570" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I570" s="1"/>
       <c r="J570" s="1"/>
@@ -17670,10 +17667,10 @@
       <c r="E571" s="1"/>
       <c r="F571" s="1"/>
       <c r="G571" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H571" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H571" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I571" s="1"/>
       <c r="J571" s="1"/>
@@ -17700,10 +17697,10 @@
       <c r="E572" s="2"/>
       <c r="F572" s="2"/>
       <c r="G572" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H572" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I572" s="1"/>
       <c r="J572" s="1"/>
@@ -17730,10 +17727,10 @@
       <c r="E573" s="2"/>
       <c r="F573" s="2"/>
       <c r="G573" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H573" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H573" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I573" s="1"/>
       <c r="J573" s="1"/>
@@ -17760,10 +17757,10 @@
       <c r="E574" s="2"/>
       <c r="F574" s="2"/>
       <c r="G574" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I574" s="1"/>
       <c r="J574" s="1"/>
@@ -17790,10 +17787,10 @@
       <c r="E575" s="1"/>
       <c r="F575" s="1"/>
       <c r="G575" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H575" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I575" s="1"/>
       <c r="J575" s="1"/>
@@ -17820,10 +17817,10 @@
       <c r="E576" s="1"/>
       <c r="F576" s="1"/>
       <c r="G576" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H576" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I576" s="1"/>
       <c r="J576" s="1"/>
@@ -17850,10 +17847,10 @@
       <c r="E577" s="2"/>
       <c r="F577" s="2"/>
       <c r="G577" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H577" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I577" s="1"/>
       <c r="J577" s="1"/>
@@ -17880,10 +17877,10 @@
       <c r="E578" s="2"/>
       <c r="F578" s="2"/>
       <c r="G578" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H578" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I578" s="1"/>
       <c r="J578" s="1"/>
@@ -17910,10 +17907,10 @@
       <c r="E579" s="2"/>
       <c r="F579" s="2"/>
       <c r="G579" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H579" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I579" s="1"/>
       <c r="J579" s="1"/>
@@ -17940,10 +17937,10 @@
       <c r="E580" s="1"/>
       <c r="F580" s="1"/>
       <c r="G580" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H580" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I580" s="1"/>
       <c r="J580" s="1"/>
@@ -17970,10 +17967,10 @@
       <c r="E581" s="1"/>
       <c r="F581" s="1"/>
       <c r="G581" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H581" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I581" s="1"/>
       <c r="J581" s="1"/>
@@ -18000,7 +17997,7 @@
       <c r="E582" s="2"/>
       <c r="F582" s="2"/>
       <c r="G582" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H582" s="1"/>
       <c r="I582" s="1"/>
@@ -18028,7 +18025,7 @@
       <c r="E583" s="2"/>
       <c r="F583" s="2"/>
       <c r="G583" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H583" s="1"/>
       <c r="I583" s="1"/>
@@ -18056,7 +18053,7 @@
       <c r="E584" s="2"/>
       <c r="F584" s="2"/>
       <c r="G584" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H584" s="1"/>
       <c r="I584" s="1"/>
@@ -18084,7 +18081,7 @@
       <c r="E585" s="2"/>
       <c r="F585" s="2"/>
       <c r="G585" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H585" s="1"/>
       <c r="I585" s="1"/>
@@ -18112,7 +18109,7 @@
       <c r="E586" s="2"/>
       <c r="F586" s="2"/>
       <c r="G586" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H586" s="1"/>
       <c r="I586" s="1"/>
@@ -18140,7 +18137,7 @@
       <c r="E587" s="2"/>
       <c r="F587" s="2"/>
       <c r="G587" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H587" s="1"/>
       <c r="I587" s="1"/>
@@ -18168,7 +18165,7 @@
       <c r="E588" s="2"/>
       <c r="F588" s="2"/>
       <c r="G588" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H588" s="1"/>
       <c r="I588" s="1"/>
@@ -18196,7 +18193,7 @@
       <c r="E589" s="2"/>
       <c r="F589" s="2"/>
       <c r="G589" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H589" s="1"/>
       <c r="I589" s="1"/>
@@ -18224,7 +18221,7 @@
       <c r="E590" s="2"/>
       <c r="F590" s="2"/>
       <c r="G590" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H590" s="1"/>
       <c r="I590" s="1"/>
@@ -18252,7 +18249,7 @@
       <c r="E591" s="2"/>
       <c r="F591" s="2"/>
       <c r="G591" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H591" s="1"/>
       <c r="I591" s="1"/>
@@ -18280,7 +18277,7 @@
       <c r="E592" s="2"/>
       <c r="F592" s="2"/>
       <c r="G592" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H592" s="1"/>
       <c r="I592" s="1"/>

--- a/awim/cal template.xlsx
+++ b/awim/cal template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/640dce341da437cb/02 Time v3 physical Clock/Time v3 Clock camera and image processing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:40009_{B2970093-D86E-46D6-A84B-1B4BF93138CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5DD7ABE-2E57-4D41-A0A0-19FD6686EC2E}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:40009_{B2970093-D86E-46D6-A84B-1B4BF93138CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2490F905-18C3-4BE1-9684-29AC6544A8B9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,12 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="46">
   <si>
-    <t>rec_x</t>
-  </si>
-  <si>
-    <t>rec_y</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -38,12 +32,6 @@
   </si>
   <si>
     <t>out2</t>
-  </si>
-  <si>
-    <t>px_x</t>
-  </si>
-  <si>
-    <t>px_y</t>
   </si>
   <si>
     <t>camera_name</t>
@@ -133,31 +121,43 @@
     <t>rotation_error_h_and_px_delta</t>
   </si>
   <si>
-    <t>xsph_sect</t>
+    <t>x_px</t>
   </si>
   <si>
-    <t>ysph_sect</t>
+    <t>y_px</t>
   </si>
   <si>
-    <t>xsph_rel</t>
+    <t>xang_sect</t>
   </si>
   <si>
-    <t>target_pos_xysph_relaim</t>
+    <t>yang_sect</t>
   </si>
   <si>
-    <t>ysph_rel</t>
+    <t>xang_rel</t>
   </si>
   <si>
-    <t>xsph_total</t>
+    <t>yang_rel</t>
   </si>
   <si>
-    <t>ysph_total</t>
+    <t>x_rec</t>
   </si>
   <si>
-    <t>xsph</t>
+    <t>xang_total</t>
   </si>
   <si>
-    <t>ysph</t>
+    <t>yang_total</t>
+  </si>
+  <si>
+    <t>xang</t>
+  </si>
+  <si>
+    <t>yang</t>
+  </si>
+  <si>
+    <t>target_pos_xyangs_relaim</t>
+  </si>
+  <si>
+    <t>y_rec</t>
   </si>
 </sst>
 </file>
@@ -1033,66 +1033,64 @@
   <dimension ref="A1:P592"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.88671875" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -1103,7 +1101,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="1"/>
@@ -1123,7 +1121,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="1"/>
@@ -1143,7 +1141,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="1"/>
@@ -1163,7 +1161,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
@@ -1183,7 +1181,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="1"/>
@@ -1203,7 +1201,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="1"/>
@@ -1223,7 +1221,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
@@ -1243,7 +1241,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
@@ -1263,7 +1261,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="1"/>
@@ -1283,7 +1281,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
@@ -1315,10 +1313,10 @@
         <v>-1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1345,10 +1343,10 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1375,10 +1373,10 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1405,10 +1403,10 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1435,10 +1433,10 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1465,10 +1463,10 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1495,10 +1493,10 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1525,10 +1523,10 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1555,10 +1553,10 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1585,10 +1583,10 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1615,10 +1613,10 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1645,10 +1643,10 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1675,10 +1673,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1705,10 +1703,10 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1735,10 +1733,10 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -1765,10 +1763,10 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1795,10 +1793,10 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -1825,10 +1823,10 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1855,10 +1853,10 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -1885,7 +1883,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1913,7 +1911,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1941,7 +1939,7 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1969,7 +1967,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1997,7 +1995,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2025,7 +2023,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2053,7 +2051,7 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2081,7 +2079,7 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -2109,7 +2107,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -2137,7 +2135,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2165,7 +2163,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -2193,10 +2191,10 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -2223,10 +2221,10 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -2253,10 +2251,10 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -2283,10 +2281,10 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -2313,10 +2311,10 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -2343,10 +2341,10 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -2373,10 +2371,10 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -2403,10 +2401,10 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -2433,10 +2431,10 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -2463,10 +2461,10 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -2493,10 +2491,10 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -2523,10 +2521,10 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -2553,10 +2551,10 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -2583,10 +2581,10 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -2613,10 +2611,10 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -2643,10 +2641,10 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -2673,10 +2671,10 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -2703,10 +2701,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -2733,7 +2731,7 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -2761,7 +2759,7 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -2789,7 +2787,7 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -2817,7 +2815,7 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -2845,7 +2843,7 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -2873,7 +2871,7 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -2901,7 +2899,7 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -2929,7 +2927,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -2957,7 +2955,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -2985,7 +2983,7 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -3013,7 +3011,7 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -3041,10 +3039,10 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -3071,10 +3069,10 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -3101,10 +3099,10 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -3131,10 +3129,10 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -3161,10 +3159,10 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -3191,10 +3189,10 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -3221,10 +3219,10 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -3251,10 +3249,10 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -3281,10 +3279,10 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -3311,10 +3309,10 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -3341,10 +3339,10 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -3371,10 +3369,10 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -3401,10 +3399,10 @@
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -3431,10 +3429,10 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -3461,10 +3459,10 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -3491,10 +3489,10 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -3521,10 +3519,10 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -3551,10 +3549,10 @@
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -3581,7 +3579,7 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -3609,7 +3607,7 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -3637,7 +3635,7 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -3665,7 +3663,7 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -3693,7 +3691,7 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -3721,7 +3719,7 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -3749,7 +3747,7 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -3777,7 +3775,7 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
@@ -3805,7 +3803,7 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
@@ -3833,7 +3831,7 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -3861,7 +3859,7 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
@@ -3889,10 +3887,10 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -3919,10 +3917,10 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -3949,10 +3947,10 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -3979,10 +3977,10 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -4009,10 +4007,10 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H104" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -4039,10 +4037,10 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -4069,10 +4067,10 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -4099,10 +4097,10 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -4129,10 +4127,10 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -4159,10 +4157,10 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -4189,10 +4187,10 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -4219,10 +4217,10 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -4249,10 +4247,10 @@
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -4279,10 +4277,10 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -4309,10 +4307,10 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -4339,10 +4337,10 @@
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -4369,10 +4367,10 @@
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -4399,10 +4397,10 @@
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -4429,7 +4427,7 @@
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -4457,7 +4455,7 @@
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -4485,7 +4483,7 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
@@ -4513,7 +4511,7 @@
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
@@ -4541,7 +4539,7 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
@@ -4569,7 +4567,7 @@
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
@@ -4597,7 +4595,7 @@
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
@@ -4625,7 +4623,7 @@
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
@@ -4653,7 +4651,7 @@
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
@@ -4681,7 +4679,7 @@
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -4709,7 +4707,7 @@
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
@@ -4737,10 +4735,10 @@
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
@@ -4767,10 +4765,10 @@
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
@@ -4797,10 +4795,10 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -4827,10 +4825,10 @@
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -4857,10 +4855,10 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -4887,10 +4885,10 @@
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
@@ -4917,10 +4915,10 @@
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -4947,10 +4945,10 @@
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
@@ -4977,10 +4975,10 @@
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -5007,10 +5005,10 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -5037,10 +5035,10 @@
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -5067,10 +5065,10 @@
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -5097,10 +5095,10 @@
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
@@ -5127,10 +5125,10 @@
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -5157,10 +5155,10 @@
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
@@ -5187,10 +5185,10 @@
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
@@ -5217,10 +5215,10 @@
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
@@ -5247,10 +5245,10 @@
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -5277,7 +5275,7 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
@@ -5305,7 +5303,7 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
@@ -5333,7 +5331,7 @@
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
@@ -5361,7 +5359,7 @@
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
@@ -5389,7 +5387,7 @@
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
@@ -5417,7 +5415,7 @@
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
@@ -5445,7 +5443,7 @@
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
@@ -5473,7 +5471,7 @@
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
@@ -5501,7 +5499,7 @@
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
@@ -5529,7 +5527,7 @@
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
@@ -5557,7 +5555,7 @@
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
@@ -5585,10 +5583,10 @@
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
@@ -5615,10 +5613,10 @@
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
@@ -5645,10 +5643,10 @@
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
@@ -5675,10 +5673,10 @@
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
@@ -5705,10 +5703,10 @@
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H162" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
@@ -5735,10 +5733,10 @@
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
@@ -5765,10 +5763,10 @@
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -5795,10 +5793,10 @@
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
@@ -5825,10 +5823,10 @@
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
@@ -5855,10 +5853,10 @@
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
@@ -5885,10 +5883,10 @@
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
@@ -5915,10 +5913,10 @@
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
@@ -5945,10 +5943,10 @@
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
@@ -5975,10 +5973,10 @@
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
@@ -6005,10 +6003,10 @@
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
@@ -6035,10 +6033,10 @@
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
@@ -6065,10 +6063,10 @@
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
@@ -6095,10 +6093,10 @@
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
       <c r="G175" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
@@ -6125,7 +6123,7 @@
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
@@ -6153,7 +6151,7 @@
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
@@ -6181,7 +6179,7 @@
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
@@ -6209,7 +6207,7 @@
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
@@ -6237,7 +6235,7 @@
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
@@ -6265,7 +6263,7 @@
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
@@ -6293,7 +6291,7 @@
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
@@ -6321,7 +6319,7 @@
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
@@ -6349,7 +6347,7 @@
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
@@ -6377,7 +6375,7 @@
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
@@ -6405,7 +6403,7 @@
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
@@ -6433,10 +6431,10 @@
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I187" s="1"/>
       <c r="J187" s="1"/>
@@ -6463,10 +6461,10 @@
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
@@ -6493,10 +6491,10 @@
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
@@ -6523,10 +6521,10 @@
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
@@ -6553,10 +6551,10 @@
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H191" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H191" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I191" s="1"/>
       <c r="J191" s="1"/>
@@ -6583,10 +6581,10 @@
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I192" s="1"/>
       <c r="J192" s="1"/>
@@ -6613,10 +6611,10 @@
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I193" s="1"/>
       <c r="J193" s="1"/>
@@ -6643,10 +6641,10 @@
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I194" s="1"/>
       <c r="J194" s="1"/>
@@ -6673,10 +6671,10 @@
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I195" s="1"/>
       <c r="J195" s="1"/>
@@ -6703,10 +6701,10 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I196" s="1"/>
       <c r="J196" s="1"/>
@@ -6733,10 +6731,10 @@
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I197" s="1"/>
       <c r="J197" s="1"/>
@@ -6763,10 +6761,10 @@
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I198" s="1"/>
       <c r="J198" s="1"/>
@@ -6793,10 +6791,10 @@
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I199" s="1"/>
       <c r="J199" s="1"/>
@@ -6823,10 +6821,10 @@
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I200" s="1"/>
       <c r="J200" s="1"/>
@@ -6853,10 +6851,10 @@
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I201" s="1"/>
       <c r="J201" s="1"/>
@@ -6883,10 +6881,10 @@
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I202" s="1"/>
       <c r="J202" s="1"/>
@@ -6913,10 +6911,10 @@
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I203" s="1"/>
       <c r="J203" s="1"/>
@@ -6943,10 +6941,10 @@
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I204" s="1"/>
       <c r="J204" s="1"/>
@@ -6973,7 +6971,7 @@
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
       <c r="G205" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H205" s="1"/>
       <c r="I205" s="1"/>
@@ -7001,7 +6999,7 @@
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
       <c r="G206" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
@@ -7029,7 +7027,7 @@
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
       <c r="G207" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H207" s="1"/>
       <c r="I207" s="1"/>
@@ -7057,7 +7055,7 @@
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
       <c r="G208" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H208" s="1"/>
       <c r="I208" s="1"/>
@@ -7085,7 +7083,7 @@
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
       <c r="G209" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H209" s="1"/>
       <c r="I209" s="1"/>
@@ -7113,7 +7111,7 @@
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
       <c r="G210" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H210" s="1"/>
       <c r="I210" s="1"/>
@@ -7141,7 +7139,7 @@
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
       <c r="G211" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H211" s="1"/>
       <c r="I211" s="1"/>
@@ -7169,7 +7167,7 @@
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
       <c r="G212" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
@@ -7197,7 +7195,7 @@
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
       <c r="G213" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H213" s="1"/>
       <c r="I213" s="1"/>
@@ -7225,7 +7223,7 @@
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
       <c r="G214" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H214" s="1"/>
       <c r="I214" s="1"/>
@@ -7253,7 +7251,7 @@
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
       <c r="G215" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H215" s="1"/>
       <c r="I215" s="1"/>
@@ -7281,10 +7279,10 @@
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I216" s="1"/>
       <c r="J216" s="1"/>
@@ -7311,10 +7309,10 @@
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
       <c r="G217" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I217" s="1"/>
       <c r="J217" s="1"/>
@@ -7341,10 +7339,10 @@
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
       <c r="G218" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I218" s="1"/>
       <c r="J218" s="1"/>
@@ -7371,10 +7369,10 @@
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
       <c r="G219" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I219" s="1"/>
       <c r="J219" s="1"/>
@@ -7401,10 +7399,10 @@
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
       <c r="G220" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H220" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H220" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I220" s="1"/>
       <c r="J220" s="1"/>
@@ -7431,10 +7429,10 @@
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
       <c r="G221" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I221" s="1"/>
       <c r="J221" s="1"/>
@@ -7461,10 +7459,10 @@
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I222" s="1"/>
       <c r="J222" s="1"/>
@@ -7491,10 +7489,10 @@
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I223" s="1"/>
       <c r="J223" s="1"/>
@@ -7521,10 +7519,10 @@
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I224" s="1"/>
       <c r="J224" s="1"/>
@@ -7551,10 +7549,10 @@
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I225" s="1"/>
       <c r="J225" s="1"/>
@@ -7581,10 +7579,10 @@
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
       <c r="G226" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I226" s="1"/>
       <c r="J226" s="1"/>
@@ -7611,10 +7609,10 @@
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I227" s="1"/>
       <c r="J227" s="1"/>
@@ -7641,10 +7639,10 @@
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I228" s="1"/>
       <c r="J228" s="1"/>
@@ -7671,10 +7669,10 @@
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I229" s="1"/>
       <c r="J229" s="1"/>
@@ -7701,10 +7699,10 @@
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I230" s="1"/>
       <c r="J230" s="1"/>
@@ -7731,10 +7729,10 @@
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
       <c r="G231" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I231" s="1"/>
       <c r="J231" s="1"/>
@@ -7761,10 +7759,10 @@
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I232" s="1"/>
       <c r="J232" s="1"/>
@@ -7791,10 +7789,10 @@
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I233" s="1"/>
       <c r="J233" s="1"/>
@@ -7821,7 +7819,7 @@
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
       <c r="G234" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
@@ -7849,7 +7847,7 @@
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
@@ -7877,7 +7875,7 @@
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
@@ -7905,7 +7903,7 @@
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
       <c r="G237" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
@@ -7933,7 +7931,7 @@
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
       <c r="G238" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H238" s="1"/>
       <c r="I238" s="1"/>
@@ -7961,7 +7959,7 @@
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
@@ -7989,7 +7987,7 @@
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
@@ -8017,7 +8015,7 @@
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
       <c r="G241" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
@@ -8045,7 +8043,7 @@
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
@@ -8073,7 +8071,7 @@
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
@@ -8101,7 +8099,7 @@
       <c r="E244" s="2"/>
       <c r="F244" s="2"/>
       <c r="G244" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
@@ -8129,10 +8127,10 @@
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I245" s="1"/>
       <c r="J245" s="1"/>
@@ -8159,10 +8157,10 @@
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I246" s="1"/>
       <c r="J246" s="1"/>
@@ -8189,10 +8187,10 @@
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I247" s="1"/>
       <c r="J247" s="1"/>
@@ -8219,10 +8217,10 @@
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I248" s="1"/>
       <c r="J248" s="1"/>
@@ -8249,10 +8247,10 @@
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
       <c r="G249" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H249" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H249" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I249" s="1"/>
       <c r="J249" s="1"/>
@@ -8279,10 +8277,10 @@
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
       <c r="G250" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
@@ -8309,10 +8307,10 @@
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I251" s="1"/>
       <c r="J251" s="1"/>
@@ -8339,10 +8337,10 @@
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I252" s="1"/>
       <c r="J252" s="1"/>
@@ -8369,10 +8367,10 @@
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
       <c r="G253" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I253" s="1"/>
       <c r="J253" s="1"/>
@@ -8399,10 +8397,10 @@
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
       <c r="G254" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
@@ -8429,10 +8427,10 @@
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
       <c r="G255" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I255" s="1"/>
       <c r="J255" s="1"/>
@@ -8459,10 +8457,10 @@
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I256" s="1"/>
       <c r="J256" s="1"/>
@@ -8489,10 +8487,10 @@
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I257" s="1"/>
       <c r="J257" s="1"/>
@@ -8519,10 +8517,10 @@
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
       <c r="G258" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
@@ -8549,10 +8547,10 @@
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
       <c r="G259" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I259" s="1"/>
       <c r="J259" s="1"/>
@@ -8579,10 +8577,10 @@
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
       <c r="G260" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
@@ -8609,10 +8607,10 @@
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
@@ -8639,10 +8637,10 @@
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
@@ -8669,7 +8667,7 @@
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
       <c r="G263" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
@@ -8697,7 +8695,7 @@
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
       <c r="G264" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
@@ -8725,7 +8723,7 @@
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
@@ -8753,7 +8751,7 @@
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
       <c r="G266" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
@@ -8781,7 +8779,7 @@
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
       <c r="G267" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H267" s="1"/>
       <c r="I267" s="1"/>
@@ -8809,7 +8807,7 @@
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
       <c r="G268" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H268" s="1"/>
       <c r="I268" s="1"/>
@@ -8837,7 +8835,7 @@
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
       <c r="G269" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H269" s="1"/>
       <c r="I269" s="1"/>
@@ -8865,7 +8863,7 @@
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
       <c r="G270" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H270" s="1"/>
       <c r="I270" s="1"/>
@@ -8893,7 +8891,7 @@
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
       <c r="G271" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H271" s="1"/>
       <c r="I271" s="1"/>
@@ -8921,7 +8919,7 @@
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
       <c r="G272" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
@@ -8949,7 +8947,7 @@
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
       <c r="G273" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H273" s="1"/>
       <c r="I273" s="1"/>
@@ -8977,10 +8975,10 @@
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I274" s="1"/>
       <c r="J274" s="1"/>
@@ -9007,10 +9005,10 @@
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
       <c r="G275" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I275" s="1"/>
       <c r="J275" s="1"/>
@@ -9037,10 +9035,10 @@
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
       <c r="G276" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I276" s="1"/>
       <c r="J276" s="1"/>
@@ -9067,10 +9065,10 @@
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
       <c r="G277" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I277" s="1"/>
       <c r="J277" s="1"/>
@@ -9097,10 +9095,10 @@
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
       <c r="G278" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H278" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H278" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I278" s="1"/>
       <c r="J278" s="1"/>
@@ -9127,10 +9125,10 @@
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
       <c r="G279" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I279" s="1"/>
       <c r="J279" s="1"/>
@@ -9157,10 +9155,10 @@
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I280" s="1"/>
       <c r="J280" s="1"/>
@@ -9187,10 +9185,10 @@
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I281" s="1"/>
       <c r="J281" s="1"/>
@@ -9217,10 +9215,10 @@
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
       <c r="G282" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I282" s="1"/>
       <c r="J282" s="1"/>
@@ -9247,10 +9245,10 @@
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
       <c r="G283" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I283" s="1"/>
       <c r="J283" s="1"/>
@@ -9277,10 +9275,10 @@
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
       <c r="G284" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I284" s="1"/>
       <c r="J284" s="1"/>
@@ -9307,10 +9305,10 @@
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I285" s="1"/>
       <c r="J285" s="1"/>
@@ -9337,10 +9335,10 @@
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
@@ -9367,10 +9365,10 @@
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
       <c r="G287" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
@@ -9397,10 +9395,10 @@
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
       <c r="G288" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I288" s="1"/>
       <c r="J288" s="1"/>
@@ -9427,10 +9425,10 @@
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
       <c r="G289" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I289" s="1"/>
       <c r="J289" s="1"/>
@@ -9457,10 +9455,10 @@
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I290" s="1"/>
       <c r="J290" s="1"/>
@@ -9487,10 +9485,10 @@
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I291" s="1"/>
       <c r="J291" s="1"/>
@@ -9517,7 +9515,7 @@
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
       <c r="G292" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H292" s="1"/>
       <c r="I292" s="1"/>
@@ -9545,7 +9543,7 @@
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
       <c r="G293" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H293" s="1"/>
       <c r="I293" s="1"/>
@@ -9573,7 +9571,7 @@
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
       <c r="G294" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H294" s="1"/>
       <c r="I294" s="1"/>
@@ -9601,7 +9599,7 @@
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
       <c r="G295" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H295" s="1"/>
       <c r="I295" s="1"/>
@@ -9629,7 +9627,7 @@
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
       <c r="G296" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H296" s="1"/>
       <c r="I296" s="1"/>
@@ -9657,7 +9655,7 @@
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
       <c r="G297" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H297" s="1"/>
       <c r="I297" s="1"/>
@@ -9685,7 +9683,7 @@
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
       <c r="G298" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H298" s="1"/>
       <c r="I298" s="1"/>
@@ -9713,7 +9711,7 @@
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
       <c r="G299" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H299" s="1"/>
       <c r="I299" s="1"/>
@@ -9741,7 +9739,7 @@
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
       <c r="G300" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
@@ -9769,7 +9767,7 @@
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
       <c r="G301" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H301" s="1"/>
       <c r="I301" s="1"/>
@@ -9797,7 +9795,7 @@
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
       <c r="G302" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H302" s="1"/>
       <c r="I302" s="1"/>
@@ -9825,10 +9823,10 @@
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H303" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I303" s="1"/>
       <c r="J303" s="1"/>
@@ -9855,10 +9853,10 @@
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
       <c r="G304" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I304" s="1"/>
       <c r="J304" s="1"/>
@@ -9885,10 +9883,10 @@
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
       <c r="G305" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I305" s="1"/>
       <c r="J305" s="1"/>
@@ -9915,10 +9913,10 @@
       <c r="E306" s="2"/>
       <c r="F306" s="2"/>
       <c r="G306" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
@@ -9945,10 +9943,10 @@
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
       <c r="G307" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H307" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H307" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I307" s="1"/>
       <c r="J307" s="1"/>
@@ -9975,10 +9973,10 @@
       <c r="E308" s="2"/>
       <c r="F308" s="2"/>
       <c r="G308" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
@@ -10005,10 +10003,10 @@
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I309" s="1"/>
       <c r="J309" s="1"/>
@@ -10035,10 +10033,10 @@
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H310" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I310" s="1"/>
       <c r="J310" s="1"/>
@@ -10065,10 +10063,10 @@
       <c r="E311" s="2"/>
       <c r="F311" s="2"/>
       <c r="G311" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I311" s="1"/>
       <c r="J311" s="1"/>
@@ -10095,10 +10093,10 @@
       <c r="E312" s="2"/>
       <c r="F312" s="2"/>
       <c r="G312" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I312" s="1"/>
       <c r="J312" s="1"/>
@@ -10125,10 +10123,10 @@
       <c r="E313" s="2"/>
       <c r="F313" s="2"/>
       <c r="G313" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
@@ -10155,10 +10153,10 @@
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I314" s="1"/>
       <c r="J314" s="1"/>
@@ -10185,10 +10183,10 @@
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I315" s="1"/>
       <c r="J315" s="1"/>
@@ -10215,10 +10213,10 @@
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
       <c r="G316" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I316" s="1"/>
       <c r="J316" s="1"/>
@@ -10245,10 +10243,10 @@
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
       <c r="G317" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I317" s="1"/>
       <c r="J317" s="1"/>
@@ -10275,10 +10273,10 @@
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
       <c r="G318" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I318" s="1"/>
       <c r="J318" s="1"/>
@@ -10305,10 +10303,10 @@
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I319" s="1"/>
       <c r="J319" s="1"/>
@@ -10335,10 +10333,10 @@
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
       <c r="G320" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I320" s="1"/>
       <c r="J320" s="1"/>
@@ -10365,7 +10363,7 @@
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
       <c r="G321" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H321" s="1"/>
       <c r="I321" s="1"/>
@@ -10393,7 +10391,7 @@
       <c r="E322" s="2"/>
       <c r="F322" s="2"/>
       <c r="G322" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H322" s="1"/>
       <c r="I322" s="1"/>
@@ -10421,7 +10419,7 @@
       <c r="E323" s="2"/>
       <c r="F323" s="2"/>
       <c r="G323" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H323" s="1"/>
       <c r="I323" s="1"/>
@@ -10449,7 +10447,7 @@
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
       <c r="G324" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H324" s="1"/>
       <c r="I324" s="1"/>
@@ -10477,7 +10475,7 @@
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
       <c r="G325" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H325" s="1"/>
       <c r="I325" s="1"/>
@@ -10505,7 +10503,7 @@
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
       <c r="G326" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H326" s="1"/>
       <c r="I326" s="1"/>
@@ -10533,7 +10531,7 @@
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
       <c r="G327" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H327" s="1"/>
       <c r="I327" s="1"/>
@@ -10561,7 +10559,7 @@
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
       <c r="G328" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H328" s="1"/>
       <c r="I328" s="1"/>
@@ -10589,7 +10587,7 @@
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
       <c r="G329" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H329" s="1"/>
       <c r="I329" s="1"/>
@@ -10617,7 +10615,7 @@
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
       <c r="G330" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H330" s="1"/>
       <c r="I330" s="1"/>
@@ -10645,7 +10643,7 @@
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
       <c r="G331" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H331" s="1"/>
       <c r="I331" s="1"/>
@@ -10673,10 +10671,10 @@
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H332" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I332" s="1"/>
       <c r="J332" s="1"/>
@@ -10703,10 +10701,10 @@
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
       <c r="G333" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I333" s="1"/>
       <c r="J333" s="1"/>
@@ -10733,10 +10731,10 @@
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
       <c r="G334" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I334" s="1"/>
       <c r="J334" s="1"/>
@@ -10763,10 +10761,10 @@
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
       <c r="G335" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I335" s="1"/>
       <c r="J335" s="1"/>
@@ -10793,10 +10791,10 @@
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
       <c r="G336" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H336" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H336" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I336" s="1"/>
       <c r="J336" s="1"/>
@@ -10823,10 +10821,10 @@
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
       <c r="G337" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
@@ -10853,10 +10851,10 @@
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I338" s="1"/>
       <c r="J338" s="1"/>
@@ -10883,10 +10881,10 @@
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I339" s="1"/>
       <c r="J339" s="1"/>
@@ -10913,10 +10911,10 @@
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
       <c r="G340" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I340" s="1"/>
       <c r="J340" s="1"/>
@@ -10943,10 +10941,10 @@
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
       <c r="G341" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
@@ -10973,10 +10971,10 @@
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
       <c r="G342" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I342" s="1"/>
       <c r="J342" s="1"/>
@@ -11003,10 +11001,10 @@
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I343" s="1"/>
       <c r="J343" s="1"/>
@@ -11033,10 +11031,10 @@
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I344" s="1"/>
       <c r="J344" s="1"/>
@@ -11063,10 +11061,10 @@
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
       <c r="G345" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I345" s="1"/>
       <c r="J345" s="1"/>
@@ -11093,10 +11091,10 @@
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
       <c r="G346" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I346" s="1"/>
       <c r="J346" s="1"/>
@@ -11123,10 +11121,10 @@
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
       <c r="G347" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I347" s="1"/>
       <c r="J347" s="1"/>
@@ -11153,10 +11151,10 @@
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
@@ -11183,10 +11181,10 @@
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
       <c r="G349" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I349" s="1"/>
       <c r="J349" s="1"/>
@@ -11213,7 +11211,7 @@
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
       <c r="G350" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H350" s="1"/>
       <c r="I350" s="1"/>
@@ -11241,7 +11239,7 @@
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
       <c r="G351" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H351" s="1"/>
       <c r="I351" s="1"/>
@@ -11269,7 +11267,7 @@
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
       <c r="G352" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H352" s="1"/>
       <c r="I352" s="1"/>
@@ -11297,7 +11295,7 @@
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
       <c r="G353" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H353" s="1"/>
       <c r="I353" s="1"/>
@@ -11325,7 +11323,7 @@
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
       <c r="G354" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
@@ -11353,7 +11351,7 @@
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
       <c r="G355" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
@@ -11381,7 +11379,7 @@
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
       <c r="G356" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H356" s="1"/>
       <c r="I356" s="1"/>
@@ -11409,7 +11407,7 @@
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
       <c r="G357" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H357" s="1"/>
       <c r="I357" s="1"/>
@@ -11437,7 +11435,7 @@
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
       <c r="G358" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H358" s="1"/>
       <c r="I358" s="1"/>
@@ -11465,7 +11463,7 @@
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
       <c r="G359" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H359" s="1"/>
       <c r="I359" s="1"/>
@@ -11493,7 +11491,7 @@
       <c r="E360" s="2"/>
       <c r="F360" s="2"/>
       <c r="G360" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H360" s="1"/>
       <c r="I360" s="1"/>
@@ -11521,10 +11519,10 @@
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H361" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I361" s="1"/>
       <c r="J361" s="1"/>
@@ -11551,10 +11549,10 @@
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
       <c r="G362" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
@@ -11581,10 +11579,10 @@
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
       <c r="G363" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I363" s="1"/>
       <c r="J363" s="1"/>
@@ -11611,10 +11609,10 @@
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
       <c r="G364" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H364" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I364" s="1"/>
       <c r="J364" s="1"/>
@@ -11641,10 +11639,10 @@
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
       <c r="G365" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H365" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H365" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I365" s="1"/>
       <c r="J365" s="1"/>
@@ -11671,10 +11669,10 @@
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
       <c r="G366" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H366" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
@@ -11701,10 +11699,10 @@
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
       <c r="G367" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H367" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I367" s="1"/>
       <c r="J367" s="1"/>
@@ -11731,10 +11729,10 @@
       <c r="E368" s="1"/>
       <c r="F368" s="1"/>
       <c r="G368" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H368" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
@@ -11761,10 +11759,10 @@
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
       <c r="G369" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H369" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I369" s="1"/>
       <c r="J369" s="1"/>
@@ -11791,10 +11789,10 @@
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
       <c r="G370" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H370" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
@@ -11821,10 +11819,10 @@
       <c r="E371" s="2"/>
       <c r="F371" s="2"/>
       <c r="G371" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H371" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
@@ -11851,10 +11849,10 @@
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
       <c r="G372" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H372" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
@@ -11881,10 +11879,10 @@
       <c r="E373" s="1"/>
       <c r="F373" s="1"/>
       <c r="G373" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
@@ -11911,10 +11909,10 @@
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
       <c r="G374" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I374" s="1"/>
       <c r="J374" s="1"/>
@@ -11941,10 +11939,10 @@
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
       <c r="G375" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I375" s="1"/>
       <c r="J375" s="1"/>
@@ -11971,10 +11969,10 @@
       <c r="E376" s="2"/>
       <c r="F376" s="2"/>
       <c r="G376" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H376" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
@@ -12001,10 +11999,10 @@
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
       <c r="G377" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H377" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I377" s="1"/>
       <c r="J377" s="1"/>
@@ -12031,10 +12029,10 @@
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
       <c r="G378" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H378" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I378" s="1"/>
       <c r="J378" s="1"/>
@@ -12061,7 +12059,7 @@
       <c r="E379" s="2"/>
       <c r="F379" s="2"/>
       <c r="G379" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H379" s="1"/>
       <c r="I379" s="1"/>
@@ -12089,7 +12087,7 @@
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
       <c r="G380" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H380" s="1"/>
       <c r="I380" s="1"/>
@@ -12117,7 +12115,7 @@
       <c r="E381" s="2"/>
       <c r="F381" s="2"/>
       <c r="G381" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H381" s="1"/>
       <c r="I381" s="1"/>
@@ -12145,7 +12143,7 @@
       <c r="E382" s="2"/>
       <c r="F382" s="2"/>
       <c r="G382" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H382" s="1"/>
       <c r="I382" s="1"/>
@@ -12173,7 +12171,7 @@
       <c r="E383" s="2"/>
       <c r="F383" s="2"/>
       <c r="G383" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H383" s="1"/>
       <c r="I383" s="1"/>
@@ -12201,7 +12199,7 @@
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
       <c r="G384" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H384" s="1"/>
       <c r="I384" s="1"/>
@@ -12229,7 +12227,7 @@
       <c r="E385" s="2"/>
       <c r="F385" s="2"/>
       <c r="G385" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H385" s="1"/>
       <c r="I385" s="1"/>
@@ -12257,7 +12255,7 @@
       <c r="E386" s="2"/>
       <c r="F386" s="2"/>
       <c r="G386" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H386" s="1"/>
       <c r="I386" s="1"/>
@@ -12285,7 +12283,7 @@
       <c r="E387" s="2"/>
       <c r="F387" s="2"/>
       <c r="G387" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H387" s="1"/>
       <c r="I387" s="1"/>
@@ -12313,7 +12311,7 @@
       <c r="E388" s="2"/>
       <c r="F388" s="2"/>
       <c r="G388" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H388" s="1"/>
       <c r="I388" s="1"/>
@@ -12341,7 +12339,7 @@
       <c r="E389" s="2"/>
       <c r="F389" s="2"/>
       <c r="G389" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H389" s="1"/>
       <c r="I389" s="1"/>
@@ -12369,10 +12367,10 @@
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H390" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I390" s="1"/>
       <c r="J390" s="1"/>
@@ -12399,10 +12397,10 @@
       <c r="E391" s="2"/>
       <c r="F391" s="2"/>
       <c r="G391" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I391" s="1"/>
       <c r="J391" s="1"/>
@@ -12429,10 +12427,10 @@
       <c r="E392" s="2"/>
       <c r="F392" s="2"/>
       <c r="G392" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H392" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I392" s="1"/>
       <c r="J392" s="1"/>
@@ -12459,10 +12457,10 @@
       <c r="E393" s="2"/>
       <c r="F393" s="2"/>
       <c r="G393" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I393" s="1"/>
       <c r="J393" s="1"/>
@@ -12489,10 +12487,10 @@
       <c r="E394" s="2"/>
       <c r="F394" s="2"/>
       <c r="G394" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H394" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H394" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I394" s="1"/>
       <c r="J394" s="1"/>
@@ -12519,10 +12517,10 @@
       <c r="E395" s="2"/>
       <c r="F395" s="2"/>
       <c r="G395" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H395" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I395" s="1"/>
       <c r="J395" s="1"/>
@@ -12549,10 +12547,10 @@
       <c r="E396" s="1"/>
       <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H396" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I396" s="1"/>
       <c r="J396" s="1"/>
@@ -12579,10 +12577,10 @@
       <c r="E397" s="1"/>
       <c r="F397" s="1"/>
       <c r="G397" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H397" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I397" s="1"/>
       <c r="J397" s="1"/>
@@ -12609,10 +12607,10 @@
       <c r="E398" s="2"/>
       <c r="F398" s="2"/>
       <c r="G398" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H398" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I398" s="1"/>
       <c r="J398" s="1"/>
@@ -12639,10 +12637,10 @@
       <c r="E399" s="2"/>
       <c r="F399" s="2"/>
       <c r="G399" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H399" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I399" s="1"/>
       <c r="J399" s="1"/>
@@ -12669,10 +12667,10 @@
       <c r="E400" s="2"/>
       <c r="F400" s="2"/>
       <c r="G400" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H400" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I400" s="1"/>
       <c r="J400" s="1"/>
@@ -12699,10 +12697,10 @@
       <c r="E401" s="1"/>
       <c r="F401" s="1"/>
       <c r="G401" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H401" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I401" s="1"/>
       <c r="J401" s="1"/>
@@ -12729,10 +12727,10 @@
       <c r="E402" s="1"/>
       <c r="F402" s="1"/>
       <c r="G402" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H402" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I402" s="1"/>
       <c r="J402" s="1"/>
@@ -12759,10 +12757,10 @@
       <c r="E403" s="2"/>
       <c r="F403" s="2"/>
       <c r="G403" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H403" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I403" s="1"/>
       <c r="J403" s="1"/>
@@ -12789,10 +12787,10 @@
       <c r="E404" s="2"/>
       <c r="F404" s="2"/>
       <c r="G404" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H404" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I404" s="1"/>
       <c r="J404" s="1"/>
@@ -12819,10 +12817,10 @@
       <c r="E405" s="2"/>
       <c r="F405" s="2"/>
       <c r="G405" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H405" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I405" s="1"/>
       <c r="J405" s="1"/>
@@ -12849,10 +12847,10 @@
       <c r="E406" s="1"/>
       <c r="F406" s="1"/>
       <c r="G406" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H406" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I406" s="1"/>
       <c r="J406" s="1"/>
@@ -12879,10 +12877,10 @@
       <c r="E407" s="1"/>
       <c r="F407" s="1"/>
       <c r="G407" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H407" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I407" s="1"/>
       <c r="J407" s="1"/>
@@ -12909,7 +12907,7 @@
       <c r="E408" s="2"/>
       <c r="F408" s="2"/>
       <c r="G408" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H408" s="1"/>
       <c r="I408" s="1"/>
@@ -12937,7 +12935,7 @@
       <c r="E409" s="2"/>
       <c r="F409" s="2"/>
       <c r="G409" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H409" s="1"/>
       <c r="I409" s="1"/>
@@ -12965,7 +12963,7 @@
       <c r="E410" s="2"/>
       <c r="F410" s="2"/>
       <c r="G410" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H410" s="1"/>
       <c r="I410" s="1"/>
@@ -12993,7 +12991,7 @@
       <c r="E411" s="2"/>
       <c r="F411" s="2"/>
       <c r="G411" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H411" s="1"/>
       <c r="I411" s="1"/>
@@ -13021,7 +13019,7 @@
       <c r="E412" s="2"/>
       <c r="F412" s="2"/>
       <c r="G412" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H412" s="1"/>
       <c r="I412" s="1"/>
@@ -13049,7 +13047,7 @@
       <c r="E413" s="2"/>
       <c r="F413" s="2"/>
       <c r="G413" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H413" s="1"/>
       <c r="I413" s="1"/>
@@ -13077,7 +13075,7 @@
       <c r="E414" s="2"/>
       <c r="F414" s="2"/>
       <c r="G414" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H414" s="1"/>
       <c r="I414" s="1"/>
@@ -13105,7 +13103,7 @@
       <c r="E415" s="2"/>
       <c r="F415" s="2"/>
       <c r="G415" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H415" s="1"/>
       <c r="I415" s="1"/>
@@ -13133,7 +13131,7 @@
       <c r="E416" s="2"/>
       <c r="F416" s="2"/>
       <c r="G416" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H416" s="1"/>
       <c r="I416" s="1"/>
@@ -13161,7 +13159,7 @@
       <c r="E417" s="2"/>
       <c r="F417" s="2"/>
       <c r="G417" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H417" s="1"/>
       <c r="I417" s="1"/>
@@ -13189,7 +13187,7 @@
       <c r="E418" s="2"/>
       <c r="F418" s="2"/>
       <c r="G418" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H418" s="1"/>
       <c r="I418" s="1"/>
@@ -13217,10 +13215,10 @@
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
       <c r="G419" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H419" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I419" s="1"/>
       <c r="J419" s="1"/>
@@ -13247,10 +13245,10 @@
       <c r="E420" s="2"/>
       <c r="F420" s="2"/>
       <c r="G420" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H420" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I420" s="1"/>
       <c r="J420" s="1"/>
@@ -13277,10 +13275,10 @@
       <c r="E421" s="2"/>
       <c r="F421" s="2"/>
       <c r="G421" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H421" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I421" s="1"/>
       <c r="J421" s="1"/>
@@ -13307,10 +13305,10 @@
       <c r="E422" s="2"/>
       <c r="F422" s="2"/>
       <c r="G422" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H422" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I422" s="1"/>
       <c r="J422" s="1"/>
@@ -13337,10 +13335,10 @@
       <c r="E423" s="2"/>
       <c r="F423" s="2"/>
       <c r="G423" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H423" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H423" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I423" s="1"/>
       <c r="J423" s="1"/>
@@ -13367,10 +13365,10 @@
       <c r="E424" s="2"/>
       <c r="F424" s="2"/>
       <c r="G424" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I424" s="1"/>
       <c r="J424" s="1"/>
@@ -13397,10 +13395,10 @@
       <c r="E425" s="1"/>
       <c r="F425" s="1"/>
       <c r="G425" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H425" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I425" s="1"/>
       <c r="J425" s="1"/>
@@ -13427,10 +13425,10 @@
       <c r="E426" s="1"/>
       <c r="F426" s="1"/>
       <c r="G426" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H426" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I426" s="1"/>
       <c r="J426" s="1"/>
@@ -13457,10 +13455,10 @@
       <c r="E427" s="2"/>
       <c r="F427" s="2"/>
       <c r="G427" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I427" s="1"/>
       <c r="J427" s="1"/>
@@ -13487,10 +13485,10 @@
       <c r="E428" s="2"/>
       <c r="F428" s="2"/>
       <c r="G428" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I428" s="1"/>
       <c r="J428" s="1"/>
@@ -13517,10 +13515,10 @@
       <c r="E429" s="2"/>
       <c r="F429" s="2"/>
       <c r="G429" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I429" s="1"/>
       <c r="J429" s="1"/>
@@ -13547,10 +13545,10 @@
       <c r="E430" s="1"/>
       <c r="F430" s="1"/>
       <c r="G430" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I430" s="1"/>
       <c r="J430" s="1"/>
@@ -13577,10 +13575,10 @@
       <c r="E431" s="1"/>
       <c r="F431" s="1"/>
       <c r="G431" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I431" s="1"/>
       <c r="J431" s="1"/>
@@ -13607,10 +13605,10 @@
       <c r="E432" s="2"/>
       <c r="F432" s="2"/>
       <c r="G432" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I432" s="1"/>
       <c r="J432" s="1"/>
@@ -13637,10 +13635,10 @@
       <c r="E433" s="2"/>
       <c r="F433" s="2"/>
       <c r="G433" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I433" s="1"/>
       <c r="J433" s="1"/>
@@ -13667,10 +13665,10 @@
       <c r="E434" s="2"/>
       <c r="F434" s="2"/>
       <c r="G434" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I434" s="1"/>
       <c r="J434" s="1"/>
@@ -13697,10 +13695,10 @@
       <c r="E435" s="1"/>
       <c r="F435" s="1"/>
       <c r="G435" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H435" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I435" s="1"/>
       <c r="J435" s="1"/>
@@ -13727,10 +13725,10 @@
       <c r="E436" s="1"/>
       <c r="F436" s="1"/>
       <c r="G436" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H436" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I436" s="1"/>
       <c r="J436" s="1"/>
@@ -13757,7 +13755,7 @@
       <c r="E437" s="2"/>
       <c r="F437" s="2"/>
       <c r="G437" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H437" s="1"/>
       <c r="I437" s="1"/>
@@ -13785,7 +13783,7 @@
       <c r="E438" s="2"/>
       <c r="F438" s="2"/>
       <c r="G438" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H438" s="1"/>
       <c r="I438" s="1"/>
@@ -13813,7 +13811,7 @@
       <c r="E439" s="2"/>
       <c r="F439" s="2"/>
       <c r="G439" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H439" s="1"/>
       <c r="I439" s="1"/>
@@ -13841,7 +13839,7 @@
       <c r="E440" s="2"/>
       <c r="F440" s="2"/>
       <c r="G440" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H440" s="1"/>
       <c r="I440" s="1"/>
@@ -13869,7 +13867,7 @@
       <c r="E441" s="2"/>
       <c r="F441" s="2"/>
       <c r="G441" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H441" s="1"/>
       <c r="I441" s="1"/>
@@ -13897,7 +13895,7 @@
       <c r="E442" s="2"/>
       <c r="F442" s="2"/>
       <c r="G442" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H442" s="1"/>
       <c r="I442" s="1"/>
@@ -13925,7 +13923,7 @@
       <c r="E443" s="2"/>
       <c r="F443" s="2"/>
       <c r="G443" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H443" s="1"/>
       <c r="I443" s="1"/>
@@ -13953,7 +13951,7 @@
       <c r="E444" s="2"/>
       <c r="F444" s="2"/>
       <c r="G444" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H444" s="1"/>
       <c r="I444" s="1"/>
@@ -13981,7 +13979,7 @@
       <c r="E445" s="2"/>
       <c r="F445" s="2"/>
       <c r="G445" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H445" s="1"/>
       <c r="I445" s="1"/>
@@ -14009,7 +14007,7 @@
       <c r="E446" s="2"/>
       <c r="F446" s="2"/>
       <c r="G446" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H446" s="1"/>
       <c r="I446" s="1"/>
@@ -14037,7 +14035,7 @@
       <c r="E447" s="2"/>
       <c r="F447" s="2"/>
       <c r="G447" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H447" s="1"/>
       <c r="I447" s="1"/>
@@ -14065,10 +14063,10 @@
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H448" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I448" s="1"/>
       <c r="J448" s="1"/>
@@ -14095,10 +14093,10 @@
       <c r="E449" s="2"/>
       <c r="F449" s="2"/>
       <c r="G449" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I449" s="1"/>
       <c r="J449" s="1"/>
@@ -14125,10 +14123,10 @@
       <c r="E450" s="2"/>
       <c r="F450" s="2"/>
       <c r="G450" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I450" s="1"/>
       <c r="J450" s="1"/>
@@ -14155,10 +14153,10 @@
       <c r="E451" s="2"/>
       <c r="F451" s="2"/>
       <c r="G451" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I451" s="1"/>
       <c r="J451" s="1"/>
@@ -14185,10 +14183,10 @@
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H452" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H452" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I452" s="1"/>
       <c r="J452" s="1"/>
@@ -14215,10 +14213,10 @@
       <c r="E453" s="2"/>
       <c r="F453" s="2"/>
       <c r="G453" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H453" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I453" s="1"/>
       <c r="J453" s="1"/>
@@ -14245,10 +14243,10 @@
       <c r="E454" s="1"/>
       <c r="F454" s="1"/>
       <c r="G454" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I454" s="1"/>
       <c r="J454" s="1"/>
@@ -14275,10 +14273,10 @@
       <c r="E455" s="1"/>
       <c r="F455" s="1"/>
       <c r="G455" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H455" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I455" s="1"/>
       <c r="J455" s="1"/>
@@ -14305,10 +14303,10 @@
       <c r="E456" s="2"/>
       <c r="F456" s="2"/>
       <c r="G456" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H456" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I456" s="1"/>
       <c r="J456" s="1"/>
@@ -14335,10 +14333,10 @@
       <c r="E457" s="2"/>
       <c r="F457" s="2"/>
       <c r="G457" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H457" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I457" s="1"/>
       <c r="J457" s="1"/>
@@ -14365,10 +14363,10 @@
       <c r="E458" s="2"/>
       <c r="F458" s="2"/>
       <c r="G458" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I458" s="1"/>
       <c r="J458" s="1"/>
@@ -14395,10 +14393,10 @@
       <c r="E459" s="1"/>
       <c r="F459" s="1"/>
       <c r="G459" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I459" s="1"/>
       <c r="J459" s="1"/>
@@ -14425,10 +14423,10 @@
       <c r="E460" s="1"/>
       <c r="F460" s="1"/>
       <c r="G460" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H460" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I460" s="1"/>
       <c r="J460" s="1"/>
@@ -14455,10 +14453,10 @@
       <c r="E461" s="2"/>
       <c r="F461" s="2"/>
       <c r="G461" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I461" s="1"/>
       <c r="J461" s="1"/>
@@ -14485,10 +14483,10 @@
       <c r="E462" s="2"/>
       <c r="F462" s="2"/>
       <c r="G462" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H462" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I462" s="1"/>
       <c r="J462" s="1"/>
@@ -14515,10 +14513,10 @@
       <c r="E463" s="2"/>
       <c r="F463" s="2"/>
       <c r="G463" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H463" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I463" s="1"/>
       <c r="J463" s="1"/>
@@ -14545,10 +14543,10 @@
       <c r="E464" s="1"/>
       <c r="F464" s="1"/>
       <c r="G464" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H464" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I464" s="1"/>
       <c r="J464" s="1"/>
@@ -14575,10 +14573,10 @@
       <c r="E465" s="1"/>
       <c r="F465" s="1"/>
       <c r="G465" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H465" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I465" s="1"/>
       <c r="J465" s="1"/>
@@ -14605,7 +14603,7 @@
       <c r="E466" s="2"/>
       <c r="F466" s="2"/>
       <c r="G466" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H466" s="1"/>
       <c r="I466" s="1"/>
@@ -14633,7 +14631,7 @@
       <c r="E467" s="2"/>
       <c r="F467" s="2"/>
       <c r="G467" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H467" s="1"/>
       <c r="I467" s="1"/>
@@ -14661,7 +14659,7 @@
       <c r="E468" s="2"/>
       <c r="F468" s="2"/>
       <c r="G468" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H468" s="1"/>
       <c r="I468" s="1"/>
@@ -14689,7 +14687,7 @@
       <c r="E469" s="2"/>
       <c r="F469" s="2"/>
       <c r="G469" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H469" s="1"/>
       <c r="I469" s="1"/>
@@ -14717,7 +14715,7 @@
       <c r="E470" s="2"/>
       <c r="F470" s="2"/>
       <c r="G470" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H470" s="1"/>
       <c r="I470" s="1"/>
@@ -14745,7 +14743,7 @@
       <c r="E471" s="2"/>
       <c r="F471" s="2"/>
       <c r="G471" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H471" s="1"/>
       <c r="I471" s="1"/>
@@ -14773,7 +14771,7 @@
       <c r="E472" s="2"/>
       <c r="F472" s="2"/>
       <c r="G472" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H472" s="1"/>
       <c r="I472" s="1"/>
@@ -14801,7 +14799,7 @@
       <c r="E473" s="2"/>
       <c r="F473" s="2"/>
       <c r="G473" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H473" s="1"/>
       <c r="I473" s="1"/>
@@ -14829,7 +14827,7 @@
       <c r="E474" s="2"/>
       <c r="F474" s="2"/>
       <c r="G474" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H474" s="1"/>
       <c r="I474" s="1"/>
@@ -14857,7 +14855,7 @@
       <c r="E475" s="2"/>
       <c r="F475" s="2"/>
       <c r="G475" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H475" s="1"/>
       <c r="I475" s="1"/>
@@ -14885,7 +14883,7 @@
       <c r="E476" s="2"/>
       <c r="F476" s="2"/>
       <c r="G476" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H476" s="1"/>
       <c r="I476" s="1"/>
@@ -14913,10 +14911,10 @@
       <c r="E477" s="3"/>
       <c r="F477" s="3"/>
       <c r="G477" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H477" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I477" s="1"/>
       <c r="J477" s="1"/>
@@ -14943,10 +14941,10 @@
       <c r="E478" s="2"/>
       <c r="F478" s="2"/>
       <c r="G478" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H478" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I478" s="1"/>
       <c r="J478" s="1"/>
@@ -14973,10 +14971,10 @@
       <c r="E479" s="2"/>
       <c r="F479" s="2"/>
       <c r="G479" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H479" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I479" s="1"/>
       <c r="J479" s="1"/>
@@ -15003,10 +15001,10 @@
       <c r="E480" s="2"/>
       <c r="F480" s="2"/>
       <c r="G480" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H480" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I480" s="1"/>
       <c r="J480" s="1"/>
@@ -15033,10 +15031,10 @@
       <c r="E481" s="2"/>
       <c r="F481" s="2"/>
       <c r="G481" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H481" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H481" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I481" s="1"/>
       <c r="J481" s="1"/>
@@ -15063,10 +15061,10 @@
       <c r="E482" s="2"/>
       <c r="F482" s="2"/>
       <c r="G482" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H482" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I482" s="1"/>
       <c r="J482" s="1"/>
@@ -15093,10 +15091,10 @@
       <c r="E483" s="1"/>
       <c r="F483" s="1"/>
       <c r="G483" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H483" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I483" s="1"/>
       <c r="J483" s="1"/>
@@ -15123,10 +15121,10 @@
       <c r="E484" s="1"/>
       <c r="F484" s="1"/>
       <c r="G484" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H484" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I484" s="1"/>
       <c r="J484" s="1"/>
@@ -15153,10 +15151,10 @@
       <c r="E485" s="2"/>
       <c r="F485" s="2"/>
       <c r="G485" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H485" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I485" s="1"/>
       <c r="J485" s="1"/>
@@ -15183,10 +15181,10 @@
       <c r="E486" s="2"/>
       <c r="F486" s="2"/>
       <c r="G486" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H486" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I486" s="1"/>
       <c r="J486" s="1"/>
@@ -15213,10 +15211,10 @@
       <c r="E487" s="2"/>
       <c r="F487" s="2"/>
       <c r="G487" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H487" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I487" s="1"/>
       <c r="J487" s="1"/>
@@ -15243,10 +15241,10 @@
       <c r="E488" s="1"/>
       <c r="F488" s="1"/>
       <c r="G488" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H488" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I488" s="1"/>
       <c r="J488" s="1"/>
@@ -15273,10 +15271,10 @@
       <c r="E489" s="1"/>
       <c r="F489" s="1"/>
       <c r="G489" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H489" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I489" s="1"/>
       <c r="J489" s="1"/>
@@ -15303,10 +15301,10 @@
       <c r="E490" s="2"/>
       <c r="F490" s="2"/>
       <c r="G490" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H490" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I490" s="1"/>
       <c r="J490" s="1"/>
@@ -15333,10 +15331,10 @@
       <c r="E491" s="2"/>
       <c r="F491" s="2"/>
       <c r="G491" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I491" s="1"/>
       <c r="J491" s="1"/>
@@ -15363,10 +15361,10 @@
       <c r="E492" s="2"/>
       <c r="F492" s="2"/>
       <c r="G492" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I492" s="1"/>
       <c r="J492" s="1"/>
@@ -15393,10 +15391,10 @@
       <c r="E493" s="1"/>
       <c r="F493" s="1"/>
       <c r="G493" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I493" s="1"/>
       <c r="J493" s="1"/>
@@ -15423,10 +15421,10 @@
       <c r="E494" s="1"/>
       <c r="F494" s="1"/>
       <c r="G494" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H494" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I494" s="1"/>
       <c r="J494" s="1"/>
@@ -15453,7 +15451,7 @@
       <c r="E495" s="2"/>
       <c r="F495" s="2"/>
       <c r="G495" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H495" s="1"/>
       <c r="I495" s="1"/>
@@ -15481,7 +15479,7 @@
       <c r="E496" s="2"/>
       <c r="F496" s="2"/>
       <c r="G496" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H496" s="1"/>
       <c r="I496" s="1"/>
@@ -15509,7 +15507,7 @@
       <c r="E497" s="2"/>
       <c r="F497" s="2"/>
       <c r="G497" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H497" s="1"/>
       <c r="I497" s="1"/>
@@ -15537,7 +15535,7 @@
       <c r="E498" s="2"/>
       <c r="F498" s="2"/>
       <c r="G498" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H498" s="1"/>
       <c r="I498" s="1"/>
@@ -15565,7 +15563,7 @@
       <c r="E499" s="2"/>
       <c r="F499" s="2"/>
       <c r="G499" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H499" s="1"/>
       <c r="I499" s="1"/>
@@ -15593,7 +15591,7 @@
       <c r="E500" s="2"/>
       <c r="F500" s="2"/>
       <c r="G500" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H500" s="1"/>
       <c r="I500" s="1"/>
@@ -15621,7 +15619,7 @@
       <c r="E501" s="2"/>
       <c r="F501" s="2"/>
       <c r="G501" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H501" s="1"/>
       <c r="I501" s="1"/>
@@ -15649,7 +15647,7 @@
       <c r="E502" s="2"/>
       <c r="F502" s="2"/>
       <c r="G502" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H502" s="1"/>
       <c r="I502" s="1"/>
@@ -15677,7 +15675,7 @@
       <c r="E503" s="2"/>
       <c r="F503" s="2"/>
       <c r="G503" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H503" s="1"/>
       <c r="I503" s="1"/>
@@ -15705,7 +15703,7 @@
       <c r="E504" s="2"/>
       <c r="F504" s="2"/>
       <c r="G504" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H504" s="1"/>
       <c r="I504" s="1"/>
@@ -15733,7 +15731,7 @@
       <c r="E505" s="2"/>
       <c r="F505" s="2"/>
       <c r="G505" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H505" s="1"/>
       <c r="I505" s="1"/>
@@ -15761,10 +15759,10 @@
       <c r="E506" s="3"/>
       <c r="F506" s="3"/>
       <c r="G506" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H506" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I506" s="1"/>
       <c r="J506" s="1"/>
@@ -15791,10 +15789,10 @@
       <c r="E507" s="2"/>
       <c r="F507" s="2"/>
       <c r="G507" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H507" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I507" s="1"/>
       <c r="J507" s="1"/>
@@ -15821,10 +15819,10 @@
       <c r="E508" s="2"/>
       <c r="F508" s="2"/>
       <c r="G508" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I508" s="1"/>
       <c r="J508" s="1"/>
@@ -15851,10 +15849,10 @@
       <c r="E509" s="2"/>
       <c r="F509" s="2"/>
       <c r="G509" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I509" s="1"/>
       <c r="J509" s="1"/>
@@ -15881,10 +15879,10 @@
       <c r="E510" s="2"/>
       <c r="F510" s="2"/>
       <c r="G510" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H510" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H510" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I510" s="1"/>
       <c r="J510" s="1"/>
@@ -15911,10 +15909,10 @@
       <c r="E511" s="2"/>
       <c r="F511" s="2"/>
       <c r="G511" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H511" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I511" s="1"/>
       <c r="J511" s="1"/>
@@ -15941,10 +15939,10 @@
       <c r="E512" s="1"/>
       <c r="F512" s="1"/>
       <c r="G512" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I512" s="1"/>
       <c r="J512" s="1"/>
@@ -15971,10 +15969,10 @@
       <c r="E513" s="1"/>
       <c r="F513" s="1"/>
       <c r="G513" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I513" s="1"/>
       <c r="J513" s="1"/>
@@ -16001,10 +15999,10 @@
       <c r="E514" s="2"/>
       <c r="F514" s="2"/>
       <c r="G514" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I514" s="1"/>
       <c r="J514" s="1"/>
@@ -16031,10 +16029,10 @@
       <c r="E515" s="2"/>
       <c r="F515" s="2"/>
       <c r="G515" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H515" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I515" s="1"/>
       <c r="J515" s="1"/>
@@ -16061,10 +16059,10 @@
       <c r="E516" s="2"/>
       <c r="F516" s="2"/>
       <c r="G516" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I516" s="1"/>
       <c r="J516" s="1"/>
@@ -16091,10 +16089,10 @@
       <c r="E517" s="1"/>
       <c r="F517" s="1"/>
       <c r="G517" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I517" s="1"/>
       <c r="J517" s="1"/>
@@ -16121,10 +16119,10 @@
       <c r="E518" s="1"/>
       <c r="F518" s="1"/>
       <c r="G518" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H518" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I518" s="1"/>
       <c r="J518" s="1"/>
@@ -16151,10 +16149,10 @@
       <c r="E519" s="2"/>
       <c r="F519" s="2"/>
       <c r="G519" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H519" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I519" s="1"/>
       <c r="J519" s="1"/>
@@ -16181,10 +16179,10 @@
       <c r="E520" s="2"/>
       <c r="F520" s="2"/>
       <c r="G520" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I520" s="1"/>
       <c r="J520" s="1"/>
@@ -16211,10 +16209,10 @@
       <c r="E521" s="2"/>
       <c r="F521" s="2"/>
       <c r="G521" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I521" s="1"/>
       <c r="J521" s="1"/>
@@ -16241,10 +16239,10 @@
       <c r="E522" s="1"/>
       <c r="F522" s="1"/>
       <c r="G522" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H522" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I522" s="1"/>
       <c r="J522" s="1"/>
@@ -16271,10 +16269,10 @@
       <c r="E523" s="1"/>
       <c r="F523" s="1"/>
       <c r="G523" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H523" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I523" s="1"/>
       <c r="J523" s="1"/>
@@ -16301,7 +16299,7 @@
       <c r="E524" s="2"/>
       <c r="F524" s="2"/>
       <c r="G524" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H524" s="1"/>
       <c r="I524" s="1"/>
@@ -16329,7 +16327,7 @@
       <c r="E525" s="2"/>
       <c r="F525" s="2"/>
       <c r="G525" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H525" s="1"/>
       <c r="I525" s="1"/>
@@ -16357,7 +16355,7 @@
       <c r="E526" s="2"/>
       <c r="F526" s="2"/>
       <c r="G526" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H526" s="1"/>
       <c r="I526" s="1"/>
@@ -16385,7 +16383,7 @@
       <c r="E527" s="2"/>
       <c r="F527" s="2"/>
       <c r="G527" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H527" s="1"/>
       <c r="I527" s="1"/>
@@ -16413,7 +16411,7 @@
       <c r="E528" s="2"/>
       <c r="F528" s="2"/>
       <c r="G528" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H528" s="1"/>
       <c r="I528" s="1"/>
@@ -16441,7 +16439,7 @@
       <c r="E529" s="2"/>
       <c r="F529" s="2"/>
       <c r="G529" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H529" s="1"/>
       <c r="I529" s="1"/>
@@ -16469,7 +16467,7 @@
       <c r="E530" s="2"/>
       <c r="F530" s="2"/>
       <c r="G530" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H530" s="1"/>
       <c r="I530" s="1"/>
@@ -16497,7 +16495,7 @@
       <c r="E531" s="2"/>
       <c r="F531" s="2"/>
       <c r="G531" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H531" s="1"/>
       <c r="I531" s="1"/>
@@ -16525,7 +16523,7 @@
       <c r="E532" s="2"/>
       <c r="F532" s="2"/>
       <c r="G532" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H532" s="1"/>
       <c r="I532" s="1"/>
@@ -16553,7 +16551,7 @@
       <c r="E533" s="2"/>
       <c r="F533" s="2"/>
       <c r="G533" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H533" s="1"/>
       <c r="I533" s="1"/>
@@ -16581,7 +16579,7 @@
       <c r="E534" s="2"/>
       <c r="F534" s="2"/>
       <c r="G534" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H534" s="1"/>
       <c r="I534" s="1"/>
@@ -16609,10 +16607,10 @@
       <c r="E535" s="3"/>
       <c r="F535" s="3"/>
       <c r="G535" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H535" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I535" s="1"/>
       <c r="J535" s="1"/>
@@ -16639,10 +16637,10 @@
       <c r="E536" s="2"/>
       <c r="F536" s="2"/>
       <c r="G536" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H536" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I536" s="1"/>
       <c r="J536" s="1"/>
@@ -16669,10 +16667,10 @@
       <c r="E537" s="2"/>
       <c r="F537" s="2"/>
       <c r="G537" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H537" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I537" s="1"/>
       <c r="J537" s="1"/>
@@ -16699,10 +16697,10 @@
       <c r="E538" s="2"/>
       <c r="F538" s="2"/>
       <c r="G538" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H538" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I538" s="1"/>
       <c r="J538" s="1"/>
@@ -16729,10 +16727,10 @@
       <c r="E539" s="2"/>
       <c r="F539" s="2"/>
       <c r="G539" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H539" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H539" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I539" s="1"/>
       <c r="J539" s="1"/>
@@ -16759,10 +16757,10 @@
       <c r="E540" s="2"/>
       <c r="F540" s="2"/>
       <c r="G540" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H540" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I540" s="1"/>
       <c r="J540" s="1"/>
@@ -16789,10 +16787,10 @@
       <c r="E541" s="1"/>
       <c r="F541" s="1"/>
       <c r="G541" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H541" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I541" s="1"/>
       <c r="J541" s="1"/>
@@ -16819,10 +16817,10 @@
       <c r="E542" s="1"/>
       <c r="F542" s="1"/>
       <c r="G542" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H542" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I542" s="1"/>
       <c r="J542" s="1"/>
@@ -16849,10 +16847,10 @@
       <c r="E543" s="2"/>
       <c r="F543" s="2"/>
       <c r="G543" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H543" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I543" s="1"/>
       <c r="J543" s="1"/>
@@ -16879,10 +16877,10 @@
       <c r="E544" s="2"/>
       <c r="F544" s="2"/>
       <c r="G544" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H544" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I544" s="1"/>
       <c r="J544" s="1"/>
@@ -16909,10 +16907,10 @@
       <c r="E545" s="2"/>
       <c r="F545" s="2"/>
       <c r="G545" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H545" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I545" s="1"/>
       <c r="J545" s="1"/>
@@ -16939,10 +16937,10 @@
       <c r="E546" s="1"/>
       <c r="F546" s="1"/>
       <c r="G546" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H546" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I546" s="1"/>
       <c r="J546" s="1"/>
@@ -16969,10 +16967,10 @@
       <c r="E547" s="1"/>
       <c r="F547" s="1"/>
       <c r="G547" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H547" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I547" s="1"/>
       <c r="J547" s="1"/>
@@ -16999,10 +16997,10 @@
       <c r="E548" s="2"/>
       <c r="F548" s="2"/>
       <c r="G548" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H548" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I548" s="1"/>
       <c r="J548" s="1"/>
@@ -17029,10 +17027,10 @@
       <c r="E549" s="2"/>
       <c r="F549" s="2"/>
       <c r="G549" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H549" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I549" s="1"/>
       <c r="J549" s="1"/>
@@ -17059,10 +17057,10 @@
       <c r="E550" s="2"/>
       <c r="F550" s="2"/>
       <c r="G550" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H550" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I550" s="1"/>
       <c r="J550" s="1"/>
@@ -17089,10 +17087,10 @@
       <c r="E551" s="1"/>
       <c r="F551" s="1"/>
       <c r="G551" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H551" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I551" s="1"/>
       <c r="J551" s="1"/>
@@ -17119,10 +17117,10 @@
       <c r="E552" s="1"/>
       <c r="F552" s="1"/>
       <c r="G552" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H552" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I552" s="1"/>
       <c r="J552" s="1"/>
@@ -17149,7 +17147,7 @@
       <c r="E553" s="2"/>
       <c r="F553" s="2"/>
       <c r="G553" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H553" s="1"/>
       <c r="I553" s="1"/>
@@ -17177,7 +17175,7 @@
       <c r="E554" s="2"/>
       <c r="F554" s="2"/>
       <c r="G554" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H554" s="1"/>
       <c r="I554" s="1"/>
@@ -17205,7 +17203,7 @@
       <c r="E555" s="2"/>
       <c r="F555" s="2"/>
       <c r="G555" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H555" s="1"/>
       <c r="I555" s="1"/>
@@ -17233,7 +17231,7 @@
       <c r="E556" s="2"/>
       <c r="F556" s="2"/>
       <c r="G556" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H556" s="1"/>
       <c r="I556" s="1"/>
@@ -17261,7 +17259,7 @@
       <c r="E557" s="2"/>
       <c r="F557" s="2"/>
       <c r="G557" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H557" s="1"/>
       <c r="I557" s="1"/>
@@ -17289,7 +17287,7 @@
       <c r="E558" s="2"/>
       <c r="F558" s="2"/>
       <c r="G558" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H558" s="1"/>
       <c r="I558" s="1"/>
@@ -17317,7 +17315,7 @@
       <c r="E559" s="2"/>
       <c r="F559" s="2"/>
       <c r="G559" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H559" s="1"/>
       <c r="I559" s="1"/>
@@ -17345,7 +17343,7 @@
       <c r="E560" s="2"/>
       <c r="F560" s="2"/>
       <c r="G560" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H560" s="1"/>
       <c r="I560" s="1"/>
@@ -17373,7 +17371,7 @@
       <c r="E561" s="2"/>
       <c r="F561" s="2"/>
       <c r="G561" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H561" s="1"/>
       <c r="I561" s="1"/>
@@ -17401,7 +17399,7 @@
       <c r="E562" s="2"/>
       <c r="F562" s="2"/>
       <c r="G562" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H562" s="1"/>
       <c r="I562" s="1"/>
@@ -17429,7 +17427,7 @@
       <c r="E563" s="2"/>
       <c r="F563" s="2"/>
       <c r="G563" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H563" s="1"/>
       <c r="I563" s="1"/>
@@ -17457,10 +17455,10 @@
       <c r="E564" s="3"/>
       <c r="F564" s="3"/>
       <c r="G564" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H564" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I564" s="1"/>
       <c r="J564" s="1"/>
@@ -17487,10 +17485,10 @@
       <c r="E565" s="2"/>
       <c r="F565" s="2"/>
       <c r="G565" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H565" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I565" s="1"/>
       <c r="J565" s="1"/>
@@ -17517,10 +17515,10 @@
       <c r="E566" s="2"/>
       <c r="F566" s="2"/>
       <c r="G566" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H566" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I566" s="1"/>
       <c r="J566" s="1"/>
@@ -17547,10 +17545,10 @@
       <c r="E567" s="2"/>
       <c r="F567" s="2"/>
       <c r="G567" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H567" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I567" s="1"/>
       <c r="J567" s="1"/>
@@ -17577,10 +17575,10 @@
       <c r="E568" s="2"/>
       <c r="F568" s="2"/>
       <c r="G568" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H568" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H568" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I568" s="1"/>
       <c r="J568" s="1"/>
@@ -17607,10 +17605,10 @@
       <c r="E569" s="2"/>
       <c r="F569" s="2"/>
       <c r="G569" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H569" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I569" s="1"/>
       <c r="J569" s="1"/>
@@ -17637,10 +17635,10 @@
       <c r="E570" s="1"/>
       <c r="F570" s="1"/>
       <c r="G570" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H570" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I570" s="1"/>
       <c r="J570" s="1"/>
@@ -17667,10 +17665,10 @@
       <c r="E571" s="1"/>
       <c r="F571" s="1"/>
       <c r="G571" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H571" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I571" s="1"/>
       <c r="J571" s="1"/>
@@ -17697,10 +17695,10 @@
       <c r="E572" s="2"/>
       <c r="F572" s="2"/>
       <c r="G572" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H572" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I572" s="1"/>
       <c r="J572" s="1"/>
@@ -17727,10 +17725,10 @@
       <c r="E573" s="2"/>
       <c r="F573" s="2"/>
       <c r="G573" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H573" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I573" s="1"/>
       <c r="J573" s="1"/>
@@ -17757,10 +17755,10 @@
       <c r="E574" s="2"/>
       <c r="F574" s="2"/>
       <c r="G574" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I574" s="1"/>
       <c r="J574" s="1"/>
@@ -17787,10 +17785,10 @@
       <c r="E575" s="1"/>
       <c r="F575" s="1"/>
       <c r="G575" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H575" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I575" s="1"/>
       <c r="J575" s="1"/>
@@ -17817,10 +17815,10 @@
       <c r="E576" s="1"/>
       <c r="F576" s="1"/>
       <c r="G576" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H576" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I576" s="1"/>
       <c r="J576" s="1"/>
@@ -17847,10 +17845,10 @@
       <c r="E577" s="2"/>
       <c r="F577" s="2"/>
       <c r="G577" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H577" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I577" s="1"/>
       <c r="J577" s="1"/>
@@ -17877,10 +17875,10 @@
       <c r="E578" s="2"/>
       <c r="F578" s="2"/>
       <c r="G578" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H578" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I578" s="1"/>
       <c r="J578" s="1"/>
@@ -17907,10 +17905,10 @@
       <c r="E579" s="2"/>
       <c r="F579" s="2"/>
       <c r="G579" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H579" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I579" s="1"/>
       <c r="J579" s="1"/>
@@ -17937,10 +17935,10 @@
       <c r="E580" s="1"/>
       <c r="F580" s="1"/>
       <c r="G580" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H580" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I580" s="1"/>
       <c r="J580" s="1"/>
@@ -17967,10 +17965,10 @@
       <c r="E581" s="1"/>
       <c r="F581" s="1"/>
       <c r="G581" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H581" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I581" s="1"/>
       <c r="J581" s="1"/>
@@ -17997,7 +17995,7 @@
       <c r="E582" s="2"/>
       <c r="F582" s="2"/>
       <c r="G582" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H582" s="1"/>
       <c r="I582" s="1"/>
@@ -18025,7 +18023,7 @@
       <c r="E583" s="2"/>
       <c r="F583" s="2"/>
       <c r="G583" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H583" s="1"/>
       <c r="I583" s="1"/>
@@ -18053,7 +18051,7 @@
       <c r="E584" s="2"/>
       <c r="F584" s="2"/>
       <c r="G584" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H584" s="1"/>
       <c r="I584" s="1"/>
@@ -18081,7 +18079,7 @@
       <c r="E585" s="2"/>
       <c r="F585" s="2"/>
       <c r="G585" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H585" s="1"/>
       <c r="I585" s="1"/>
@@ -18109,7 +18107,7 @@
       <c r="E586" s="2"/>
       <c r="F586" s="2"/>
       <c r="G586" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H586" s="1"/>
       <c r="I586" s="1"/>
@@ -18137,7 +18135,7 @@
       <c r="E587" s="2"/>
       <c r="F587" s="2"/>
       <c r="G587" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H587" s="1"/>
       <c r="I587" s="1"/>
@@ -18165,7 +18163,7 @@
       <c r="E588" s="2"/>
       <c r="F588" s="2"/>
       <c r="G588" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H588" s="1"/>
       <c r="I588" s="1"/>
@@ -18193,7 +18191,7 @@
       <c r="E589" s="2"/>
       <c r="F589" s="2"/>
       <c r="G589" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H589" s="1"/>
       <c r="I589" s="1"/>
@@ -18221,7 +18219,7 @@
       <c r="E590" s="2"/>
       <c r="F590" s="2"/>
       <c r="G590" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H590" s="1"/>
       <c r="I590" s="1"/>
@@ -18249,7 +18247,7 @@
       <c r="E591" s="2"/>
       <c r="F591" s="2"/>
       <c r="G591" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H591" s="1"/>
       <c r="I591" s="1"/>
@@ -18277,7 +18275,7 @@
       <c r="E592" s="2"/>
       <c r="F592" s="2"/>
       <c r="G592" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H592" s="1"/>
       <c r="I592" s="1"/>

--- a/awim/cal template.xlsx
+++ b/awim/cal template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/640dce341da437cb/02 Time v3 physical Clock/Time v3 Clock camera and image processing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:40009_{B2970093-D86E-46D6-A84B-1B4BF93138CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2490F905-18C3-4BE1-9684-29AC6544A8B9}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:40009_{B2970093-D86E-46D6-A84B-1B4BF93138CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99F352DC-A87E-4789-9E7C-B7BF735873CD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="45">
   <si>
     <t>type</t>
   </si>
@@ -37,9 +37,6 @@
     <t>camera_name</t>
   </si>
   <si>
-    <t>sensor_dimensions</t>
-  </si>
-  <si>
     <t>lens_name</t>
   </si>
   <si>
@@ -47,9 +44,6 @@
   </si>
   <si>
     <t>settings_notes</t>
-  </si>
-  <si>
-    <t>cal_image_dimensions</t>
   </si>
   <si>
     <t>pixel_map_type</t>
@@ -158,6 +152,9 @@
   </si>
   <si>
     <t>y_rec</t>
+  </si>
+  <si>
+    <t>cam_image_dimensions</t>
   </si>
 </sst>
 </file>
@@ -1030,13 +1027,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P592"/>
+  <dimension ref="A1:P591"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="7.88671875" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -1045,22 +1042,22 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>0</v>
@@ -1075,22 +1072,22 @@
         <v>3</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -1118,12 +1115,12 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1178,12 +1175,12 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
       <c r="G6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1198,12 +1195,12 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="H7" s="2"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1221,7 +1218,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
@@ -1241,7 +1238,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
@@ -1261,7 +1258,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="1"/>
@@ -1274,16 +1271,30 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="A11" s="4">
+        <v>0</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>-1</v>
+      </c>
       <c r="G11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="2"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1306,16 +1317,12 @@
       <c r="D12" s="4">
         <v>0</v>
       </c>
-      <c r="E12" s="4">
-        <v>-1</v>
-      </c>
-      <c r="F12" s="4">
-        <v>-1</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="I12" s="1"/>
@@ -1340,12 +1347,12 @@
       <c r="D13" s="4">
         <v>0</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I13" s="1"/>
@@ -1373,10 +1380,10 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1403,10 +1410,10 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1433,10 +1440,10 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1463,10 +1470,10 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1490,13 +1497,13 @@
       <c r="D18" s="4">
         <v>0</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1523,10 +1530,10 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1548,15 +1555,15 @@
         <v>0</v>
       </c>
       <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
       <c r="G20" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1583,10 +1590,10 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1613,10 +1620,10 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1640,13 +1647,13 @@
       <c r="D23" s="4">
         <v>-20</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1673,10 +1680,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1695,18 +1702,18 @@
         <v>0</v>
       </c>
       <c r="C25" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D25" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
       <c r="G25" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1733,10 +1740,10 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -1763,10 +1770,10 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1790,13 +1797,13 @@
       <c r="D28" s="4">
         <v>0</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -1823,10 +1830,10 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1845,19 +1852,17 @@
         <v>0</v>
       </c>
       <c r="C30" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
       <c r="G30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -1878,12 +1883,12 @@
         <v>0</v>
       </c>
       <c r="D31" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1906,12 +1911,12 @@
         <v>0</v>
       </c>
       <c r="D32" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1931,15 +1936,15 @@
         <v>0</v>
       </c>
       <c r="C33" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D33" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1962,12 +1967,12 @@
         <v>-5</v>
       </c>
       <c r="D34" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1990,12 +1995,12 @@
         <v>-5</v>
       </c>
       <c r="D35" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2018,12 +2023,12 @@
         <v>-5</v>
       </c>
       <c r="D36" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2043,15 +2048,15 @@
         <v>0</v>
       </c>
       <c r="C37" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D37" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2074,12 +2079,12 @@
         <v>-10</v>
       </c>
       <c r="D38" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -2102,12 +2107,12 @@
         <v>-10</v>
       </c>
       <c r="D39" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -2130,12 +2135,12 @@
         <v>-10</v>
       </c>
       <c r="D40" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2152,20 +2157,22 @@
         <v>0</v>
       </c>
       <c r="B41" s="4">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="C41" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D41" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H41" s="1"/>
+      <c r="H41" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2188,12 +2195,12 @@
       <c r="D42" s="4">
         <v>0</v>
       </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="H42" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I42" s="1"/>
@@ -2221,10 +2228,10 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -2251,10 +2258,10 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -2281,10 +2288,10 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -2311,10 +2318,10 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -2338,13 +2345,13 @@
       <c r="D47" s="4">
         <v>0</v>
       </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
       <c r="G47" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -2371,10 +2378,10 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -2396,15 +2403,15 @@
         <v>0</v>
       </c>
       <c r="D49" s="4">
-        <v>0</v>
-      </c>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
       <c r="G49" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -2431,10 +2438,10 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -2461,10 +2468,10 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -2488,13 +2495,13 @@
       <c r="D52" s="4">
         <v>-20</v>
       </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
       <c r="G52" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -2521,10 +2528,10 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -2543,18 +2550,18 @@
         <v>-20</v>
       </c>
       <c r="C54" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D54" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
       <c r="G54" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -2581,10 +2588,10 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -2611,10 +2618,10 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -2638,13 +2645,13 @@
       <c r="D57" s="4">
         <v>0</v>
       </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
       <c r="G57" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -2671,10 +2678,10 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -2693,19 +2700,17 @@
         <v>-20</v>
       </c>
       <c r="C59" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D59" s="4">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
       <c r="G59" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -2726,12 +2731,12 @@
         <v>0</v>
       </c>
       <c r="D60" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -2754,12 +2759,12 @@
         <v>0</v>
       </c>
       <c r="D61" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -2779,15 +2784,15 @@
         <v>-20</v>
       </c>
       <c r="C62" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D62" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -2810,12 +2815,12 @@
         <v>-5</v>
       </c>
       <c r="D63" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -2838,12 +2843,12 @@
         <v>-5</v>
       </c>
       <c r="D64" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -2866,12 +2871,12 @@
         <v>-5</v>
       </c>
       <c r="D65" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -2891,15 +2896,15 @@
         <v>-20</v>
       </c>
       <c r="C66" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D66" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -2922,12 +2927,12 @@
         <v>-10</v>
       </c>
       <c r="D67" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -2950,12 +2955,12 @@
         <v>-10</v>
       </c>
       <c r="D68" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -2978,12 +2983,12 @@
         <v>-10</v>
       </c>
       <c r="D69" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -3000,20 +3005,22 @@
         <v>0</v>
       </c>
       <c r="B70" s="4">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="C70" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D70" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H70" s="1"/>
+      <c r="H70" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -3036,12 +3043,12 @@
       <c r="D71" s="4">
         <v>0</v>
       </c>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3" t="s">
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="H71" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I71" s="1"/>
@@ -3069,10 +3076,10 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -3099,10 +3106,10 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -3129,10 +3136,10 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -3159,10 +3166,10 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -3186,13 +3193,13 @@
       <c r="D76" s="4">
         <v>0</v>
       </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
       <c r="G76" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -3219,10 +3226,10 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -3244,15 +3251,15 @@
         <v>0</v>
       </c>
       <c r="D78" s="4">
-        <v>0</v>
-      </c>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
       <c r="G78" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -3279,10 +3286,10 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -3309,10 +3316,10 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -3336,13 +3343,13 @@
       <c r="D81" s="4">
         <v>-20</v>
       </c>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -3369,10 +3376,10 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -3391,18 +3398,18 @@
         <v>-40</v>
       </c>
       <c r="C83" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D83" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
       <c r="G83" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -3429,10 +3436,10 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -3459,10 +3466,10 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -3486,13 +3493,13 @@
       <c r="D86" s="4">
         <v>0</v>
       </c>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
       <c r="G86" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -3519,10 +3526,10 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -3541,19 +3548,17 @@
         <v>-40</v>
       </c>
       <c r="C88" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D88" s="4">
-        <v>0</v>
-      </c>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
       <c r="G88" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H88" s="1"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
@@ -3574,12 +3579,12 @@
         <v>0</v>
       </c>
       <c r="D89" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -3602,12 +3607,12 @@
         <v>0</v>
       </c>
       <c r="D90" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -3627,15 +3632,15 @@
         <v>-40</v>
       </c>
       <c r="C91" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D91" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -3658,12 +3663,12 @@
         <v>-5</v>
       </c>
       <c r="D92" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -3686,12 +3691,12 @@
         <v>-5</v>
       </c>
       <c r="D93" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -3714,12 +3719,12 @@
         <v>-5</v>
       </c>
       <c r="D94" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -3739,15 +3744,15 @@
         <v>-40</v>
       </c>
       <c r="C95" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D95" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -3770,12 +3775,12 @@
         <v>-10</v>
       </c>
       <c r="D96" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
@@ -3798,12 +3803,12 @@
         <v>-10</v>
       </c>
       <c r="D97" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
@@ -3826,12 +3831,12 @@
         <v>-10</v>
       </c>
       <c r="D98" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -3848,20 +3853,22 @@
         <v>0</v>
       </c>
       <c r="B99" s="4">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="C99" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D99" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H99" s="1"/>
+      <c r="H99" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
@@ -3884,12 +3891,12 @@
       <c r="D100" s="4">
         <v>0</v>
       </c>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="H100" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I100" s="1"/>
@@ -3917,10 +3924,10 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -3947,10 +3954,10 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -3977,10 +3984,10 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -4007,10 +4014,10 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -4034,13 +4041,13 @@
       <c r="D105" s="4">
         <v>0</v>
       </c>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
       <c r="G105" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -4067,10 +4074,10 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -4092,15 +4099,15 @@
         <v>0</v>
       </c>
       <c r="D107" s="4">
-        <v>0</v>
-      </c>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
       <c r="G107" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -4127,10 +4134,10 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -4157,10 +4164,10 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -4184,13 +4191,13 @@
       <c r="D110" s="4">
         <v>-20</v>
       </c>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
       <c r="G110" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -4217,10 +4224,10 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -4239,18 +4246,18 @@
         <v>-60</v>
       </c>
       <c r="C112" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D112" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
       <c r="G112" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -4277,10 +4284,10 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -4307,10 +4314,10 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -4334,13 +4341,13 @@
       <c r="D115" s="4">
         <v>0</v>
       </c>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
       <c r="G115" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -4367,10 +4374,10 @@
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -4389,19 +4396,17 @@
         <v>-60</v>
       </c>
       <c r="C117" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D117" s="4">
-        <v>0</v>
-      </c>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
       <c r="G117" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H117" s="1"/>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
       <c r="K117" s="1"/>
@@ -4422,12 +4427,12 @@
         <v>0</v>
       </c>
       <c r="D118" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -4450,12 +4455,12 @@
         <v>0</v>
       </c>
       <c r="D119" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -4475,15 +4480,15 @@
         <v>-60</v>
       </c>
       <c r="C120" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D120" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
@@ -4506,12 +4511,12 @@
         <v>-5</v>
       </c>
       <c r="D121" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
@@ -4534,12 +4539,12 @@
         <v>-5</v>
       </c>
       <c r="D122" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
@@ -4562,12 +4567,12 @@
         <v>-5</v>
       </c>
       <c r="D123" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
@@ -4587,15 +4592,15 @@
         <v>-60</v>
       </c>
       <c r="C124" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D124" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
@@ -4618,12 +4623,12 @@
         <v>-10</v>
       </c>
       <c r="D125" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
@@ -4646,12 +4651,12 @@
         <v>-10</v>
       </c>
       <c r="D126" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
@@ -4674,12 +4679,12 @@
         <v>-10</v>
       </c>
       <c r="D127" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -4696,20 +4701,22 @@
         <v>0</v>
       </c>
       <c r="B128" s="4">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="C128" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D128" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H128" s="1"/>
+      <c r="H128" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
@@ -4732,12 +4739,12 @@
       <c r="D129" s="4">
         <v>0</v>
       </c>
-      <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
-      <c r="G129" s="3" t="s">
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H129" s="3" t="s">
+      <c r="H129" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I129" s="1"/>
@@ -4765,10 +4772,10 @@
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H130" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
@@ -4795,10 +4802,10 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -4825,10 +4832,10 @@
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -4855,10 +4862,10 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -4882,13 +4889,13 @@
       <c r="D134" s="4">
         <v>0</v>
       </c>
-      <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
       <c r="G134" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
@@ -4915,10 +4922,10 @@
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -4940,15 +4947,15 @@
         <v>0</v>
       </c>
       <c r="D136" s="4">
-        <v>0</v>
-      </c>
-      <c r="E136" s="1"/>
-      <c r="F136" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
       <c r="G136" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
@@ -4975,10 +4982,10 @@
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -5005,10 +5012,10 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -5032,13 +5039,13 @@
       <c r="D139" s="4">
         <v>-20</v>
       </c>
-      <c r="E139" s="2"/>
-      <c r="F139" s="2"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1"/>
       <c r="G139" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -5065,10 +5072,10 @@
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -5087,18 +5094,18 @@
         <v>-80</v>
       </c>
       <c r="C141" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D141" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E141" s="1"/>
-      <c r="F141" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
       <c r="G141" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
@@ -5125,10 +5132,10 @@
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -5155,10 +5162,10 @@
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
@@ -5182,13 +5189,13 @@
       <c r="D144" s="4">
         <v>0</v>
       </c>
-      <c r="E144" s="2"/>
-      <c r="F144" s="2"/>
+      <c r="E144" s="1"/>
+      <c r="F144" s="1"/>
       <c r="G144" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
@@ -5215,10 +5222,10 @@
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
@@ -5237,19 +5244,17 @@
         <v>-80</v>
       </c>
       <c r="C146" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D146" s="4">
-        <v>0</v>
-      </c>
-      <c r="E146" s="1"/>
-      <c r="F146" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
       <c r="G146" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H146" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H146" s="1"/>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
       <c r="K146" s="1"/>
@@ -5270,12 +5275,12 @@
         <v>0</v>
       </c>
       <c r="D147" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
@@ -5298,12 +5303,12 @@
         <v>0</v>
       </c>
       <c r="D148" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
@@ -5323,15 +5328,15 @@
         <v>-80</v>
       </c>
       <c r="C149" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D149" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
@@ -5354,12 +5359,12 @@
         <v>-5</v>
       </c>
       <c r="D150" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
@@ -5382,12 +5387,12 @@
         <v>-5</v>
       </c>
       <c r="D151" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
@@ -5410,12 +5415,12 @@
         <v>-5</v>
       </c>
       <c r="D152" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
@@ -5435,15 +5440,15 @@
         <v>-80</v>
       </c>
       <c r="C153" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D153" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
@@ -5466,12 +5471,12 @@
         <v>-10</v>
       </c>
       <c r="D154" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
@@ -5494,12 +5499,12 @@
         <v>-10</v>
       </c>
       <c r="D155" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
@@ -5522,12 +5527,12 @@
         <v>-10</v>
       </c>
       <c r="D156" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
@@ -5541,23 +5546,25 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="B157" s="4">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="C157" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D157" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E157" s="2"/>
-      <c r="F157" s="2"/>
-      <c r="G157" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H157" s="1"/>
+      <c r="H157" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
       <c r="K157" s="1"/>
@@ -5580,12 +5587,12 @@
       <c r="D158" s="4">
         <v>0</v>
       </c>
-      <c r="E158" s="3"/>
-      <c r="F158" s="3"/>
-      <c r="G158" s="3" t="s">
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H158" s="3" t="s">
+      <c r="H158" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I158" s="1"/>
@@ -5613,10 +5620,10 @@
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H159" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H159" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
@@ -5643,10 +5650,10 @@
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
@@ -5673,10 +5680,10 @@
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
@@ -5703,10 +5710,10 @@
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
@@ -5730,13 +5737,13 @@
       <c r="D163" s="4">
         <v>0</v>
       </c>
-      <c r="E163" s="2"/>
-      <c r="F163" s="2"/>
+      <c r="E163" s="1"/>
+      <c r="F163" s="1"/>
       <c r="G163" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
@@ -5763,10 +5770,10 @@
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -5788,15 +5795,15 @@
         <v>0</v>
       </c>
       <c r="D165" s="4">
-        <v>0</v>
-      </c>
-      <c r="E165" s="1"/>
-      <c r="F165" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
       <c r="G165" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
@@ -5823,10 +5830,10 @@
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
@@ -5853,10 +5860,10 @@
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
@@ -5880,13 +5887,13 @@
       <c r="D168" s="4">
         <v>-20</v>
       </c>
-      <c r="E168" s="2"/>
-      <c r="F168" s="2"/>
+      <c r="E168" s="1"/>
+      <c r="F168" s="1"/>
       <c r="G168" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
@@ -5913,10 +5920,10 @@
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
@@ -5935,18 +5942,18 @@
         <v>0</v>
       </c>
       <c r="C170" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D170" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E170" s="1"/>
-      <c r="F170" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
       <c r="G170" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
@@ -5973,10 +5980,10 @@
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
@@ -6003,10 +6010,10 @@
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
@@ -6030,13 +6037,13 @@
       <c r="D173" s="4">
         <v>0</v>
       </c>
-      <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
+      <c r="E173" s="1"/>
+      <c r="F173" s="1"/>
       <c r="G173" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
@@ -6063,10 +6070,10 @@
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
@@ -6085,19 +6092,17 @@
         <v>0</v>
       </c>
       <c r="C175" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D175" s="4">
-        <v>0</v>
-      </c>
-      <c r="E175" s="1"/>
-      <c r="F175" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
       <c r="G175" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H175" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H175" s="1"/>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
@@ -6118,12 +6123,12 @@
         <v>0</v>
       </c>
       <c r="D176" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
@@ -6146,12 +6151,12 @@
         <v>0</v>
       </c>
       <c r="D177" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
@@ -6171,15 +6176,15 @@
         <v>0</v>
       </c>
       <c r="C178" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D178" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
@@ -6202,12 +6207,12 @@
         <v>-5</v>
       </c>
       <c r="D179" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
@@ -6230,12 +6235,12 @@
         <v>-5</v>
       </c>
       <c r="D180" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
@@ -6258,12 +6263,12 @@
         <v>-5</v>
       </c>
       <c r="D181" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
@@ -6283,15 +6288,15 @@
         <v>0</v>
       </c>
       <c r="C182" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D182" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
@@ -6314,12 +6319,12 @@
         <v>-10</v>
       </c>
       <c r="D183" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
@@ -6342,12 +6347,12 @@
         <v>-10</v>
       </c>
       <c r="D184" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
@@ -6370,12 +6375,12 @@
         <v>-10</v>
       </c>
       <c r="D185" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
@@ -6392,20 +6397,22 @@
         <v>-15</v>
       </c>
       <c r="B186" s="4">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="C186" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D186" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" s="2"/>
-      <c r="G186" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E186" s="3"/>
+      <c r="F186" s="3"/>
+      <c r="G186" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H186" s="1"/>
+      <c r="H186" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I186" s="1"/>
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
@@ -6428,12 +6435,12 @@
       <c r="D187" s="4">
         <v>0</v>
       </c>
-      <c r="E187" s="3"/>
-      <c r="F187" s="3"/>
-      <c r="G187" s="3" t="s">
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H187" s="3" t="s">
+      <c r="H187" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I187" s="1"/>
@@ -6461,10 +6468,10 @@
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H188" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H188" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
@@ -6491,10 +6498,10 @@
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
@@ -6521,10 +6528,10 @@
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
@@ -6551,10 +6558,10 @@
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I191" s="1"/>
       <c r="J191" s="1"/>
@@ -6578,13 +6585,13 @@
       <c r="D192" s="4">
         <v>0</v>
       </c>
-      <c r="E192" s="2"/>
-      <c r="F192" s="2"/>
+      <c r="E192" s="1"/>
+      <c r="F192" s="1"/>
       <c r="G192" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I192" s="1"/>
       <c r="J192" s="1"/>
@@ -6611,10 +6618,10 @@
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I193" s="1"/>
       <c r="J193" s="1"/>
@@ -6636,15 +6643,15 @@
         <v>0</v>
       </c>
       <c r="D194" s="4">
-        <v>0</v>
-      </c>
-      <c r="E194" s="1"/>
-      <c r="F194" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
       <c r="G194" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I194" s="1"/>
       <c r="J194" s="1"/>
@@ -6671,10 +6678,10 @@
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I195" s="1"/>
       <c r="J195" s="1"/>
@@ -6701,10 +6708,10 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I196" s="1"/>
       <c r="J196" s="1"/>
@@ -6728,13 +6735,13 @@
       <c r="D197" s="4">
         <v>-20</v>
       </c>
-      <c r="E197" s="2"/>
-      <c r="F197" s="2"/>
+      <c r="E197" s="1"/>
+      <c r="F197" s="1"/>
       <c r="G197" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I197" s="1"/>
       <c r="J197" s="1"/>
@@ -6761,10 +6768,10 @@
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I198" s="1"/>
       <c r="J198" s="1"/>
@@ -6783,18 +6790,18 @@
         <v>-20</v>
       </c>
       <c r="C199" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D199" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E199" s="1"/>
-      <c r="F199" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
       <c r="G199" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I199" s="1"/>
       <c r="J199" s="1"/>
@@ -6821,10 +6828,10 @@
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I200" s="1"/>
       <c r="J200" s="1"/>
@@ -6851,10 +6858,10 @@
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I201" s="1"/>
       <c r="J201" s="1"/>
@@ -6878,13 +6885,13 @@
       <c r="D202" s="4">
         <v>0</v>
       </c>
-      <c r="E202" s="2"/>
-      <c r="F202" s="2"/>
+      <c r="E202" s="1"/>
+      <c r="F202" s="1"/>
       <c r="G202" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I202" s="1"/>
       <c r="J202" s="1"/>
@@ -6911,10 +6918,10 @@
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I203" s="1"/>
       <c r="J203" s="1"/>
@@ -6933,19 +6940,17 @@
         <v>-20</v>
       </c>
       <c r="C204" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D204" s="4">
-        <v>0</v>
-      </c>
-      <c r="E204" s="1"/>
-      <c r="F204" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
       <c r="G204" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H204" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H204" s="1"/>
       <c r="I204" s="1"/>
       <c r="J204" s="1"/>
       <c r="K204" s="1"/>
@@ -6966,12 +6971,12 @@
         <v>0</v>
       </c>
       <c r="D205" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
       <c r="G205" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H205" s="1"/>
       <c r="I205" s="1"/>
@@ -6994,12 +6999,12 @@
         <v>0</v>
       </c>
       <c r="D206" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
       <c r="G206" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
@@ -7019,15 +7024,15 @@
         <v>-20</v>
       </c>
       <c r="C207" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D207" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
       <c r="G207" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H207" s="1"/>
       <c r="I207" s="1"/>
@@ -7050,12 +7055,12 @@
         <v>-5</v>
       </c>
       <c r="D208" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
       <c r="G208" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H208" s="1"/>
       <c r="I208" s="1"/>
@@ -7078,12 +7083,12 @@
         <v>-5</v>
       </c>
       <c r="D209" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
       <c r="G209" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H209" s="1"/>
       <c r="I209" s="1"/>
@@ -7106,12 +7111,12 @@
         <v>-5</v>
       </c>
       <c r="D210" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
       <c r="G210" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H210" s="1"/>
       <c r="I210" s="1"/>
@@ -7131,15 +7136,15 @@
         <v>-20</v>
       </c>
       <c r="C211" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D211" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
       <c r="G211" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H211" s="1"/>
       <c r="I211" s="1"/>
@@ -7162,12 +7167,12 @@
         <v>-10</v>
       </c>
       <c r="D212" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
       <c r="G212" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
@@ -7190,12 +7195,12 @@
         <v>-10</v>
       </c>
       <c r="D213" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
       <c r="G213" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H213" s="1"/>
       <c r="I213" s="1"/>
@@ -7218,12 +7223,12 @@
         <v>-10</v>
       </c>
       <c r="D214" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
       <c r="G214" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H214" s="1"/>
       <c r="I214" s="1"/>
@@ -7240,20 +7245,22 @@
         <v>-15</v>
       </c>
       <c r="B215" s="4">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="C215" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D215" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E215" s="2"/>
-      <c r="F215" s="2"/>
-      <c r="G215" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E215" s="3"/>
+      <c r="F215" s="3"/>
+      <c r="G215" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H215" s="1"/>
+      <c r="H215" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I215" s="1"/>
       <c r="J215" s="1"/>
       <c r="K215" s="1"/>
@@ -7276,12 +7283,12 @@
       <c r="D216" s="4">
         <v>0</v>
       </c>
-      <c r="E216" s="3"/>
-      <c r="F216" s="3"/>
-      <c r="G216" s="3" t="s">
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H216" s="3" t="s">
+      <c r="H216" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I216" s="1"/>
@@ -7309,10 +7316,10 @@
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
       <c r="G217" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H217" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H217" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I217" s="1"/>
       <c r="J217" s="1"/>
@@ -7339,10 +7346,10 @@
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
       <c r="G218" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I218" s="1"/>
       <c r="J218" s="1"/>
@@ -7369,10 +7376,10 @@
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
       <c r="G219" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I219" s="1"/>
       <c r="J219" s="1"/>
@@ -7399,10 +7406,10 @@
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
       <c r="G220" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I220" s="1"/>
       <c r="J220" s="1"/>
@@ -7426,13 +7433,13 @@
       <c r="D221" s="4">
         <v>0</v>
       </c>
-      <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
+      <c r="E221" s="1"/>
+      <c r="F221" s="1"/>
       <c r="G221" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I221" s="1"/>
       <c r="J221" s="1"/>
@@ -7459,10 +7466,10 @@
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I222" s="1"/>
       <c r="J222" s="1"/>
@@ -7484,15 +7491,15 @@
         <v>0</v>
       </c>
       <c r="D223" s="4">
-        <v>0</v>
-      </c>
-      <c r="E223" s="1"/>
-      <c r="F223" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
       <c r="G223" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I223" s="1"/>
       <c r="J223" s="1"/>
@@ -7519,10 +7526,10 @@
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I224" s="1"/>
       <c r="J224" s="1"/>
@@ -7549,10 +7556,10 @@
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I225" s="1"/>
       <c r="J225" s="1"/>
@@ -7576,13 +7583,13 @@
       <c r="D226" s="4">
         <v>-20</v>
       </c>
-      <c r="E226" s="2"/>
-      <c r="F226" s="2"/>
+      <c r="E226" s="1"/>
+      <c r="F226" s="1"/>
       <c r="G226" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I226" s="1"/>
       <c r="J226" s="1"/>
@@ -7609,10 +7616,10 @@
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I227" s="1"/>
       <c r="J227" s="1"/>
@@ -7631,18 +7638,18 @@
         <v>-40</v>
       </c>
       <c r="C228" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D228" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E228" s="1"/>
-      <c r="F228" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E228" s="2"/>
+      <c r="F228" s="2"/>
       <c r="G228" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I228" s="1"/>
       <c r="J228" s="1"/>
@@ -7669,10 +7676,10 @@
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I229" s="1"/>
       <c r="J229" s="1"/>
@@ -7699,10 +7706,10 @@
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I230" s="1"/>
       <c r="J230" s="1"/>
@@ -7726,13 +7733,13 @@
       <c r="D231" s="4">
         <v>0</v>
       </c>
-      <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
+      <c r="E231" s="1"/>
+      <c r="F231" s="1"/>
       <c r="G231" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I231" s="1"/>
       <c r="J231" s="1"/>
@@ -7759,10 +7766,10 @@
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I232" s="1"/>
       <c r="J232" s="1"/>
@@ -7781,19 +7788,17 @@
         <v>-40</v>
       </c>
       <c r="C233" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D233" s="4">
-        <v>0</v>
-      </c>
-      <c r="E233" s="1"/>
-      <c r="F233" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E233" s="2"/>
+      <c r="F233" s="2"/>
       <c r="G233" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H233" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H233" s="1"/>
       <c r="I233" s="1"/>
       <c r="J233" s="1"/>
       <c r="K233" s="1"/>
@@ -7814,12 +7819,12 @@
         <v>0</v>
       </c>
       <c r="D234" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
       <c r="G234" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
@@ -7842,12 +7847,12 @@
         <v>0</v>
       </c>
       <c r="D235" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
@@ -7867,15 +7872,15 @@
         <v>-40</v>
       </c>
       <c r="C236" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D236" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
@@ -7898,12 +7903,12 @@
         <v>-5</v>
       </c>
       <c r="D237" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
       <c r="G237" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
@@ -7926,12 +7931,12 @@
         <v>-5</v>
       </c>
       <c r="D238" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
       <c r="G238" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H238" s="1"/>
       <c r="I238" s="1"/>
@@ -7954,12 +7959,12 @@
         <v>-5</v>
       </c>
       <c r="D239" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
@@ -7979,15 +7984,15 @@
         <v>-40</v>
       </c>
       <c r="C240" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D240" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
@@ -8010,12 +8015,12 @@
         <v>-10</v>
       </c>
       <c r="D241" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
       <c r="G241" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
@@ -8038,12 +8043,12 @@
         <v>-10</v>
       </c>
       <c r="D242" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
@@ -8066,12 +8071,12 @@
         <v>-10</v>
       </c>
       <c r="D243" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
@@ -8088,20 +8093,22 @@
         <v>-15</v>
       </c>
       <c r="B244" s="4">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="C244" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D244" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
-      <c r="G244" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E244" s="3"/>
+      <c r="F244" s="3"/>
+      <c r="G244" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H244" s="1"/>
+      <c r="H244" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I244" s="1"/>
       <c r="J244" s="1"/>
       <c r="K244" s="1"/>
@@ -8124,12 +8131,12 @@
       <c r="D245" s="4">
         <v>0</v>
       </c>
-      <c r="E245" s="3"/>
-      <c r="F245" s="3"/>
-      <c r="G245" s="3" t="s">
+      <c r="E245" s="2"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H245" s="3" t="s">
+      <c r="H245" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I245" s="1"/>
@@ -8157,10 +8164,10 @@
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H246" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H246" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I246" s="1"/>
       <c r="J246" s="1"/>
@@ -8187,10 +8194,10 @@
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I247" s="1"/>
       <c r="J247" s="1"/>
@@ -8217,10 +8224,10 @@
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I248" s="1"/>
       <c r="J248" s="1"/>
@@ -8247,10 +8254,10 @@
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
       <c r="G249" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I249" s="1"/>
       <c r="J249" s="1"/>
@@ -8274,13 +8281,13 @@
       <c r="D250" s="4">
         <v>0</v>
       </c>
-      <c r="E250" s="2"/>
-      <c r="F250" s="2"/>
+      <c r="E250" s="1"/>
+      <c r="F250" s="1"/>
       <c r="G250" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
@@ -8307,10 +8314,10 @@
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I251" s="1"/>
       <c r="J251" s="1"/>
@@ -8332,15 +8339,15 @@
         <v>0</v>
       </c>
       <c r="D252" s="4">
-        <v>0</v>
-      </c>
-      <c r="E252" s="1"/>
-      <c r="F252" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
       <c r="G252" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I252" s="1"/>
       <c r="J252" s="1"/>
@@ -8367,10 +8374,10 @@
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
       <c r="G253" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I253" s="1"/>
       <c r="J253" s="1"/>
@@ -8397,10 +8404,10 @@
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
       <c r="G254" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
@@ -8424,13 +8431,13 @@
       <c r="D255" s="4">
         <v>-20</v>
       </c>
-      <c r="E255" s="2"/>
-      <c r="F255" s="2"/>
+      <c r="E255" s="1"/>
+      <c r="F255" s="1"/>
       <c r="G255" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I255" s="1"/>
       <c r="J255" s="1"/>
@@ -8457,10 +8464,10 @@
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I256" s="1"/>
       <c r="J256" s="1"/>
@@ -8479,18 +8486,18 @@
         <v>-60</v>
       </c>
       <c r="C257" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D257" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E257" s="1"/>
-      <c r="F257" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E257" s="2"/>
+      <c r="F257" s="2"/>
       <c r="G257" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I257" s="1"/>
       <c r="J257" s="1"/>
@@ -8517,10 +8524,10 @@
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
       <c r="G258" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
@@ -8547,10 +8554,10 @@
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
       <c r="G259" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I259" s="1"/>
       <c r="J259" s="1"/>
@@ -8574,13 +8581,13 @@
       <c r="D260" s="4">
         <v>0</v>
       </c>
-      <c r="E260" s="2"/>
-      <c r="F260" s="2"/>
+      <c r="E260" s="1"/>
+      <c r="F260" s="1"/>
       <c r="G260" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
@@ -8607,10 +8614,10 @@
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
@@ -8629,19 +8636,17 @@
         <v>-60</v>
       </c>
       <c r="C262" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D262" s="4">
-        <v>0</v>
-      </c>
-      <c r="E262" s="1"/>
-      <c r="F262" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E262" s="2"/>
+      <c r="F262" s="2"/>
       <c r="G262" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H262" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H262" s="1"/>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
       <c r="K262" s="1"/>
@@ -8662,12 +8667,12 @@
         <v>0</v>
       </c>
       <c r="D263" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
       <c r="G263" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
@@ -8690,12 +8695,12 @@
         <v>0</v>
       </c>
       <c r="D264" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
       <c r="G264" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
@@ -8715,15 +8720,15 @@
         <v>-60</v>
       </c>
       <c r="C265" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D265" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
@@ -8746,12 +8751,12 @@
         <v>-5</v>
       </c>
       <c r="D266" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
       <c r="G266" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
@@ -8774,12 +8779,12 @@
         <v>-5</v>
       </c>
       <c r="D267" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
       <c r="G267" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H267" s="1"/>
       <c r="I267" s="1"/>
@@ -8802,12 +8807,12 @@
         <v>-5</v>
       </c>
       <c r="D268" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
       <c r="G268" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H268" s="1"/>
       <c r="I268" s="1"/>
@@ -8827,15 +8832,15 @@
         <v>-60</v>
       </c>
       <c r="C269" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D269" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
       <c r="G269" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H269" s="1"/>
       <c r="I269" s="1"/>
@@ -8858,12 +8863,12 @@
         <v>-10</v>
       </c>
       <c r="D270" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
       <c r="G270" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H270" s="1"/>
       <c r="I270" s="1"/>
@@ -8886,12 +8891,12 @@
         <v>-10</v>
       </c>
       <c r="D271" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
       <c r="G271" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H271" s="1"/>
       <c r="I271" s="1"/>
@@ -8914,12 +8919,12 @@
         <v>-10</v>
       </c>
       <c r="D272" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
       <c r="G272" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
@@ -8936,20 +8941,22 @@
         <v>-15</v>
       </c>
       <c r="B273" s="4">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="C273" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D273" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E273" s="2"/>
-      <c r="F273" s="2"/>
-      <c r="G273" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E273" s="3"/>
+      <c r="F273" s="3"/>
+      <c r="G273" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H273" s="1"/>
+      <c r="H273" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I273" s="1"/>
       <c r="J273" s="1"/>
       <c r="K273" s="1"/>
@@ -8972,12 +8979,12 @@
       <c r="D274" s="4">
         <v>0</v>
       </c>
-      <c r="E274" s="3"/>
-      <c r="F274" s="3"/>
-      <c r="G274" s="3" t="s">
+      <c r="E274" s="2"/>
+      <c r="F274" s="2"/>
+      <c r="G274" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H274" s="3" t="s">
+      <c r="H274" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I274" s="1"/>
@@ -9005,10 +9012,10 @@
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
       <c r="G275" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H275" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H275" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I275" s="1"/>
       <c r="J275" s="1"/>
@@ -9035,10 +9042,10 @@
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
       <c r="G276" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I276" s="1"/>
       <c r="J276" s="1"/>
@@ -9065,10 +9072,10 @@
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
       <c r="G277" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I277" s="1"/>
       <c r="J277" s="1"/>
@@ -9095,10 +9102,10 @@
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
       <c r="G278" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I278" s="1"/>
       <c r="J278" s="1"/>
@@ -9122,13 +9129,13 @@
       <c r="D279" s="4">
         <v>0</v>
       </c>
-      <c r="E279" s="2"/>
-      <c r="F279" s="2"/>
+      <c r="E279" s="1"/>
+      <c r="F279" s="1"/>
       <c r="G279" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I279" s="1"/>
       <c r="J279" s="1"/>
@@ -9155,10 +9162,10 @@
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I280" s="1"/>
       <c r="J280" s="1"/>
@@ -9180,15 +9187,15 @@
         <v>0</v>
       </c>
       <c r="D281" s="4">
-        <v>0</v>
-      </c>
-      <c r="E281" s="1"/>
-      <c r="F281" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E281" s="2"/>
+      <c r="F281" s="2"/>
       <c r="G281" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I281" s="1"/>
       <c r="J281" s="1"/>
@@ -9215,10 +9222,10 @@
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
       <c r="G282" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I282" s="1"/>
       <c r="J282" s="1"/>
@@ -9245,10 +9252,10 @@
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
       <c r="G283" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I283" s="1"/>
       <c r="J283" s="1"/>
@@ -9272,13 +9279,13 @@
       <c r="D284" s="4">
         <v>-20</v>
       </c>
-      <c r="E284" s="2"/>
-      <c r="F284" s="2"/>
+      <c r="E284" s="1"/>
+      <c r="F284" s="1"/>
       <c r="G284" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I284" s="1"/>
       <c r="J284" s="1"/>
@@ -9305,10 +9312,10 @@
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I285" s="1"/>
       <c r="J285" s="1"/>
@@ -9327,18 +9334,18 @@
         <v>-80</v>
       </c>
       <c r="C286" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D286" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E286" s="1"/>
-      <c r="F286" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E286" s="2"/>
+      <c r="F286" s="2"/>
       <c r="G286" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
@@ -9365,10 +9372,10 @@
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
       <c r="G287" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
@@ -9395,10 +9402,10 @@
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
       <c r="G288" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I288" s="1"/>
       <c r="J288" s="1"/>
@@ -9422,13 +9429,13 @@
       <c r="D289" s="4">
         <v>0</v>
       </c>
-      <c r="E289" s="2"/>
-      <c r="F289" s="2"/>
+      <c r="E289" s="1"/>
+      <c r="F289" s="1"/>
       <c r="G289" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I289" s="1"/>
       <c r="J289" s="1"/>
@@ -9455,10 +9462,10 @@
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I290" s="1"/>
       <c r="J290" s="1"/>
@@ -9477,19 +9484,17 @@
         <v>-80</v>
       </c>
       <c r="C291" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D291" s="4">
-        <v>0</v>
-      </c>
-      <c r="E291" s="1"/>
-      <c r="F291" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E291" s="2"/>
+      <c r="F291" s="2"/>
       <c r="G291" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H291" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H291" s="1"/>
       <c r="I291" s="1"/>
       <c r="J291" s="1"/>
       <c r="K291" s="1"/>
@@ -9510,12 +9515,12 @@
         <v>0</v>
       </c>
       <c r="D292" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
       <c r="G292" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H292" s="1"/>
       <c r="I292" s="1"/>
@@ -9538,12 +9543,12 @@
         <v>0</v>
       </c>
       <c r="D293" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
       <c r="G293" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H293" s="1"/>
       <c r="I293" s="1"/>
@@ -9563,15 +9568,15 @@
         <v>-80</v>
       </c>
       <c r="C294" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D294" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
       <c r="G294" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H294" s="1"/>
       <c r="I294" s="1"/>
@@ -9594,12 +9599,12 @@
         <v>-5</v>
       </c>
       <c r="D295" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
       <c r="G295" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H295" s="1"/>
       <c r="I295" s="1"/>
@@ -9622,12 +9627,12 @@
         <v>-5</v>
       </c>
       <c r="D296" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
       <c r="G296" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H296" s="1"/>
       <c r="I296" s="1"/>
@@ -9650,12 +9655,12 @@
         <v>-5</v>
       </c>
       <c r="D297" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
       <c r="G297" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H297" s="1"/>
       <c r="I297" s="1"/>
@@ -9675,15 +9680,15 @@
         <v>-80</v>
       </c>
       <c r="C298" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D298" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
       <c r="G298" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H298" s="1"/>
       <c r="I298" s="1"/>
@@ -9706,12 +9711,12 @@
         <v>-10</v>
       </c>
       <c r="D299" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
       <c r="G299" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H299" s="1"/>
       <c r="I299" s="1"/>
@@ -9734,12 +9739,12 @@
         <v>-10</v>
       </c>
       <c r="D300" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
       <c r="G300" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
@@ -9762,12 +9767,12 @@
         <v>-10</v>
       </c>
       <c r="D301" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
       <c r="G301" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H301" s="1"/>
       <c r="I301" s="1"/>
@@ -9781,23 +9786,25 @@
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="B302" s="4">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="C302" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D302" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E302" s="2"/>
-      <c r="F302" s="2"/>
-      <c r="G302" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E302" s="3"/>
+      <c r="F302" s="3"/>
+      <c r="G302" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H302" s="1"/>
+      <c r="H302" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I302" s="1"/>
       <c r="J302" s="1"/>
       <c r="K302" s="1"/>
@@ -9820,12 +9827,12 @@
       <c r="D303" s="4">
         <v>0</v>
       </c>
-      <c r="E303" s="3"/>
-      <c r="F303" s="3"/>
-      <c r="G303" s="3" t="s">
+      <c r="E303" s="2"/>
+      <c r="F303" s="2"/>
+      <c r="G303" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H303" s="3" t="s">
+      <c r="H303" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I303" s="1"/>
@@ -9853,10 +9860,10 @@
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
       <c r="G304" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H304" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H304" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I304" s="1"/>
       <c r="J304" s="1"/>
@@ -9883,10 +9890,10 @@
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
       <c r="G305" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I305" s="1"/>
       <c r="J305" s="1"/>
@@ -9913,10 +9920,10 @@
       <c r="E306" s="2"/>
       <c r="F306" s="2"/>
       <c r="G306" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
@@ -9943,10 +9950,10 @@
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
       <c r="G307" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I307" s="1"/>
       <c r="J307" s="1"/>
@@ -9970,13 +9977,13 @@
       <c r="D308" s="4">
         <v>0</v>
       </c>
-      <c r="E308" s="2"/>
-      <c r="F308" s="2"/>
+      <c r="E308" s="1"/>
+      <c r="F308" s="1"/>
       <c r="G308" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
@@ -10003,10 +10010,10 @@
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I309" s="1"/>
       <c r="J309" s="1"/>
@@ -10028,15 +10035,15 @@
         <v>0</v>
       </c>
       <c r="D310" s="4">
-        <v>0</v>
-      </c>
-      <c r="E310" s="1"/>
-      <c r="F310" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E310" s="2"/>
+      <c r="F310" s="2"/>
       <c r="G310" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H310" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I310" s="1"/>
       <c r="J310" s="1"/>
@@ -10063,10 +10070,10 @@
       <c r="E311" s="2"/>
       <c r="F311" s="2"/>
       <c r="G311" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I311" s="1"/>
       <c r="J311" s="1"/>
@@ -10093,10 +10100,10 @@
       <c r="E312" s="2"/>
       <c r="F312" s="2"/>
       <c r="G312" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I312" s="1"/>
       <c r="J312" s="1"/>
@@ -10120,13 +10127,13 @@
       <c r="D313" s="4">
         <v>-20</v>
       </c>
-      <c r="E313" s="2"/>
-      <c r="F313" s="2"/>
+      <c r="E313" s="1"/>
+      <c r="F313" s="1"/>
       <c r="G313" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
@@ -10153,10 +10160,10 @@
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I314" s="1"/>
       <c r="J314" s="1"/>
@@ -10175,18 +10182,18 @@
         <v>0</v>
       </c>
       <c r="C315" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D315" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E315" s="1"/>
-      <c r="F315" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E315" s="2"/>
+      <c r="F315" s="2"/>
       <c r="G315" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I315" s="1"/>
       <c r="J315" s="1"/>
@@ -10213,10 +10220,10 @@
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
       <c r="G316" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I316" s="1"/>
       <c r="J316" s="1"/>
@@ -10243,10 +10250,10 @@
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
       <c r="G317" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I317" s="1"/>
       <c r="J317" s="1"/>
@@ -10270,13 +10277,13 @@
       <c r="D318" s="4">
         <v>0</v>
       </c>
-      <c r="E318" s="2"/>
-      <c r="F318" s="2"/>
+      <c r="E318" s="1"/>
+      <c r="F318" s="1"/>
       <c r="G318" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I318" s="1"/>
       <c r="J318" s="1"/>
@@ -10303,10 +10310,10 @@
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I319" s="1"/>
       <c r="J319" s="1"/>
@@ -10325,19 +10332,17 @@
         <v>0</v>
       </c>
       <c r="C320" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D320" s="4">
-        <v>0</v>
-      </c>
-      <c r="E320" s="1"/>
-      <c r="F320" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E320" s="2"/>
+      <c r="F320" s="2"/>
       <c r="G320" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H320" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H320" s="1"/>
       <c r="I320" s="1"/>
       <c r="J320" s="1"/>
       <c r="K320" s="1"/>
@@ -10358,12 +10363,12 @@
         <v>0</v>
       </c>
       <c r="D321" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
       <c r="G321" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H321" s="1"/>
       <c r="I321" s="1"/>
@@ -10386,12 +10391,12 @@
         <v>0</v>
       </c>
       <c r="D322" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E322" s="2"/>
       <c r="F322" s="2"/>
       <c r="G322" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H322" s="1"/>
       <c r="I322" s="1"/>
@@ -10411,15 +10416,15 @@
         <v>0</v>
       </c>
       <c r="C323" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D323" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E323" s="2"/>
       <c r="F323" s="2"/>
       <c r="G323" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H323" s="1"/>
       <c r="I323" s="1"/>
@@ -10442,12 +10447,12 @@
         <v>-5</v>
       </c>
       <c r="D324" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
       <c r="G324" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H324" s="1"/>
       <c r="I324" s="1"/>
@@ -10470,12 +10475,12 @@
         <v>-5</v>
       </c>
       <c r="D325" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
       <c r="G325" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H325" s="1"/>
       <c r="I325" s="1"/>
@@ -10498,12 +10503,12 @@
         <v>-5</v>
       </c>
       <c r="D326" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
       <c r="G326" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H326" s="1"/>
       <c r="I326" s="1"/>
@@ -10523,15 +10528,15 @@
         <v>0</v>
       </c>
       <c r="C327" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D327" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
       <c r="G327" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H327" s="1"/>
       <c r="I327" s="1"/>
@@ -10554,12 +10559,12 @@
         <v>-10</v>
       </c>
       <c r="D328" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
       <c r="G328" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H328" s="1"/>
       <c r="I328" s="1"/>
@@ -10582,12 +10587,12 @@
         <v>-10</v>
       </c>
       <c r="D329" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
       <c r="G329" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H329" s="1"/>
       <c r="I329" s="1"/>
@@ -10610,12 +10615,12 @@
         <v>-10</v>
       </c>
       <c r="D330" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
       <c r="G330" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H330" s="1"/>
       <c r="I330" s="1"/>
@@ -10632,20 +10637,22 @@
         <v>-30</v>
       </c>
       <c r="B331" s="4">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="C331" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D331" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E331" s="2"/>
-      <c r="F331" s="2"/>
-      <c r="G331" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E331" s="3"/>
+      <c r="F331" s="3"/>
+      <c r="G331" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H331" s="1"/>
+      <c r="H331" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I331" s="1"/>
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
@@ -10668,12 +10675,12 @@
       <c r="D332" s="4">
         <v>0</v>
       </c>
-      <c r="E332" s="3"/>
-      <c r="F332" s="3"/>
-      <c r="G332" s="3" t="s">
+      <c r="E332" s="2"/>
+      <c r="F332" s="2"/>
+      <c r="G332" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H332" s="3" t="s">
+      <c r="H332" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I332" s="1"/>
@@ -10701,10 +10708,10 @@
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
       <c r="G333" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H333" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H333" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I333" s="1"/>
       <c r="J333" s="1"/>
@@ -10731,10 +10738,10 @@
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
       <c r="G334" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I334" s="1"/>
       <c r="J334" s="1"/>
@@ -10761,10 +10768,10 @@
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
       <c r="G335" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I335" s="1"/>
       <c r="J335" s="1"/>
@@ -10791,10 +10798,10 @@
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
       <c r="G336" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I336" s="1"/>
       <c r="J336" s="1"/>
@@ -10818,13 +10825,13 @@
       <c r="D337" s="4">
         <v>0</v>
       </c>
-      <c r="E337" s="2"/>
-      <c r="F337" s="2"/>
+      <c r="E337" s="1"/>
+      <c r="F337" s="1"/>
       <c r="G337" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
@@ -10851,10 +10858,10 @@
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I338" s="1"/>
       <c r="J338" s="1"/>
@@ -10876,15 +10883,15 @@
         <v>0</v>
       </c>
       <c r="D339" s="4">
-        <v>0</v>
-      </c>
-      <c r="E339" s="1"/>
-      <c r="F339" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E339" s="2"/>
+      <c r="F339" s="2"/>
       <c r="G339" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I339" s="1"/>
       <c r="J339" s="1"/>
@@ -10911,10 +10918,10 @@
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
       <c r="G340" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I340" s="1"/>
       <c r="J340" s="1"/>
@@ -10941,10 +10948,10 @@
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
       <c r="G341" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
@@ -10968,13 +10975,13 @@
       <c r="D342" s="4">
         <v>-20</v>
       </c>
-      <c r="E342" s="2"/>
-      <c r="F342" s="2"/>
+      <c r="E342" s="1"/>
+      <c r="F342" s="1"/>
       <c r="G342" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I342" s="1"/>
       <c r="J342" s="1"/>
@@ -11001,10 +11008,10 @@
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I343" s="1"/>
       <c r="J343" s="1"/>
@@ -11023,18 +11030,18 @@
         <v>-20</v>
       </c>
       <c r="C344" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D344" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E344" s="1"/>
-      <c r="F344" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E344" s="2"/>
+      <c r="F344" s="2"/>
       <c r="G344" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I344" s="1"/>
       <c r="J344" s="1"/>
@@ -11061,10 +11068,10 @@
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
       <c r="G345" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I345" s="1"/>
       <c r="J345" s="1"/>
@@ -11091,10 +11098,10 @@
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
       <c r="G346" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I346" s="1"/>
       <c r="J346" s="1"/>
@@ -11118,13 +11125,13 @@
       <c r="D347" s="4">
         <v>0</v>
       </c>
-      <c r="E347" s="2"/>
-      <c r="F347" s="2"/>
+      <c r="E347" s="1"/>
+      <c r="F347" s="1"/>
       <c r="G347" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I347" s="1"/>
       <c r="J347" s="1"/>
@@ -11151,10 +11158,10 @@
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
@@ -11173,19 +11180,17 @@
         <v>-20</v>
       </c>
       <c r="C349" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D349" s="4">
-        <v>0</v>
-      </c>
-      <c r="E349" s="1"/>
-      <c r="F349" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E349" s="2"/>
+      <c r="F349" s="2"/>
       <c r="G349" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H349" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H349" s="1"/>
       <c r="I349" s="1"/>
       <c r="J349" s="1"/>
       <c r="K349" s="1"/>
@@ -11206,12 +11211,12 @@
         <v>0</v>
       </c>
       <c r="D350" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
       <c r="G350" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H350" s="1"/>
       <c r="I350" s="1"/>
@@ -11234,12 +11239,12 @@
         <v>0</v>
       </c>
       <c r="D351" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
       <c r="G351" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H351" s="1"/>
       <c r="I351" s="1"/>
@@ -11259,15 +11264,15 @@
         <v>-20</v>
       </c>
       <c r="C352" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D352" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
       <c r="G352" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H352" s="1"/>
       <c r="I352" s="1"/>
@@ -11290,12 +11295,12 @@
         <v>-5</v>
       </c>
       <c r="D353" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
       <c r="G353" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H353" s="1"/>
       <c r="I353" s="1"/>
@@ -11318,12 +11323,12 @@
         <v>-5</v>
       </c>
       <c r="D354" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
       <c r="G354" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
@@ -11346,12 +11351,12 @@
         <v>-5</v>
       </c>
       <c r="D355" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
       <c r="G355" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
@@ -11371,15 +11376,15 @@
         <v>-20</v>
       </c>
       <c r="C356" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D356" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
       <c r="G356" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H356" s="1"/>
       <c r="I356" s="1"/>
@@ -11402,12 +11407,12 @@
         <v>-10</v>
       </c>
       <c r="D357" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
       <c r="G357" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H357" s="1"/>
       <c r="I357" s="1"/>
@@ -11430,12 +11435,12 @@
         <v>-10</v>
       </c>
       <c r="D358" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
       <c r="G358" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H358" s="1"/>
       <c r="I358" s="1"/>
@@ -11458,12 +11463,12 @@
         <v>-10</v>
       </c>
       <c r="D359" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
       <c r="G359" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H359" s="1"/>
       <c r="I359" s="1"/>
@@ -11480,20 +11485,22 @@
         <v>-30</v>
       </c>
       <c r="B360" s="4">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="C360" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D360" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E360" s="2"/>
-      <c r="F360" s="2"/>
-      <c r="G360" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E360" s="3"/>
+      <c r="F360" s="3"/>
+      <c r="G360" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H360" s="1"/>
+      <c r="H360" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I360" s="1"/>
       <c r="J360" s="1"/>
       <c r="K360" s="1"/>
@@ -11516,12 +11523,12 @@
       <c r="D361" s="4">
         <v>0</v>
       </c>
-      <c r="E361" s="3"/>
-      <c r="F361" s="3"/>
-      <c r="G361" s="3" t="s">
+      <c r="E361" s="2"/>
+      <c r="F361" s="2"/>
+      <c r="G361" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H361" s="3" t="s">
+      <c r="H361" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I361" s="1"/>
@@ -11549,10 +11556,10 @@
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
       <c r="G362" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H362" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H362" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
@@ -11579,10 +11586,10 @@
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
       <c r="G363" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I363" s="1"/>
       <c r="J363" s="1"/>
@@ -11609,10 +11616,10 @@
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
       <c r="G364" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H364" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I364" s="1"/>
       <c r="J364" s="1"/>
@@ -11639,10 +11646,10 @@
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
       <c r="G365" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H365" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I365" s="1"/>
       <c r="J365" s="1"/>
@@ -11666,13 +11673,13 @@
       <c r="D366" s="4">
         <v>0</v>
       </c>
-      <c r="E366" s="2"/>
-      <c r="F366" s="2"/>
+      <c r="E366" s="1"/>
+      <c r="F366" s="1"/>
       <c r="G366" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H366" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
@@ -11699,10 +11706,10 @@
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
       <c r="G367" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H367" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I367" s="1"/>
       <c r="J367" s="1"/>
@@ -11724,15 +11731,15 @@
         <v>0</v>
       </c>
       <c r="D368" s="4">
-        <v>0</v>
-      </c>
-      <c r="E368" s="1"/>
-      <c r="F368" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E368" s="2"/>
+      <c r="F368" s="2"/>
       <c r="G368" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H368" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
@@ -11759,10 +11766,10 @@
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
       <c r="G369" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H369" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I369" s="1"/>
       <c r="J369" s="1"/>
@@ -11789,10 +11796,10 @@
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
       <c r="G370" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H370" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
@@ -11816,13 +11823,13 @@
       <c r="D371" s="4">
         <v>-20</v>
       </c>
-      <c r="E371" s="2"/>
-      <c r="F371" s="2"/>
+      <c r="E371" s="1"/>
+      <c r="F371" s="1"/>
       <c r="G371" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H371" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
@@ -11849,10 +11856,10 @@
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
       <c r="G372" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H372" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
@@ -11871,18 +11878,18 @@
         <v>-40</v>
       </c>
       <c r="C373" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D373" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E373" s="1"/>
-      <c r="F373" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E373" s="2"/>
+      <c r="F373" s="2"/>
       <c r="G373" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
@@ -11909,10 +11916,10 @@
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
       <c r="G374" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I374" s="1"/>
       <c r="J374" s="1"/>
@@ -11939,10 +11946,10 @@
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
       <c r="G375" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I375" s="1"/>
       <c r="J375" s="1"/>
@@ -11966,13 +11973,13 @@
       <c r="D376" s="4">
         <v>0</v>
       </c>
-      <c r="E376" s="2"/>
-      <c r="F376" s="2"/>
+      <c r="E376" s="1"/>
+      <c r="F376" s="1"/>
       <c r="G376" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H376" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
@@ -11999,10 +12006,10 @@
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
       <c r="G377" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H377" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I377" s="1"/>
       <c r="J377" s="1"/>
@@ -12021,19 +12028,17 @@
         <v>-40</v>
       </c>
       <c r="C378" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D378" s="4">
-        <v>0</v>
-      </c>
-      <c r="E378" s="1"/>
-      <c r="F378" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E378" s="2"/>
+      <c r="F378" s="2"/>
       <c r="G378" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H378" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H378" s="1"/>
       <c r="I378" s="1"/>
       <c r="J378" s="1"/>
       <c r="K378" s="1"/>
@@ -12054,12 +12059,12 @@
         <v>0</v>
       </c>
       <c r="D379" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E379" s="2"/>
       <c r="F379" s="2"/>
       <c r="G379" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H379" s="1"/>
       <c r="I379" s="1"/>
@@ -12082,12 +12087,12 @@
         <v>0</v>
       </c>
       <c r="D380" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
       <c r="G380" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H380" s="1"/>
       <c r="I380" s="1"/>
@@ -12107,15 +12112,15 @@
         <v>-40</v>
       </c>
       <c r="C381" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D381" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E381" s="2"/>
       <c r="F381" s="2"/>
       <c r="G381" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H381" s="1"/>
       <c r="I381" s="1"/>
@@ -12138,12 +12143,12 @@
         <v>-5</v>
       </c>
       <c r="D382" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E382" s="2"/>
       <c r="F382" s="2"/>
       <c r="G382" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H382" s="1"/>
       <c r="I382" s="1"/>
@@ -12166,12 +12171,12 @@
         <v>-5</v>
       </c>
       <c r="D383" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E383" s="2"/>
       <c r="F383" s="2"/>
       <c r="G383" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H383" s="1"/>
       <c r="I383" s="1"/>
@@ -12194,12 +12199,12 @@
         <v>-5</v>
       </c>
       <c r="D384" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
       <c r="G384" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H384" s="1"/>
       <c r="I384" s="1"/>
@@ -12219,15 +12224,15 @@
         <v>-40</v>
       </c>
       <c r="C385" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D385" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E385" s="2"/>
       <c r="F385" s="2"/>
       <c r="G385" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H385" s="1"/>
       <c r="I385" s="1"/>
@@ -12250,12 +12255,12 @@
         <v>-10</v>
       </c>
       <c r="D386" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E386" s="2"/>
       <c r="F386" s="2"/>
       <c r="G386" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H386" s="1"/>
       <c r="I386" s="1"/>
@@ -12278,12 +12283,12 @@
         <v>-10</v>
       </c>
       <c r="D387" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E387" s="2"/>
       <c r="F387" s="2"/>
       <c r="G387" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H387" s="1"/>
       <c r="I387" s="1"/>
@@ -12306,12 +12311,12 @@
         <v>-10</v>
       </c>
       <c r="D388" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E388" s="2"/>
       <c r="F388" s="2"/>
       <c r="G388" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H388" s="1"/>
       <c r="I388" s="1"/>
@@ -12328,20 +12333,22 @@
         <v>-30</v>
       </c>
       <c r="B389" s="4">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="C389" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D389" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E389" s="2"/>
-      <c r="F389" s="2"/>
-      <c r="G389" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E389" s="3"/>
+      <c r="F389" s="3"/>
+      <c r="G389" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H389" s="1"/>
+      <c r="H389" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I389" s="1"/>
       <c r="J389" s="1"/>
       <c r="K389" s="1"/>
@@ -12364,12 +12371,12 @@
       <c r="D390" s="4">
         <v>0</v>
       </c>
-      <c r="E390" s="3"/>
-      <c r="F390" s="3"/>
-      <c r="G390" s="3" t="s">
+      <c r="E390" s="2"/>
+      <c r="F390" s="2"/>
+      <c r="G390" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H390" s="3" t="s">
+      <c r="H390" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I390" s="1"/>
@@ -12397,10 +12404,10 @@
       <c r="E391" s="2"/>
       <c r="F391" s="2"/>
       <c r="G391" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H391" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H391" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I391" s="1"/>
       <c r="J391" s="1"/>
@@ -12427,10 +12434,10 @@
       <c r="E392" s="2"/>
       <c r="F392" s="2"/>
       <c r="G392" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H392" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I392" s="1"/>
       <c r="J392" s="1"/>
@@ -12457,10 +12464,10 @@
       <c r="E393" s="2"/>
       <c r="F393" s="2"/>
       <c r="G393" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I393" s="1"/>
       <c r="J393" s="1"/>
@@ -12487,10 +12494,10 @@
       <c r="E394" s="2"/>
       <c r="F394" s="2"/>
       <c r="G394" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H394" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I394" s="1"/>
       <c r="J394" s="1"/>
@@ -12514,13 +12521,13 @@
       <c r="D395" s="4">
         <v>0</v>
       </c>
-      <c r="E395" s="2"/>
-      <c r="F395" s="2"/>
+      <c r="E395" s="1"/>
+      <c r="F395" s="1"/>
       <c r="G395" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H395" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I395" s="1"/>
       <c r="J395" s="1"/>
@@ -12547,10 +12554,10 @@
       <c r="E396" s="1"/>
       <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H396" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I396" s="1"/>
       <c r="J396" s="1"/>
@@ -12572,15 +12579,15 @@
         <v>0</v>
       </c>
       <c r="D397" s="4">
-        <v>0</v>
-      </c>
-      <c r="E397" s="1"/>
-      <c r="F397" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E397" s="2"/>
+      <c r="F397" s="2"/>
       <c r="G397" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H397" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I397" s="1"/>
       <c r="J397" s="1"/>
@@ -12607,10 +12614,10 @@
       <c r="E398" s="2"/>
       <c r="F398" s="2"/>
       <c r="G398" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H398" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I398" s="1"/>
       <c r="J398" s="1"/>
@@ -12637,10 +12644,10 @@
       <c r="E399" s="2"/>
       <c r="F399" s="2"/>
       <c r="G399" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H399" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I399" s="1"/>
       <c r="J399" s="1"/>
@@ -12664,13 +12671,13 @@
       <c r="D400" s="4">
         <v>-20</v>
       </c>
-      <c r="E400" s="2"/>
-      <c r="F400" s="2"/>
+      <c r="E400" s="1"/>
+      <c r="F400" s="1"/>
       <c r="G400" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H400" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I400" s="1"/>
       <c r="J400" s="1"/>
@@ -12697,10 +12704,10 @@
       <c r="E401" s="1"/>
       <c r="F401" s="1"/>
       <c r="G401" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H401" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I401" s="1"/>
       <c r="J401" s="1"/>
@@ -12719,18 +12726,18 @@
         <v>-60</v>
       </c>
       <c r="C402" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D402" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E402" s="1"/>
-      <c r="F402" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E402" s="2"/>
+      <c r="F402" s="2"/>
       <c r="G402" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H402" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I402" s="1"/>
       <c r="J402" s="1"/>
@@ -12757,10 +12764,10 @@
       <c r="E403" s="2"/>
       <c r="F403" s="2"/>
       <c r="G403" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H403" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I403" s="1"/>
       <c r="J403" s="1"/>
@@ -12787,10 +12794,10 @@
       <c r="E404" s="2"/>
       <c r="F404" s="2"/>
       <c r="G404" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H404" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I404" s="1"/>
       <c r="J404" s="1"/>
@@ -12814,13 +12821,13 @@
       <c r="D405" s="4">
         <v>0</v>
       </c>
-      <c r="E405" s="2"/>
-      <c r="F405" s="2"/>
+      <c r="E405" s="1"/>
+      <c r="F405" s="1"/>
       <c r="G405" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H405" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I405" s="1"/>
       <c r="J405" s="1"/>
@@ -12847,10 +12854,10 @@
       <c r="E406" s="1"/>
       <c r="F406" s="1"/>
       <c r="G406" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H406" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I406" s="1"/>
       <c r="J406" s="1"/>
@@ -12869,19 +12876,17 @@
         <v>-60</v>
       </c>
       <c r="C407" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D407" s="4">
-        <v>0</v>
-      </c>
-      <c r="E407" s="1"/>
-      <c r="F407" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E407" s="2"/>
+      <c r="F407" s="2"/>
       <c r="G407" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H407" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H407" s="1"/>
       <c r="I407" s="1"/>
       <c r="J407" s="1"/>
       <c r="K407" s="1"/>
@@ -12902,12 +12907,12 @@
         <v>0</v>
       </c>
       <c r="D408" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E408" s="2"/>
       <c r="F408" s="2"/>
       <c r="G408" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H408" s="1"/>
       <c r="I408" s="1"/>
@@ -12930,12 +12935,12 @@
         <v>0</v>
       </c>
       <c r="D409" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E409" s="2"/>
       <c r="F409" s="2"/>
       <c r="G409" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H409" s="1"/>
       <c r="I409" s="1"/>
@@ -12955,15 +12960,15 @@
         <v>-60</v>
       </c>
       <c r="C410" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D410" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E410" s="2"/>
       <c r="F410" s="2"/>
       <c r="G410" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H410" s="1"/>
       <c r="I410" s="1"/>
@@ -12986,12 +12991,12 @@
         <v>-5</v>
       </c>
       <c r="D411" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E411" s="2"/>
       <c r="F411" s="2"/>
       <c r="G411" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H411" s="1"/>
       <c r="I411" s="1"/>
@@ -13014,12 +13019,12 @@
         <v>-5</v>
       </c>
       <c r="D412" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E412" s="2"/>
       <c r="F412" s="2"/>
       <c r="G412" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H412" s="1"/>
       <c r="I412" s="1"/>
@@ -13042,12 +13047,12 @@
         <v>-5</v>
       </c>
       <c r="D413" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E413" s="2"/>
       <c r="F413" s="2"/>
       <c r="G413" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H413" s="1"/>
       <c r="I413" s="1"/>
@@ -13067,15 +13072,15 @@
         <v>-60</v>
       </c>
       <c r="C414" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D414" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E414" s="2"/>
       <c r="F414" s="2"/>
       <c r="G414" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H414" s="1"/>
       <c r="I414" s="1"/>
@@ -13098,12 +13103,12 @@
         <v>-10</v>
       </c>
       <c r="D415" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E415" s="2"/>
       <c r="F415" s="2"/>
       <c r="G415" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H415" s="1"/>
       <c r="I415" s="1"/>
@@ -13126,12 +13131,12 @@
         <v>-10</v>
       </c>
       <c r="D416" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E416" s="2"/>
       <c r="F416" s="2"/>
       <c r="G416" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H416" s="1"/>
       <c r="I416" s="1"/>
@@ -13154,12 +13159,12 @@
         <v>-10</v>
       </c>
       <c r="D417" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E417" s="2"/>
       <c r="F417" s="2"/>
       <c r="G417" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H417" s="1"/>
       <c r="I417" s="1"/>
@@ -13176,20 +13181,22 @@
         <v>-30</v>
       </c>
       <c r="B418" s="4">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="C418" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D418" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E418" s="2"/>
-      <c r="F418" s="2"/>
-      <c r="G418" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E418" s="3"/>
+      <c r="F418" s="3"/>
+      <c r="G418" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H418" s="1"/>
+      <c r="H418" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I418" s="1"/>
       <c r="J418" s="1"/>
       <c r="K418" s="1"/>
@@ -13212,12 +13219,12 @@
       <c r="D419" s="4">
         <v>0</v>
       </c>
-      <c r="E419" s="3"/>
-      <c r="F419" s="3"/>
-      <c r="G419" s="3" t="s">
+      <c r="E419" s="2"/>
+      <c r="F419" s="2"/>
+      <c r="G419" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H419" s="3" t="s">
+      <c r="H419" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I419" s="1"/>
@@ -13245,10 +13252,10 @@
       <c r="E420" s="2"/>
       <c r="F420" s="2"/>
       <c r="G420" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H420" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H420" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I420" s="1"/>
       <c r="J420" s="1"/>
@@ -13275,10 +13282,10 @@
       <c r="E421" s="2"/>
       <c r="F421" s="2"/>
       <c r="G421" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H421" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I421" s="1"/>
       <c r="J421" s="1"/>
@@ -13305,10 +13312,10 @@
       <c r="E422" s="2"/>
       <c r="F422" s="2"/>
       <c r="G422" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H422" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I422" s="1"/>
       <c r="J422" s="1"/>
@@ -13335,10 +13342,10 @@
       <c r="E423" s="2"/>
       <c r="F423" s="2"/>
       <c r="G423" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I423" s="1"/>
       <c r="J423" s="1"/>
@@ -13362,13 +13369,13 @@
       <c r="D424" s="4">
         <v>0</v>
       </c>
-      <c r="E424" s="2"/>
-      <c r="F424" s="2"/>
+      <c r="E424" s="1"/>
+      <c r="F424" s="1"/>
       <c r="G424" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I424" s="1"/>
       <c r="J424" s="1"/>
@@ -13395,10 +13402,10 @@
       <c r="E425" s="1"/>
       <c r="F425" s="1"/>
       <c r="G425" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H425" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I425" s="1"/>
       <c r="J425" s="1"/>
@@ -13420,15 +13427,15 @@
         <v>0</v>
       </c>
       <c r="D426" s="4">
-        <v>0</v>
-      </c>
-      <c r="E426" s="1"/>
-      <c r="F426" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E426" s="2"/>
+      <c r="F426" s="2"/>
       <c r="G426" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H426" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I426" s="1"/>
       <c r="J426" s="1"/>
@@ -13455,10 +13462,10 @@
       <c r="E427" s="2"/>
       <c r="F427" s="2"/>
       <c r="G427" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I427" s="1"/>
       <c r="J427" s="1"/>
@@ -13485,10 +13492,10 @@
       <c r="E428" s="2"/>
       <c r="F428" s="2"/>
       <c r="G428" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I428" s="1"/>
       <c r="J428" s="1"/>
@@ -13512,13 +13519,13 @@
       <c r="D429" s="4">
         <v>-20</v>
       </c>
-      <c r="E429" s="2"/>
-      <c r="F429" s="2"/>
+      <c r="E429" s="1"/>
+      <c r="F429" s="1"/>
       <c r="G429" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I429" s="1"/>
       <c r="J429" s="1"/>
@@ -13545,10 +13552,10 @@
       <c r="E430" s="1"/>
       <c r="F430" s="1"/>
       <c r="G430" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I430" s="1"/>
       <c r="J430" s="1"/>
@@ -13567,18 +13574,18 @@
         <v>-80</v>
       </c>
       <c r="C431" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D431" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E431" s="1"/>
-      <c r="F431" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E431" s="2"/>
+      <c r="F431" s="2"/>
       <c r="G431" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I431" s="1"/>
       <c r="J431" s="1"/>
@@ -13605,10 +13612,10 @@
       <c r="E432" s="2"/>
       <c r="F432" s="2"/>
       <c r="G432" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I432" s="1"/>
       <c r="J432" s="1"/>
@@ -13635,10 +13642,10 @@
       <c r="E433" s="2"/>
       <c r="F433" s="2"/>
       <c r="G433" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I433" s="1"/>
       <c r="J433" s="1"/>
@@ -13662,13 +13669,13 @@
       <c r="D434" s="4">
         <v>0</v>
       </c>
-      <c r="E434" s="2"/>
-      <c r="F434" s="2"/>
+      <c r="E434" s="1"/>
+      <c r="F434" s="1"/>
       <c r="G434" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I434" s="1"/>
       <c r="J434" s="1"/>
@@ -13695,10 +13702,10 @@
       <c r="E435" s="1"/>
       <c r="F435" s="1"/>
       <c r="G435" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H435" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I435" s="1"/>
       <c r="J435" s="1"/>
@@ -13717,19 +13724,17 @@
         <v>-80</v>
       </c>
       <c r="C436" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D436" s="4">
-        <v>0</v>
-      </c>
-      <c r="E436" s="1"/>
-      <c r="F436" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E436" s="2"/>
+      <c r="F436" s="2"/>
       <c r="G436" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H436" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H436" s="1"/>
       <c r="I436" s="1"/>
       <c r="J436" s="1"/>
       <c r="K436" s="1"/>
@@ -13750,12 +13755,12 @@
         <v>0</v>
       </c>
       <c r="D437" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E437" s="2"/>
       <c r="F437" s="2"/>
       <c r="G437" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H437" s="1"/>
       <c r="I437" s="1"/>
@@ -13778,12 +13783,12 @@
         <v>0</v>
       </c>
       <c r="D438" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E438" s="2"/>
       <c r="F438" s="2"/>
       <c r="G438" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H438" s="1"/>
       <c r="I438" s="1"/>
@@ -13803,15 +13808,15 @@
         <v>-80</v>
       </c>
       <c r="C439" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D439" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E439" s="2"/>
       <c r="F439" s="2"/>
       <c r="G439" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H439" s="1"/>
       <c r="I439" s="1"/>
@@ -13834,12 +13839,12 @@
         <v>-5</v>
       </c>
       <c r="D440" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E440" s="2"/>
       <c r="F440" s="2"/>
       <c r="G440" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H440" s="1"/>
       <c r="I440" s="1"/>
@@ -13862,12 +13867,12 @@
         <v>-5</v>
       </c>
       <c r="D441" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E441" s="2"/>
       <c r="F441" s="2"/>
       <c r="G441" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H441" s="1"/>
       <c r="I441" s="1"/>
@@ -13890,12 +13895,12 @@
         <v>-5</v>
       </c>
       <c r="D442" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E442" s="2"/>
       <c r="F442" s="2"/>
       <c r="G442" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H442" s="1"/>
       <c r="I442" s="1"/>
@@ -13915,15 +13920,15 @@
         <v>-80</v>
       </c>
       <c r="C443" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D443" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E443" s="2"/>
       <c r="F443" s="2"/>
       <c r="G443" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H443" s="1"/>
       <c r="I443" s="1"/>
@@ -13946,12 +13951,12 @@
         <v>-10</v>
       </c>
       <c r="D444" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E444" s="2"/>
       <c r="F444" s="2"/>
       <c r="G444" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H444" s="1"/>
       <c r="I444" s="1"/>
@@ -13974,12 +13979,12 @@
         <v>-10</v>
       </c>
       <c r="D445" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E445" s="2"/>
       <c r="F445" s="2"/>
       <c r="G445" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H445" s="1"/>
       <c r="I445" s="1"/>
@@ -14002,12 +14007,12 @@
         <v>-10</v>
       </c>
       <c r="D446" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E446" s="2"/>
       <c r="F446" s="2"/>
       <c r="G446" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H446" s="1"/>
       <c r="I446" s="1"/>
@@ -14021,23 +14026,25 @@
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
-        <v>-30</v>
+        <v>-45</v>
       </c>
       <c r="B447" s="4">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="C447" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D447" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E447" s="2"/>
-      <c r="F447" s="2"/>
-      <c r="G447" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E447" s="3"/>
+      <c r="F447" s="3"/>
+      <c r="G447" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H447" s="1"/>
+      <c r="H447" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I447" s="1"/>
       <c r="J447" s="1"/>
       <c r="K447" s="1"/>
@@ -14060,12 +14067,12 @@
       <c r="D448" s="4">
         <v>0</v>
       </c>
-      <c r="E448" s="3"/>
-      <c r="F448" s="3"/>
-      <c r="G448" s="3" t="s">
+      <c r="E448" s="2"/>
+      <c r="F448" s="2"/>
+      <c r="G448" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H448" s="3" t="s">
+      <c r="H448" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I448" s="1"/>
@@ -14093,10 +14100,10 @@
       <c r="E449" s="2"/>
       <c r="F449" s="2"/>
       <c r="G449" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H449" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H449" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I449" s="1"/>
       <c r="J449" s="1"/>
@@ -14123,10 +14130,10 @@
       <c r="E450" s="2"/>
       <c r="F450" s="2"/>
       <c r="G450" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I450" s="1"/>
       <c r="J450" s="1"/>
@@ -14153,10 +14160,10 @@
       <c r="E451" s="2"/>
       <c r="F451" s="2"/>
       <c r="G451" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I451" s="1"/>
       <c r="J451" s="1"/>
@@ -14183,10 +14190,10 @@
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H452" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I452" s="1"/>
       <c r="J452" s="1"/>
@@ -14210,13 +14217,13 @@
       <c r="D453" s="4">
         <v>0</v>
       </c>
-      <c r="E453" s="2"/>
-      <c r="F453" s="2"/>
+      <c r="E453" s="1"/>
+      <c r="F453" s="1"/>
       <c r="G453" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H453" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I453" s="1"/>
       <c r="J453" s="1"/>
@@ -14243,10 +14250,10 @@
       <c r="E454" s="1"/>
       <c r="F454" s="1"/>
       <c r="G454" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I454" s="1"/>
       <c r="J454" s="1"/>
@@ -14268,15 +14275,15 @@
         <v>0</v>
       </c>
       <c r="D455" s="4">
-        <v>0</v>
-      </c>
-      <c r="E455" s="1"/>
-      <c r="F455" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E455" s="2"/>
+      <c r="F455" s="2"/>
       <c r="G455" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H455" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I455" s="1"/>
       <c r="J455" s="1"/>
@@ -14303,10 +14310,10 @@
       <c r="E456" s="2"/>
       <c r="F456" s="2"/>
       <c r="G456" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H456" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I456" s="1"/>
       <c r="J456" s="1"/>
@@ -14333,10 +14340,10 @@
       <c r="E457" s="2"/>
       <c r="F457" s="2"/>
       <c r="G457" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H457" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I457" s="1"/>
       <c r="J457" s="1"/>
@@ -14360,13 +14367,13 @@
       <c r="D458" s="4">
         <v>-20</v>
       </c>
-      <c r="E458" s="2"/>
-      <c r="F458" s="2"/>
+      <c r="E458" s="1"/>
+      <c r="F458" s="1"/>
       <c r="G458" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I458" s="1"/>
       <c r="J458" s="1"/>
@@ -14393,10 +14400,10 @@
       <c r="E459" s="1"/>
       <c r="F459" s="1"/>
       <c r="G459" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I459" s="1"/>
       <c r="J459" s="1"/>
@@ -14415,18 +14422,18 @@
         <v>0</v>
       </c>
       <c r="C460" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D460" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E460" s="1"/>
-      <c r="F460" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E460" s="2"/>
+      <c r="F460" s="2"/>
       <c r="G460" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H460" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I460" s="1"/>
       <c r="J460" s="1"/>
@@ -14453,10 +14460,10 @@
       <c r="E461" s="2"/>
       <c r="F461" s="2"/>
       <c r="G461" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I461" s="1"/>
       <c r="J461" s="1"/>
@@ -14483,10 +14490,10 @@
       <c r="E462" s="2"/>
       <c r="F462" s="2"/>
       <c r="G462" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H462" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I462" s="1"/>
       <c r="J462" s="1"/>
@@ -14510,13 +14517,13 @@
       <c r="D463" s="4">
         <v>0</v>
       </c>
-      <c r="E463" s="2"/>
-      <c r="F463" s="2"/>
+      <c r="E463" s="1"/>
+      <c r="F463" s="1"/>
       <c r="G463" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H463" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I463" s="1"/>
       <c r="J463" s="1"/>
@@ -14543,10 +14550,10 @@
       <c r="E464" s="1"/>
       <c r="F464" s="1"/>
       <c r="G464" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H464" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I464" s="1"/>
       <c r="J464" s="1"/>
@@ -14565,19 +14572,17 @@
         <v>0</v>
       </c>
       <c r="C465" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D465" s="4">
-        <v>0</v>
-      </c>
-      <c r="E465" s="1"/>
-      <c r="F465" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E465" s="2"/>
+      <c r="F465" s="2"/>
       <c r="G465" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H465" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H465" s="1"/>
       <c r="I465" s="1"/>
       <c r="J465" s="1"/>
       <c r="K465" s="1"/>
@@ -14598,12 +14603,12 @@
         <v>0</v>
       </c>
       <c r="D466" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E466" s="2"/>
       <c r="F466" s="2"/>
       <c r="G466" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H466" s="1"/>
       <c r="I466" s="1"/>
@@ -14626,12 +14631,12 @@
         <v>0</v>
       </c>
       <c r="D467" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E467" s="2"/>
       <c r="F467" s="2"/>
       <c r="G467" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H467" s="1"/>
       <c r="I467" s="1"/>
@@ -14651,15 +14656,15 @@
         <v>0</v>
       </c>
       <c r="C468" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D468" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E468" s="2"/>
       <c r="F468" s="2"/>
       <c r="G468" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H468" s="1"/>
       <c r="I468" s="1"/>
@@ -14682,12 +14687,12 @@
         <v>-5</v>
       </c>
       <c r="D469" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E469" s="2"/>
       <c r="F469" s="2"/>
       <c r="G469" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H469" s="1"/>
       <c r="I469" s="1"/>
@@ -14710,12 +14715,12 @@
         <v>-5</v>
       </c>
       <c r="D470" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E470" s="2"/>
       <c r="F470" s="2"/>
       <c r="G470" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H470" s="1"/>
       <c r="I470" s="1"/>
@@ -14738,12 +14743,12 @@
         <v>-5</v>
       </c>
       <c r="D471" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E471" s="2"/>
       <c r="F471" s="2"/>
       <c r="G471" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H471" s="1"/>
       <c r="I471" s="1"/>
@@ -14763,15 +14768,15 @@
         <v>0</v>
       </c>
       <c r="C472" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D472" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E472" s="2"/>
       <c r="F472" s="2"/>
       <c r="G472" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H472" s="1"/>
       <c r="I472" s="1"/>
@@ -14794,12 +14799,12 @@
         <v>-10</v>
       </c>
       <c r="D473" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E473" s="2"/>
       <c r="F473" s="2"/>
       <c r="G473" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H473" s="1"/>
       <c r="I473" s="1"/>
@@ -14822,12 +14827,12 @@
         <v>-10</v>
       </c>
       <c r="D474" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E474" s="2"/>
       <c r="F474" s="2"/>
       <c r="G474" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H474" s="1"/>
       <c r="I474" s="1"/>
@@ -14850,12 +14855,12 @@
         <v>-10</v>
       </c>
       <c r="D475" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E475" s="2"/>
       <c r="F475" s="2"/>
       <c r="G475" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H475" s="1"/>
       <c r="I475" s="1"/>
@@ -14872,20 +14877,22 @@
         <v>-45</v>
       </c>
       <c r="B476" s="4">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="C476" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D476" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E476" s="2"/>
-      <c r="F476" s="2"/>
-      <c r="G476" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E476" s="3"/>
+      <c r="F476" s="3"/>
+      <c r="G476" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H476" s="1"/>
+      <c r="H476" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I476" s="1"/>
       <c r="J476" s="1"/>
       <c r="K476" s="1"/>
@@ -14908,12 +14915,12 @@
       <c r="D477" s="4">
         <v>0</v>
       </c>
-      <c r="E477" s="3"/>
-      <c r="F477" s="3"/>
-      <c r="G477" s="3" t="s">
+      <c r="E477" s="2"/>
+      <c r="F477" s="2"/>
+      <c r="G477" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H477" s="3" t="s">
+      <c r="H477" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I477" s="1"/>
@@ -14941,10 +14948,10 @@
       <c r="E478" s="2"/>
       <c r="F478" s="2"/>
       <c r="G478" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H478" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H478" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I478" s="1"/>
       <c r="J478" s="1"/>
@@ -14971,10 +14978,10 @@
       <c r="E479" s="2"/>
       <c r="F479" s="2"/>
       <c r="G479" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H479" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I479" s="1"/>
       <c r="J479" s="1"/>
@@ -15001,10 +15008,10 @@
       <c r="E480" s="2"/>
       <c r="F480" s="2"/>
       <c r="G480" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H480" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I480" s="1"/>
       <c r="J480" s="1"/>
@@ -15031,10 +15038,10 @@
       <c r="E481" s="2"/>
       <c r="F481" s="2"/>
       <c r="G481" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H481" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I481" s="1"/>
       <c r="J481" s="1"/>
@@ -15058,13 +15065,13 @@
       <c r="D482" s="4">
         <v>0</v>
       </c>
-      <c r="E482" s="2"/>
-      <c r="F482" s="2"/>
+      <c r="E482" s="1"/>
+      <c r="F482" s="1"/>
       <c r="G482" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H482" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I482" s="1"/>
       <c r="J482" s="1"/>
@@ -15091,10 +15098,10 @@
       <c r="E483" s="1"/>
       <c r="F483" s="1"/>
       <c r="G483" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H483" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I483" s="1"/>
       <c r="J483" s="1"/>
@@ -15116,15 +15123,15 @@
         <v>0</v>
       </c>
       <c r="D484" s="4">
-        <v>0</v>
-      </c>
-      <c r="E484" s="1"/>
-      <c r="F484" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E484" s="2"/>
+      <c r="F484" s="2"/>
       <c r="G484" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H484" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I484" s="1"/>
       <c r="J484" s="1"/>
@@ -15151,10 +15158,10 @@
       <c r="E485" s="2"/>
       <c r="F485" s="2"/>
       <c r="G485" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H485" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I485" s="1"/>
       <c r="J485" s="1"/>
@@ -15181,10 +15188,10 @@
       <c r="E486" s="2"/>
       <c r="F486" s="2"/>
       <c r="G486" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H486" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I486" s="1"/>
       <c r="J486" s="1"/>
@@ -15208,13 +15215,13 @@
       <c r="D487" s="4">
         <v>-20</v>
       </c>
-      <c r="E487" s="2"/>
-      <c r="F487" s="2"/>
+      <c r="E487" s="1"/>
+      <c r="F487" s="1"/>
       <c r="G487" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H487" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I487" s="1"/>
       <c r="J487" s="1"/>
@@ -15241,10 +15248,10 @@
       <c r="E488" s="1"/>
       <c r="F488" s="1"/>
       <c r="G488" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H488" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I488" s="1"/>
       <c r="J488" s="1"/>
@@ -15263,18 +15270,18 @@
         <v>-20</v>
       </c>
       <c r="C489" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D489" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E489" s="1"/>
-      <c r="F489" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E489" s="2"/>
+      <c r="F489" s="2"/>
       <c r="G489" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H489" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I489" s="1"/>
       <c r="J489" s="1"/>
@@ -15301,10 +15308,10 @@
       <c r="E490" s="2"/>
       <c r="F490" s="2"/>
       <c r="G490" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H490" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I490" s="1"/>
       <c r="J490" s="1"/>
@@ -15331,10 +15338,10 @@
       <c r="E491" s="2"/>
       <c r="F491" s="2"/>
       <c r="G491" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I491" s="1"/>
       <c r="J491" s="1"/>
@@ -15358,13 +15365,13 @@
       <c r="D492" s="4">
         <v>0</v>
       </c>
-      <c r="E492" s="2"/>
-      <c r="F492" s="2"/>
+      <c r="E492" s="1"/>
+      <c r="F492" s="1"/>
       <c r="G492" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I492" s="1"/>
       <c r="J492" s="1"/>
@@ -15391,10 +15398,10 @@
       <c r="E493" s="1"/>
       <c r="F493" s="1"/>
       <c r="G493" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I493" s="1"/>
       <c r="J493" s="1"/>
@@ -15413,19 +15420,17 @@
         <v>-20</v>
       </c>
       <c r="C494" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D494" s="4">
-        <v>0</v>
-      </c>
-      <c r="E494" s="1"/>
-      <c r="F494" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E494" s="2"/>
+      <c r="F494" s="2"/>
       <c r="G494" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H494" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H494" s="1"/>
       <c r="I494" s="1"/>
       <c r="J494" s="1"/>
       <c r="K494" s="1"/>
@@ -15446,12 +15451,12 @@
         <v>0</v>
       </c>
       <c r="D495" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E495" s="2"/>
       <c r="F495" s="2"/>
       <c r="G495" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H495" s="1"/>
       <c r="I495" s="1"/>
@@ -15474,12 +15479,12 @@
         <v>0</v>
       </c>
       <c r="D496" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E496" s="2"/>
       <c r="F496" s="2"/>
       <c r="G496" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H496" s="1"/>
       <c r="I496" s="1"/>
@@ -15499,15 +15504,15 @@
         <v>-20</v>
       </c>
       <c r="C497" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D497" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E497" s="2"/>
       <c r="F497" s="2"/>
       <c r="G497" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H497" s="1"/>
       <c r="I497" s="1"/>
@@ -15530,12 +15535,12 @@
         <v>-5</v>
       </c>
       <c r="D498" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E498" s="2"/>
       <c r="F498" s="2"/>
       <c r="G498" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H498" s="1"/>
       <c r="I498" s="1"/>
@@ -15558,12 +15563,12 @@
         <v>-5</v>
       </c>
       <c r="D499" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E499" s="2"/>
       <c r="F499" s="2"/>
       <c r="G499" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H499" s="1"/>
       <c r="I499" s="1"/>
@@ -15586,12 +15591,12 @@
         <v>-5</v>
       </c>
       <c r="D500" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E500" s="2"/>
       <c r="F500" s="2"/>
       <c r="G500" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H500" s="1"/>
       <c r="I500" s="1"/>
@@ -15611,15 +15616,15 @@
         <v>-20</v>
       </c>
       <c r="C501" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D501" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E501" s="2"/>
       <c r="F501" s="2"/>
       <c r="G501" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H501" s="1"/>
       <c r="I501" s="1"/>
@@ -15642,12 +15647,12 @@
         <v>-10</v>
       </c>
       <c r="D502" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E502" s="2"/>
       <c r="F502" s="2"/>
       <c r="G502" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H502" s="1"/>
       <c r="I502" s="1"/>
@@ -15670,12 +15675,12 @@
         <v>-10</v>
       </c>
       <c r="D503" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E503" s="2"/>
       <c r="F503" s="2"/>
       <c r="G503" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H503" s="1"/>
       <c r="I503" s="1"/>
@@ -15698,12 +15703,12 @@
         <v>-10</v>
       </c>
       <c r="D504" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E504" s="2"/>
       <c r="F504" s="2"/>
       <c r="G504" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H504" s="1"/>
       <c r="I504" s="1"/>
@@ -15720,20 +15725,22 @@
         <v>-45</v>
       </c>
       <c r="B505" s="4">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="C505" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D505" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E505" s="2"/>
-      <c r="F505" s="2"/>
-      <c r="G505" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E505" s="3"/>
+      <c r="F505" s="3"/>
+      <c r="G505" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H505" s="1"/>
+      <c r="H505" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I505" s="1"/>
       <c r="J505" s="1"/>
       <c r="K505" s="1"/>
@@ -15756,12 +15763,12 @@
       <c r="D506" s="4">
         <v>0</v>
       </c>
-      <c r="E506" s="3"/>
-      <c r="F506" s="3"/>
-      <c r="G506" s="3" t="s">
+      <c r="E506" s="2"/>
+      <c r="F506" s="2"/>
+      <c r="G506" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H506" s="3" t="s">
+      <c r="H506" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I506" s="1"/>
@@ -15789,10 +15796,10 @@
       <c r="E507" s="2"/>
       <c r="F507" s="2"/>
       <c r="G507" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H507" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H507" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I507" s="1"/>
       <c r="J507" s="1"/>
@@ -15819,10 +15826,10 @@
       <c r="E508" s="2"/>
       <c r="F508" s="2"/>
       <c r="G508" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I508" s="1"/>
       <c r="J508" s="1"/>
@@ -15849,10 +15856,10 @@
       <c r="E509" s="2"/>
       <c r="F509" s="2"/>
       <c r="G509" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I509" s="1"/>
       <c r="J509" s="1"/>
@@ -15879,10 +15886,10 @@
       <c r="E510" s="2"/>
       <c r="F510" s="2"/>
       <c r="G510" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H510" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I510" s="1"/>
       <c r="J510" s="1"/>
@@ -15906,13 +15913,13 @@
       <c r="D511" s="4">
         <v>0</v>
       </c>
-      <c r="E511" s="2"/>
-      <c r="F511" s="2"/>
+      <c r="E511" s="1"/>
+      <c r="F511" s="1"/>
       <c r="G511" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H511" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I511" s="1"/>
       <c r="J511" s="1"/>
@@ -15939,10 +15946,10 @@
       <c r="E512" s="1"/>
       <c r="F512" s="1"/>
       <c r="G512" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I512" s="1"/>
       <c r="J512" s="1"/>
@@ -15964,15 +15971,15 @@
         <v>0</v>
       </c>
       <c r="D513" s="4">
-        <v>0</v>
-      </c>
-      <c r="E513" s="1"/>
-      <c r="F513" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E513" s="2"/>
+      <c r="F513" s="2"/>
       <c r="G513" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I513" s="1"/>
       <c r="J513" s="1"/>
@@ -15999,10 +16006,10 @@
       <c r="E514" s="2"/>
       <c r="F514" s="2"/>
       <c r="G514" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I514" s="1"/>
       <c r="J514" s="1"/>
@@ -16029,10 +16036,10 @@
       <c r="E515" s="2"/>
       <c r="F515" s="2"/>
       <c r="G515" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H515" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I515" s="1"/>
       <c r="J515" s="1"/>
@@ -16056,13 +16063,13 @@
       <c r="D516" s="4">
         <v>-20</v>
       </c>
-      <c r="E516" s="2"/>
-      <c r="F516" s="2"/>
+      <c r="E516" s="1"/>
+      <c r="F516" s="1"/>
       <c r="G516" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I516" s="1"/>
       <c r="J516" s="1"/>
@@ -16089,10 +16096,10 @@
       <c r="E517" s="1"/>
       <c r="F517" s="1"/>
       <c r="G517" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I517" s="1"/>
       <c r="J517" s="1"/>
@@ -16111,18 +16118,18 @@
         <v>-40</v>
       </c>
       <c r="C518" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D518" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E518" s="1"/>
-      <c r="F518" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E518" s="2"/>
+      <c r="F518" s="2"/>
       <c r="G518" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H518" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I518" s="1"/>
       <c r="J518" s="1"/>
@@ -16149,10 +16156,10 @@
       <c r="E519" s="2"/>
       <c r="F519" s="2"/>
       <c r="G519" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H519" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I519" s="1"/>
       <c r="J519" s="1"/>
@@ -16179,10 +16186,10 @@
       <c r="E520" s="2"/>
       <c r="F520" s="2"/>
       <c r="G520" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I520" s="1"/>
       <c r="J520" s="1"/>
@@ -16206,13 +16213,13 @@
       <c r="D521" s="4">
         <v>0</v>
       </c>
-      <c r="E521" s="2"/>
-      <c r="F521" s="2"/>
+      <c r="E521" s="1"/>
+      <c r="F521" s="1"/>
       <c r="G521" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I521" s="1"/>
       <c r="J521" s="1"/>
@@ -16239,10 +16246,10 @@
       <c r="E522" s="1"/>
       <c r="F522" s="1"/>
       <c r="G522" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H522" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I522" s="1"/>
       <c r="J522" s="1"/>
@@ -16261,19 +16268,17 @@
         <v>-40</v>
       </c>
       <c r="C523" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D523" s="4">
-        <v>0</v>
-      </c>
-      <c r="E523" s="1"/>
-      <c r="F523" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E523" s="2"/>
+      <c r="F523" s="2"/>
       <c r="G523" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H523" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H523" s="1"/>
       <c r="I523" s="1"/>
       <c r="J523" s="1"/>
       <c r="K523" s="1"/>
@@ -16294,12 +16299,12 @@
         <v>0</v>
       </c>
       <c r="D524" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E524" s="2"/>
       <c r="F524" s="2"/>
       <c r="G524" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H524" s="1"/>
       <c r="I524" s="1"/>
@@ -16322,12 +16327,12 @@
         <v>0</v>
       </c>
       <c r="D525" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E525" s="2"/>
       <c r="F525" s="2"/>
       <c r="G525" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H525" s="1"/>
       <c r="I525" s="1"/>
@@ -16347,15 +16352,15 @@
         <v>-40</v>
       </c>
       <c r="C526" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D526" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E526" s="2"/>
       <c r="F526" s="2"/>
       <c r="G526" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H526" s="1"/>
       <c r="I526" s="1"/>
@@ -16378,12 +16383,12 @@
         <v>-5</v>
       </c>
       <c r="D527" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E527" s="2"/>
       <c r="F527" s="2"/>
       <c r="G527" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H527" s="1"/>
       <c r="I527" s="1"/>
@@ -16406,12 +16411,12 @@
         <v>-5</v>
       </c>
       <c r="D528" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E528" s="2"/>
       <c r="F528" s="2"/>
       <c r="G528" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H528" s="1"/>
       <c r="I528" s="1"/>
@@ -16434,12 +16439,12 @@
         <v>-5</v>
       </c>
       <c r="D529" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E529" s="2"/>
       <c r="F529" s="2"/>
       <c r="G529" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H529" s="1"/>
       <c r="I529" s="1"/>
@@ -16459,15 +16464,15 @@
         <v>-40</v>
       </c>
       <c r="C530" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D530" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E530" s="2"/>
       <c r="F530" s="2"/>
       <c r="G530" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H530" s="1"/>
       <c r="I530" s="1"/>
@@ -16490,12 +16495,12 @@
         <v>-10</v>
       </c>
       <c r="D531" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E531" s="2"/>
       <c r="F531" s="2"/>
       <c r="G531" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H531" s="1"/>
       <c r="I531" s="1"/>
@@ -16518,12 +16523,12 @@
         <v>-10</v>
       </c>
       <c r="D532" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E532" s="2"/>
       <c r="F532" s="2"/>
       <c r="G532" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H532" s="1"/>
       <c r="I532" s="1"/>
@@ -16546,12 +16551,12 @@
         <v>-10</v>
       </c>
       <c r="D533" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E533" s="2"/>
       <c r="F533" s="2"/>
       <c r="G533" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H533" s="1"/>
       <c r="I533" s="1"/>
@@ -16568,20 +16573,22 @@
         <v>-45</v>
       </c>
       <c r="B534" s="4">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="C534" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D534" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E534" s="2"/>
-      <c r="F534" s="2"/>
-      <c r="G534" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E534" s="3"/>
+      <c r="F534" s="3"/>
+      <c r="G534" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H534" s="1"/>
+      <c r="H534" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I534" s="1"/>
       <c r="J534" s="1"/>
       <c r="K534" s="1"/>
@@ -16604,12 +16611,12 @@
       <c r="D535" s="4">
         <v>0</v>
       </c>
-      <c r="E535" s="3"/>
-      <c r="F535" s="3"/>
-      <c r="G535" s="3" t="s">
+      <c r="E535" s="2"/>
+      <c r="F535" s="2"/>
+      <c r="G535" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H535" s="3" t="s">
+      <c r="H535" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I535" s="1"/>
@@ -16637,10 +16644,10 @@
       <c r="E536" s="2"/>
       <c r="F536" s="2"/>
       <c r="G536" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H536" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H536" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I536" s="1"/>
       <c r="J536" s="1"/>
@@ -16667,10 +16674,10 @@
       <c r="E537" s="2"/>
       <c r="F537" s="2"/>
       <c r="G537" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H537" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I537" s="1"/>
       <c r="J537" s="1"/>
@@ -16697,10 +16704,10 @@
       <c r="E538" s="2"/>
       <c r="F538" s="2"/>
       <c r="G538" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H538" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I538" s="1"/>
       <c r="J538" s="1"/>
@@ -16727,10 +16734,10 @@
       <c r="E539" s="2"/>
       <c r="F539" s="2"/>
       <c r="G539" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H539" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I539" s="1"/>
       <c r="J539" s="1"/>
@@ -16754,13 +16761,13 @@
       <c r="D540" s="4">
         <v>0</v>
       </c>
-      <c r="E540" s="2"/>
-      <c r="F540" s="2"/>
+      <c r="E540" s="1"/>
+      <c r="F540" s="1"/>
       <c r="G540" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H540" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I540" s="1"/>
       <c r="J540" s="1"/>
@@ -16787,10 +16794,10 @@
       <c r="E541" s="1"/>
       <c r="F541" s="1"/>
       <c r="G541" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H541" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I541" s="1"/>
       <c r="J541" s="1"/>
@@ -16812,15 +16819,15 @@
         <v>0</v>
       </c>
       <c r="D542" s="4">
-        <v>0</v>
-      </c>
-      <c r="E542" s="1"/>
-      <c r="F542" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E542" s="2"/>
+      <c r="F542" s="2"/>
       <c r="G542" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H542" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I542" s="1"/>
       <c r="J542" s="1"/>
@@ -16847,10 +16854,10 @@
       <c r="E543" s="2"/>
       <c r="F543" s="2"/>
       <c r="G543" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H543" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I543" s="1"/>
       <c r="J543" s="1"/>
@@ -16877,10 +16884,10 @@
       <c r="E544" s="2"/>
       <c r="F544" s="2"/>
       <c r="G544" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H544" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I544" s="1"/>
       <c r="J544" s="1"/>
@@ -16904,13 +16911,13 @@
       <c r="D545" s="4">
         <v>-20</v>
       </c>
-      <c r="E545" s="2"/>
-      <c r="F545" s="2"/>
+      <c r="E545" s="1"/>
+      <c r="F545" s="1"/>
       <c r="G545" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H545" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I545" s="1"/>
       <c r="J545" s="1"/>
@@ -16937,10 +16944,10 @@
       <c r="E546" s="1"/>
       <c r="F546" s="1"/>
       <c r="G546" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H546" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I546" s="1"/>
       <c r="J546" s="1"/>
@@ -16959,18 +16966,18 @@
         <v>-60</v>
       </c>
       <c r="C547" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D547" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E547" s="1"/>
-      <c r="F547" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E547" s="2"/>
+      <c r="F547" s="2"/>
       <c r="G547" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H547" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I547" s="1"/>
       <c r="J547" s="1"/>
@@ -16997,10 +17004,10 @@
       <c r="E548" s="2"/>
       <c r="F548" s="2"/>
       <c r="G548" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H548" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I548" s="1"/>
       <c r="J548" s="1"/>
@@ -17027,10 +17034,10 @@
       <c r="E549" s="2"/>
       <c r="F549" s="2"/>
       <c r="G549" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H549" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I549" s="1"/>
       <c r="J549" s="1"/>
@@ -17054,13 +17061,13 @@
       <c r="D550" s="4">
         <v>0</v>
       </c>
-      <c r="E550" s="2"/>
-      <c r="F550" s="2"/>
+      <c r="E550" s="1"/>
+      <c r="F550" s="1"/>
       <c r="G550" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H550" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I550" s="1"/>
       <c r="J550" s="1"/>
@@ -17087,10 +17094,10 @@
       <c r="E551" s="1"/>
       <c r="F551" s="1"/>
       <c r="G551" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H551" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I551" s="1"/>
       <c r="J551" s="1"/>
@@ -17109,19 +17116,17 @@
         <v>-60</v>
       </c>
       <c r="C552" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D552" s="4">
-        <v>0</v>
-      </c>
-      <c r="E552" s="1"/>
-      <c r="F552" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E552" s="2"/>
+      <c r="F552" s="2"/>
       <c r="G552" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H552" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H552" s="1"/>
       <c r="I552" s="1"/>
       <c r="J552" s="1"/>
       <c r="K552" s="1"/>
@@ -17142,12 +17147,12 @@
         <v>0</v>
       </c>
       <c r="D553" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E553" s="2"/>
       <c r="F553" s="2"/>
       <c r="G553" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H553" s="1"/>
       <c r="I553" s="1"/>
@@ -17170,12 +17175,12 @@
         <v>0</v>
       </c>
       <c r="D554" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E554" s="2"/>
       <c r="F554" s="2"/>
       <c r="G554" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H554" s="1"/>
       <c r="I554" s="1"/>
@@ -17195,15 +17200,15 @@
         <v>-60</v>
       </c>
       <c r="C555" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D555" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E555" s="2"/>
       <c r="F555" s="2"/>
       <c r="G555" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H555" s="1"/>
       <c r="I555" s="1"/>
@@ -17226,12 +17231,12 @@
         <v>-5</v>
       </c>
       <c r="D556" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E556" s="2"/>
       <c r="F556" s="2"/>
       <c r="G556" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H556" s="1"/>
       <c r="I556" s="1"/>
@@ -17254,12 +17259,12 @@
         <v>-5</v>
       </c>
       <c r="D557" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E557" s="2"/>
       <c r="F557" s="2"/>
       <c r="G557" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H557" s="1"/>
       <c r="I557" s="1"/>
@@ -17282,12 +17287,12 @@
         <v>-5</v>
       </c>
       <c r="D558" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E558" s="2"/>
       <c r="F558" s="2"/>
       <c r="G558" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H558" s="1"/>
       <c r="I558" s="1"/>
@@ -17307,15 +17312,15 @@
         <v>-60</v>
       </c>
       <c r="C559" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D559" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E559" s="2"/>
       <c r="F559" s="2"/>
       <c r="G559" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H559" s="1"/>
       <c r="I559" s="1"/>
@@ -17338,12 +17343,12 @@
         <v>-10</v>
       </c>
       <c r="D560" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E560" s="2"/>
       <c r="F560" s="2"/>
       <c r="G560" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H560" s="1"/>
       <c r="I560" s="1"/>
@@ -17366,12 +17371,12 @@
         <v>-10</v>
       </c>
       <c r="D561" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E561" s="2"/>
       <c r="F561" s="2"/>
       <c r="G561" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H561" s="1"/>
       <c r="I561" s="1"/>
@@ -17394,12 +17399,12 @@
         <v>-10</v>
       </c>
       <c r="D562" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E562" s="2"/>
       <c r="F562" s="2"/>
       <c r="G562" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H562" s="1"/>
       <c r="I562" s="1"/>
@@ -17416,20 +17421,22 @@
         <v>-45</v>
       </c>
       <c r="B563" s="4">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="C563" s="4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D563" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E563" s="2"/>
-      <c r="F563" s="2"/>
-      <c r="G563" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E563" s="3"/>
+      <c r="F563" s="3"/>
+      <c r="G563" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H563" s="1"/>
+      <c r="H563" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I563" s="1"/>
       <c r="J563" s="1"/>
       <c r="K563" s="1"/>
@@ -17452,12 +17459,12 @@
       <c r="D564" s="4">
         <v>0</v>
       </c>
-      <c r="E564" s="3"/>
-      <c r="F564" s="3"/>
-      <c r="G564" s="3" t="s">
+      <c r="E564" s="2"/>
+      <c r="F564" s="2"/>
+      <c r="G564" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H564" s="3" t="s">
+      <c r="H564" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I564" s="1"/>
@@ -17485,10 +17492,10 @@
       <c r="E565" s="2"/>
       <c r="F565" s="2"/>
       <c r="G565" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H565" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H565" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I565" s="1"/>
       <c r="J565" s="1"/>
@@ -17515,10 +17522,10 @@
       <c r="E566" s="2"/>
       <c r="F566" s="2"/>
       <c r="G566" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H566" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I566" s="1"/>
       <c r="J566" s="1"/>
@@ -17545,10 +17552,10 @@
       <c r="E567" s="2"/>
       <c r="F567" s="2"/>
       <c r="G567" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H567" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I567" s="1"/>
       <c r="J567" s="1"/>
@@ -17575,10 +17582,10 @@
       <c r="E568" s="2"/>
       <c r="F568" s="2"/>
       <c r="G568" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H568" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I568" s="1"/>
       <c r="J568" s="1"/>
@@ -17602,13 +17609,13 @@
       <c r="D569" s="4">
         <v>0</v>
       </c>
-      <c r="E569" s="2"/>
-      <c r="F569" s="2"/>
+      <c r="E569" s="1"/>
+      <c r="F569" s="1"/>
       <c r="G569" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H569" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I569" s="1"/>
       <c r="J569" s="1"/>
@@ -17635,10 +17642,10 @@
       <c r="E570" s="1"/>
       <c r="F570" s="1"/>
       <c r="G570" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H570" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I570" s="1"/>
       <c r="J570" s="1"/>
@@ -17660,15 +17667,15 @@
         <v>0</v>
       </c>
       <c r="D571" s="4">
-        <v>0</v>
-      </c>
-      <c r="E571" s="1"/>
-      <c r="F571" s="1"/>
+        <v>-20</v>
+      </c>
+      <c r="E571" s="2"/>
+      <c r="F571" s="2"/>
       <c r="G571" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H571" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I571" s="1"/>
       <c r="J571" s="1"/>
@@ -17695,10 +17702,10 @@
       <c r="E572" s="2"/>
       <c r="F572" s="2"/>
       <c r="G572" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H572" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I572" s="1"/>
       <c r="J572" s="1"/>
@@ -17725,10 +17732,10 @@
       <c r="E573" s="2"/>
       <c r="F573" s="2"/>
       <c r="G573" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H573" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I573" s="1"/>
       <c r="J573" s="1"/>
@@ -17752,13 +17759,13 @@
       <c r="D574" s="4">
         <v>-20</v>
       </c>
-      <c r="E574" s="2"/>
-      <c r="F574" s="2"/>
+      <c r="E574" s="1"/>
+      <c r="F574" s="1"/>
       <c r="G574" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I574" s="1"/>
       <c r="J574" s="1"/>
@@ -17785,10 +17792,10 @@
       <c r="E575" s="1"/>
       <c r="F575" s="1"/>
       <c r="G575" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H575" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I575" s="1"/>
       <c r="J575" s="1"/>
@@ -17807,18 +17814,18 @@
         <v>-80</v>
       </c>
       <c r="C576" s="4">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="D576" s="4">
-        <v>-20</v>
-      </c>
-      <c r="E576" s="1"/>
-      <c r="F576" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E576" s="2"/>
+      <c r="F576" s="2"/>
       <c r="G576" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H576" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I576" s="1"/>
       <c r="J576" s="1"/>
@@ -17845,10 +17852,10 @@
       <c r="E577" s="2"/>
       <c r="F577" s="2"/>
       <c r="G577" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H577" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I577" s="1"/>
       <c r="J577" s="1"/>
@@ -17875,10 +17882,10 @@
       <c r="E578" s="2"/>
       <c r="F578" s="2"/>
       <c r="G578" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H578" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I578" s="1"/>
       <c r="J578" s="1"/>
@@ -17902,13 +17909,13 @@
       <c r="D579" s="4">
         <v>0</v>
       </c>
-      <c r="E579" s="2"/>
-      <c r="F579" s="2"/>
+      <c r="E579" s="1"/>
+      <c r="F579" s="1"/>
       <c r="G579" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H579" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I579" s="1"/>
       <c r="J579" s="1"/>
@@ -17935,10 +17942,10 @@
       <c r="E580" s="1"/>
       <c r="F580" s="1"/>
       <c r="G580" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H580" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I580" s="1"/>
       <c r="J580" s="1"/>
@@ -17957,19 +17964,17 @@
         <v>-80</v>
       </c>
       <c r="C581" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D581" s="4">
-        <v>0</v>
-      </c>
-      <c r="E581" s="1"/>
-      <c r="F581" s="1"/>
+        <v>-5</v>
+      </c>
+      <c r="E581" s="2"/>
+      <c r="F581" s="2"/>
       <c r="G581" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H581" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H581" s="1"/>
       <c r="I581" s="1"/>
       <c r="J581" s="1"/>
       <c r="K581" s="1"/>
@@ -17990,12 +17995,12 @@
         <v>0</v>
       </c>
       <c r="D582" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E582" s="2"/>
       <c r="F582" s="2"/>
       <c r="G582" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H582" s="1"/>
       <c r="I582" s="1"/>
@@ -18018,12 +18023,12 @@
         <v>0</v>
       </c>
       <c r="D583" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E583" s="2"/>
       <c r="F583" s="2"/>
       <c r="G583" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H583" s="1"/>
       <c r="I583" s="1"/>
@@ -18043,15 +18048,15 @@
         <v>-80</v>
       </c>
       <c r="C584" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D584" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E584" s="2"/>
       <c r="F584" s="2"/>
       <c r="G584" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H584" s="1"/>
       <c r="I584" s="1"/>
@@ -18074,12 +18079,12 @@
         <v>-5</v>
       </c>
       <c r="D585" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E585" s="2"/>
       <c r="F585" s="2"/>
       <c r="G585" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H585" s="1"/>
       <c r="I585" s="1"/>
@@ -18102,12 +18107,12 @@
         <v>-5</v>
       </c>
       <c r="D586" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E586" s="2"/>
       <c r="F586" s="2"/>
       <c r="G586" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H586" s="1"/>
       <c r="I586" s="1"/>
@@ -18130,12 +18135,12 @@
         <v>-5</v>
       </c>
       <c r="D587" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E587" s="2"/>
       <c r="F587" s="2"/>
       <c r="G587" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H587" s="1"/>
       <c r="I587" s="1"/>
@@ -18155,15 +18160,15 @@
         <v>-80</v>
       </c>
       <c r="C588" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D588" s="4">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E588" s="2"/>
       <c r="F588" s="2"/>
       <c r="G588" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H588" s="1"/>
       <c r="I588" s="1"/>
@@ -18186,12 +18191,12 @@
         <v>-10</v>
       </c>
       <c r="D589" s="4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E589" s="2"/>
       <c r="F589" s="2"/>
       <c r="G589" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H589" s="1"/>
       <c r="I589" s="1"/>
@@ -18214,12 +18219,12 @@
         <v>-10</v>
       </c>
       <c r="D590" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E590" s="2"/>
       <c r="F590" s="2"/>
       <c r="G590" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H590" s="1"/>
       <c r="I590" s="1"/>
@@ -18242,12 +18247,12 @@
         <v>-10</v>
       </c>
       <c r="D591" s="4">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E591" s="2"/>
       <c r="F591" s="2"/>
       <c r="G591" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H591" s="1"/>
       <c r="I591" s="1"/>
@@ -18259,34 +18264,6 @@
       <c r="O591" s="1"/>
       <c r="P591" s="1"/>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A592" s="4">
-        <v>-45</v>
-      </c>
-      <c r="B592" s="4">
-        <v>-80</v>
-      </c>
-      <c r="C592" s="4">
-        <v>-10</v>
-      </c>
-      <c r="D592" s="4">
-        <v>-15</v>
-      </c>
-      <c r="E592" s="2"/>
-      <c r="F592" s="2"/>
-      <c r="G592" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H592" s="1"/>
-      <c r="I592" s="1"/>
-      <c r="J592" s="1"/>
-      <c r="K592" s="1"/>
-      <c r="L592" s="1"/>
-      <c r="M592" s="1"/>
-      <c r="N592" s="1"/>
-      <c r="O592" s="1"/>
-      <c r="P592" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
